--- a/AAII_Financials/Quarterly/BEAM_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BEAM_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="92">
   <si>
     <t>BEAM</t>
   </si>
@@ -656,153 +656,156 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AA102"/>
+  <dimension ref="A5:AB102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="27" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="28" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Z7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AA7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>316200</v>
+      </c>
+      <c r="E8" s="3">
         <v>17200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>20100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>24200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>20000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>15800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>16700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>8400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>51100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>800</v>
       </c>
-      <c r="M8" s="3">
-        <v>0</v>
-      </c>
       <c r="N8" s="3">
         <v>0</v>
       </c>
@@ -845,8 +848,11 @@
       <c r="AA8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -922,8 +928,11 @@
       <c r="AA9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -999,8 +1008,11 @@
       <c r="AA10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1028,85 +1040,89 @@
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB11" s="3"/>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>140100</v>
+      </c>
+      <c r="E12" s="3">
         <v>100100</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>97600</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>99600</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>86300</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>85300</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>74600</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>65400</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>96800</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>54600</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>45600</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>190100</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>32500</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>29800</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>19400</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>21500</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>20200</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>12500</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>34500</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>9200</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>29600</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>9900</v>
       </c>
-      <c r="Y12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1182,8 +1198,11 @@
       <c r="AA13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1259,8 +1278,11 @@
       <c r="AA14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1336,8 +1358,11 @@
       <c r="AA15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1362,162 +1387,169 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
-    </row>
-    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB16" s="3"/>
+    </row>
+    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>183300</v>
+      </c>
+      <c r="E17" s="3">
         <v>125500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>122300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>123100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>109000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>107100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>98600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>84700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>114600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>70400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>59000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>200400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>40800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>37300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>26300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>28400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>26400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>18000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>48400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>13100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>39800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>12700</v>
       </c>
-      <c r="Y17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>132900</v>
+      </c>
+      <c r="E18" s="3">
         <v>-108300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-102200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-98900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-89000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-91300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-81900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-76300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-63500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-69600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-59000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-200400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-40800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-37300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-26300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-28400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-26400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-18000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-48400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-13100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-39800</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-12700</v>
       </c>
-      <c r="Y18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1545,162 +1577,169 @@
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
-    </row>
-    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB19" s="3"/>
+    </row>
+    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>11300</v>
+      </c>
+      <c r="E20" s="3">
         <v>12200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>19400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>2500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>51700</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>9600</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>10000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>7000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-1300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>41500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-17300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-1200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-54700</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>2900</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-7900</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-2100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-1400</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-900</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>30600</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-500</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>14600</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-58500</v>
       </c>
-      <c r="Y20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>149500</v>
+      </c>
+      <c r="E21" s="3">
         <v>-90900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-78000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-91800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-33400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-78200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-68500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-65900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-62100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-26400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-74600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-200200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-94200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-33200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-33100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-29400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-26700</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-19600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-15400</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-12900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-24000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-71100</v>
       </c>
-      <c r="Y21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1731,8 +1770,8 @@
       <c r="L22" s="3">
         <v>0</v>
       </c>
-      <c r="M22" s="3" t="s">
-        <v>3</v>
+      <c r="M22" s="3">
+        <v>0</v>
       </c>
       <c r="N22" s="3" t="s">
         <v>3</v>
@@ -1749,14 +1788,14 @@
       <c r="R22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S22" s="3">
-        <v>100</v>
+      <c r="S22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T22" s="3">
         <v>100</v>
       </c>
-      <c r="U22" s="3" t="s">
-        <v>3</v>
+      <c r="U22" s="3">
+        <v>100</v>
       </c>
       <c r="V22" s="3" t="s">
         <v>3</v>
@@ -1776,106 +1815,112 @@
       <c r="AA22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>144200</v>
+      </c>
+      <c r="E23" s="3">
         <v>-96100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-82800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-96500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-37300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-81700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-72000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-69200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-64700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-28100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-76300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-201600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-95500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-34500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-34200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-30500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-27900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-19000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-17900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-13600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-25200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-71200</v>
       </c>
-      <c r="Y23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>0</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>3</v>
+        <v>1400</v>
+      </c>
+      <c r="E24" s="3">
+        <v>0</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G24" s="3">
+      <c r="G24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H24" s="3">
         <v>1000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>2400</v>
       </c>
-      <c r="I24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1909,18 +1954,18 @@
       <c r="T24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U24" s="3">
+      <c r="U24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V24" s="3">
         <v>-31500</v>
       </c>
-      <c r="V24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W24" s="3">
+      <c r="W24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X24" s="3">
         <v>-96300</v>
       </c>
-      <c r="X24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1930,8 +1975,11 @@
       <c r="AA24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2007,162 +2055,171 @@
       <c r="AA25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>142800</v>
+      </c>
+      <c r="E26" s="3">
         <v>-96100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-82800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-96500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-38300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-84100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-72000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-69200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-64700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-28100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-76300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-201600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-95500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-34500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-34200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-30500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-27900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-19000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-17900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-13600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-23800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-71200</v>
       </c>
-      <c r="Y26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>142800</v>
+      </c>
+      <c r="E27" s="3">
         <v>-96100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-82800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-96500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-38300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-109600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-72000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-69200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-64700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-28100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-76300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-201600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-95500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-34500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-34200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-31700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-31100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-22300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-52600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-16600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-216700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-70400</v>
       </c>
-      <c r="Y27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2238,8 +2295,11 @@
       <c r="AA28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2315,8 +2375,11 @@
       <c r="AA29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2392,8 +2455,11 @@
       <c r="AA30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2469,162 +2535,171 @@
       <c r="AA31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-11300</v>
+      </c>
+      <c r="E32" s="3">
         <v>-12200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-19400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-2500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-51700</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-9600</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-10000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-7000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>1300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-41500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>17300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>1200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>54700</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-2900</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>7900</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>2100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>1400</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>900</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-30600</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>500</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-14600</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>58500</v>
       </c>
-      <c r="Y32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>142800</v>
+      </c>
+      <c r="E33" s="3">
         <v>-96100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-82800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-96500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-38300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-109600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-72000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-69200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-64700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-28100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-76300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-201600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-95500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-34500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-34200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-31700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-31100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-22300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-52600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-16600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-216700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-70400</v>
       </c>
-      <c r="Y33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2700,167 +2775,176 @@
       <c r="AA34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>142800</v>
+      </c>
+      <c r="E35" s="3">
         <v>-96100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-82800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-96500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-38300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-109600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-72000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-69200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-64700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-28100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-76300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-201600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-95500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-34500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-34200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-31700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-31100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-22300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-52600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-16600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-216700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-70400</v>
       </c>
-      <c r="Y35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Z38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AA38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2888,8 +2972,9 @@
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
-    </row>
-    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB39" s="3"/>
+    </row>
+    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2917,68 +3002,69 @@
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
-    </row>
-    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB40" s="3"/>
+    </row>
+    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>435900</v>
+      </c>
+      <c r="E41" s="3">
         <v>169000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>225500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>249800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>232800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>156500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>265600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>296800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>560000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>612000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>212000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>97200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>162200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>137900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>125300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>126100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>37200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>37800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>37900</v>
       </c>
-      <c r="V41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2994,68 +3080,71 @@
       <c r="AA41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>754000</v>
+      </c>
+      <c r="E42" s="3">
         <v>846400</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>847500</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>809700</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>845400</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>938000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>900500</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>925800</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>405700</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>321400</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>403300</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>406200</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>137500</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>64300</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>102600</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>127400</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>54600</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>73100</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>88900</v>
       </c>
-      <c r="V42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3071,19 +3160,22 @@
       <c r="AA42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F43" s="3" t="s">
-        <v>3</v>
+      <c r="D43" s="3">
+        <v>0</v>
+      </c>
+      <c r="E43" s="3">
+        <v>0</v>
+      </c>
+      <c r="F43" s="3">
+        <v>0</v>
       </c>
       <c r="G43" s="3">
         <v>0</v>
@@ -3098,17 +3190,17 @@
         <v>0</v>
       </c>
       <c r="K43" s="3">
+        <v>0</v>
+      </c>
+      <c r="L43" s="3">
         <v>300000</v>
       </c>
-      <c r="L43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M43" s="3">
+      <c r="M43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N43" s="3">
         <v>50000</v>
       </c>
-      <c r="N43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3124,8 +3216,8 @@
       <c r="S43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T43" s="3">
-        <v>0</v>
+      <c r="T43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U43" s="3">
         <v>0</v>
@@ -3148,8 +3240,11 @@
       <c r="AA43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3225,68 +3320,71 @@
       <c r="AA44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>21200</v>
+      </c>
+      <c r="E45" s="3">
         <v>24100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>21800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>23600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>14800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>14400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>13800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>16900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>7400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>8000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>12700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>11100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>8700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>6500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>6900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>6200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>2700</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>3900</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>2600</v>
       </c>
-      <c r="V45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3302,68 +3400,71 @@
       <c r="AA45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1211000</v>
+      </c>
+      <c r="E46" s="3">
         <v>1039500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1094800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1083000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1092900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1108900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1179900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1239500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1273000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>941400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>678000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>514600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>308300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>208700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>234800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>259600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>94500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>114800</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>129400</v>
       </c>
-      <c r="V46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3379,8 +3480,11 @@
       <c r="AA46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3405,18 +3509,18 @@
       <c r="J47" s="3">
         <v>0</v>
       </c>
-      <c r="K47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L47" s="3">
+      <c r="K47" s="3">
+        <v>0</v>
+      </c>
+      <c r="L47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M47" s="3">
         <v>24500</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>29400</v>
       </c>
-      <c r="N47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3432,8 +3536,8 @@
       <c r="S47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T47" s="3">
-        <v>0</v>
+      <c r="T47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U47" s="3">
         <v>0</v>
@@ -3456,68 +3560,71 @@
       <c r="AA47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>237800</v>
+      </c>
+      <c r="E48" s="3">
         <v>239700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>242300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>238000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>234100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>226700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>223500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>199800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>187000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>174700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>169700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>158800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>125400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>51200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>48600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>46900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>43200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>38000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>36800</v>
       </c>
-      <c r="V48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3533,8 +3640,11 @@
       <c r="AA48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3610,8 +3720,11 @@
       <c r="AA49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3687,8 +3800,11 @@
       <c r="AA50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3764,68 +3880,71 @@
       <c r="AA51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>10900</v>
+      </c>
+      <c r="E52" s="3">
         <v>11300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>16800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>11300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>14700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>14600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>15000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>14100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>14500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>15900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>16000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>19900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>18000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>18400</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>16600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>16100</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>18300</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>17800</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>14400</v>
       </c>
-      <c r="V52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3841,8 +3960,11 @@
       <c r="AA52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3918,68 +4040,71 @@
       <c r="AA53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1459700</v>
+      </c>
+      <c r="E54" s="3">
         <v>1290500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1353900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1332400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1341700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1350300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1418400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1453400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1474500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1156600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>893100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>693200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>451700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>278300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>300000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>322600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>156100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>170600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>180500</v>
       </c>
-      <c r="V54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3995,8 +4120,11 @@
       <c r="AA54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4024,8 +4152,9 @@
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
-    </row>
-    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB55" s="3"/>
+    </row>
+    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4053,68 +4182,69 @@
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
-    </row>
-    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB56" s="3"/>
+    </row>
+    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E57" s="3">
         <v>3200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>6900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>14100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>9000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>7000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>7100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>6300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>7500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>7300</v>
-      </c>
-      <c r="M57" s="3">
-        <v>8000</v>
       </c>
       <c r="N57" s="3">
         <v>8000</v>
       </c>
       <c r="O57" s="3">
+        <v>8000</v>
+      </c>
+      <c r="P57" s="3">
         <v>6300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>6600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>6200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>6100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>7800</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>3900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>4000</v>
       </c>
-      <c r="V57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4130,49 +4260,52 @@
       <c r="AA57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>500</v>
+      </c>
+      <c r="E58" s="3">
         <v>1100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>2200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>2400</v>
-      </c>
-      <c r="J58" s="3">
-        <v>2300</v>
       </c>
       <c r="K58" s="3">
         <v>2300</v>
       </c>
       <c r="L58" s="3">
-        <v>2200</v>
+        <v>2300</v>
       </c>
       <c r="M58" s="3">
         <v>2200</v>
       </c>
       <c r="N58" s="3">
-        <v>2100</v>
+        <v>2200</v>
       </c>
       <c r="O58" s="3">
         <v>2100</v>
       </c>
       <c r="P58" s="3">
-        <v>1700</v>
+        <v>2100</v>
       </c>
       <c r="Q58" s="3">
         <v>1700</v>
@@ -4181,17 +4314,17 @@
         <v>1700</v>
       </c>
       <c r="S58" s="3">
+        <v>1700</v>
+      </c>
+      <c r="T58" s="3">
         <v>1300</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>800</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>7300</v>
       </c>
-      <c r="V58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W58" s="3" t="s">
         <v>3</v>
       </c>
@@ -4207,68 +4340,71 @@
       <c r="AA58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>203500</v>
+      </c>
+      <c r="E59" s="3">
         <v>216100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>201700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>204400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>212700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>229600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>202800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>210200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>203700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>91900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>118500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>92000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>93900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>39100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>31100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>23700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>20000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>15300</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>56200</v>
       </c>
-      <c r="V59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4284,68 +4420,71 @@
       <c r="AA59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>205600</v>
+      </c>
+      <c r="E60" s="3">
         <v>220400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>209500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>219900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>223600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>238900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>212300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>218800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>213400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>101400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>128700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>102100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>102300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>47500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>39000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>31400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>29100</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>19900</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>52200</v>
       </c>
-      <c r="V60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4361,68 +4500,71 @@
       <c r="AA60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>0</v>
+      </c>
+      <c r="E61" s="3">
         <v>300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>3000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>3600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>4200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>4700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>5300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>4400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>4900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>5300</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>4400</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>2800</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>300</v>
       </c>
-      <c r="V61" s="3">
-        <v>0</v>
-      </c>
       <c r="W61" s="3">
         <v>0</v>
       </c>
@@ -4438,65 +4580,68 @@
       <c r="AA61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>272800</v>
+      </c>
+      <c r="E62" s="3">
         <v>290900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>331800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>349900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>383500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>395500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>404100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>403100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>431300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>197800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>211600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>164000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>98500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>26300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>25300</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>24500</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>21600</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>21100</v>
       </c>
-      <c r="U62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4515,8 +4660,11 @@
       <c r="AA62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4592,8 +4740,11 @@
       <c r="AA63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4669,8 +4820,11 @@
       <c r="AA64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4746,68 +4900,71 @@
       <c r="AA65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>478400</v>
+      </c>
+      <c r="E66" s="3">
         <v>511600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>542200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>570800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>608200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>635800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>618200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>624300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>647700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>302700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>344500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>270800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>206100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>78200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>69200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>61200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>55200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>43800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>36900</v>
       </c>
-      <c r="V66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4823,8 +4980,11 @@
       <c r="AA66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4852,8 +5012,9 @@
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
-    </row>
-    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB67" s="3"/>
+    </row>
+    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4929,8 +5090,11 @@
       <c r="AA68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5006,8 +5170,11 @@
       <c r="AA69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5057,17 +5224,17 @@
         <v>0</v>
       </c>
       <c r="S70" s="3">
+        <v>0</v>
+      </c>
+      <c r="T70" s="3">
         <v>302000</v>
       </c>
-      <c r="T70" s="3">
+      <c r="U70" s="3">
         <v>298800</v>
       </c>
-      <c r="U70" s="3">
+      <c r="V70" s="3">
         <v>439200</v>
       </c>
-      <c r="V70" s="3">
-        <v>0</v>
-      </c>
       <c r="W70" s="3">
         <v>0</v>
       </c>
@@ -5083,8 +5250,11 @@
       <c r="AA70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5160,68 +5330,71 @@
       <c r="AA71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1189900</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1332700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1236600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1153800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1057400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-1019000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-909400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-837500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-768300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-703600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-675400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-599200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-397600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-302200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-267700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-233500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-203000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-175200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-156200</v>
       </c>
-      <c r="V72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5237,8 +5410,11 @@
       <c r="AA72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5314,8 +5490,11 @@
       <c r="AA73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5391,8 +5570,11 @@
       <c r="AA74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5468,68 +5650,71 @@
       <c r="AA75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>981300</v>
+      </c>
+      <c r="E76" s="3">
         <v>778900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>811600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>761500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>733500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>714500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>800200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>829100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>826700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>853800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>548600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>422400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>245600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>200100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>230800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>261400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>-201100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>-172100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>-295500</v>
       </c>
-      <c r="V76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5545,8 +5730,11 @@
       <c r="AA76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5622,167 +5810,176 @@
       <c r="AA77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Z80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AA80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>142800</v>
+      </c>
+      <c r="E81" s="3">
         <v>-96100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-82800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-96500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-38300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-109600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-72000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-69200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-64700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-28100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-76300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-201600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-95500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-34500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-34200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-31700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-31100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-22300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-52600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-16600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-216700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-70400</v>
       </c>
-      <c r="Y81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5810,85 +6007,89 @@
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
-    </row>
-    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB82" s="3"/>
+    </row>
+    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>5400</v>
+      </c>
+      <c r="E83" s="3">
         <v>5200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>4800</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>4600</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>3900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>3500</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>3400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>3300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>2600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>1800</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>1700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>1400</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>1300</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>1200</v>
-      </c>
-      <c r="Q83" s="3">
-        <v>1100</v>
       </c>
       <c r="R83" s="3">
         <v>1100</v>
       </c>
       <c r="S83" s="3">
+        <v>1100</v>
+      </c>
+      <c r="T83" s="3">
         <v>1000</v>
-      </c>
-      <c r="T83" s="3">
-        <v>900</v>
       </c>
       <c r="U83" s="3">
         <v>900</v>
       </c>
       <c r="V83" s="3">
+        <v>900</v>
+      </c>
+      <c r="W83" s="3">
         <v>700</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>500</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>100</v>
       </c>
-      <c r="Y83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z83" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5964,8 +6165,11 @@
       <c r="AA84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6041,8 +6245,11 @@
       <c r="AA85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6118,8 +6325,11 @@
       <c r="AA86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6195,8 +6405,11 @@
       <c r="AA87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6272,85 +6485,91 @@
       <c r="AA88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>135100</v>
+      </c>
+      <c r="E89" s="3">
         <v>-89800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-84700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-109800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-69200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-74500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-52300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>218500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>3000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-32500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-38600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-24300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-21200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-22800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-27400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-17800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-17000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>16900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-25900</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>4200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-9400</v>
       </c>
-      <c r="Y89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6378,85 +6597,89 @@
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
-    </row>
-    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB90" s="3"/>
+    </row>
+    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="E91" s="3">
         <v>-7900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-16200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-6000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-8300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-11800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-21600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-7300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-13400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-5800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-16200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-11500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-8100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-2800</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-2400</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-3000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-2200</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-1400</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-6600</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-2400</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-11200</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-700</v>
       </c>
-      <c r="Y91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z91" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6532,8 +6755,11 @@
       <c r="AA92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6609,85 +6835,91 @@
       <c r="AA93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>98100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-10200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-41500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>25500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>113400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-36200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-537300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-77500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>76100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-13100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-279600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-81400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>35200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>22900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-76800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>16600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-83200</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>2400</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-2400</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>22000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-2200</v>
       </c>
-      <c r="Y94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6715,8 +6947,9 @@
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
-    </row>
-    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB95" s="3"/>
+    </row>
+    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6792,8 +7025,11 @@
       <c r="AA96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6869,8 +7105,11 @@
       <c r="AA97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6946,8 +7185,11 @@
       <c r="AA98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7023,85 +7265,91 @@
       <c r="AA99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>33700</v>
+      </c>
+      <c r="E100" s="3">
         <v>36800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>107500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>98400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>32000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>1600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>22300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>55700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>21500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>320900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>160400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>253300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>130000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>193000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>700</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>2700</v>
       </c>
-      <c r="U100" s="3">
-        <v>0</v>
-      </c>
       <c r="V100" s="3">
+        <v>0</v>
+      </c>
+      <c r="W100" s="3">
         <v>37900</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>120100</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>9900</v>
       </c>
-      <c r="Y100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7177,81 +7425,87 @@
       <c r="AA101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>266900</v>
+      </c>
+      <c r="E102" s="3">
         <v>-63200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-18600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>14100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>76300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-109100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-31200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-263200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-54100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>400000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>114800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-64900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>24300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>14100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>88800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-106500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>9700</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>105900</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-500</v>
       </c>
-      <c r="Y102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BEAM_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BEAM_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="92">
   <si>
     <t>BEAM</t>
   </si>
@@ -656,159 +656,163 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AB102"/>
+  <dimension ref="A5:AC102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="28" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="29" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Z7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AA7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AB7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>7400</v>
+      </c>
+      <c r="E8" s="3">
         <v>316200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>17200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>20100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>24200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>20000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>15800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>16700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>8400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>51100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>800</v>
       </c>
-      <c r="N8" s="3">
-        <v>0</v>
-      </c>
       <c r="O8" s="3">
         <v>0</v>
       </c>
@@ -851,8 +855,11 @@
       <c r="AB8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -931,8 +938,11 @@
       <c r="AB9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1011,8 +1021,11 @@
       <c r="AB10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1041,88 +1054,92 @@
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
-    </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC11" s="3"/>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>84800</v>
+      </c>
+      <c r="E12" s="3">
         <v>140100</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>100100</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>97600</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>99600</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>86300</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>85300</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>74600</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>65400</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>96800</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>54600</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>45600</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>190100</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>32500</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>29800</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>19400</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>21500</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>20200</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>12500</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>34500</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>9200</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>29600</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>9900</v>
       </c>
-      <c r="Z12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1201,8 +1218,11 @@
       <c r="AB13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1281,8 +1301,11 @@
       <c r="AB14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1361,8 +1384,11 @@
       <c r="AB15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1388,168 +1414,175 @@
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
-    </row>
-    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC16" s="3"/>
+    </row>
+    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>111500</v>
+      </c>
+      <c r="E17" s="3">
         <v>183300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>125500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>122300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>123100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>109000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>107100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>98600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>84700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>114600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>70400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>59000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>200400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>40800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>37300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>26300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>28400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>26400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>18000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>48400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>13100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>39800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>12700</v>
       </c>
-      <c r="Z17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-104100</v>
+      </c>
+      <c r="E18" s="3">
         <v>132900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-108300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-102200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-98900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-89000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-91300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-81900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-76300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-63500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-69600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-59000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-200400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-40800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-37300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-26300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-28400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-26400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-18000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-48400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-13100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-39800</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-12700</v>
       </c>
-      <c r="Z18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1578,168 +1611,175 @@
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
-    </row>
-    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC19" s="3"/>
+    </row>
+    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>5500</v>
+      </c>
+      <c r="E20" s="3">
         <v>11300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>12200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>19400</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>2500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>51700</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>9600</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>10000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>7000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-1300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>41500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-17300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-1200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-54700</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>2900</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-7900</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-2100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-1400</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-900</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>30600</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-500</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>14600</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-58500</v>
       </c>
-      <c r="Z20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-93200</v>
+      </c>
+      <c r="E21" s="3">
         <v>149500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-90900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-78000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-91800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-33400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-78200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-68500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-65900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-62100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-26400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-74600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-200200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-94200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-33200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-33100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-29400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-26700</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-19600</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-15400</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-12900</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-24000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-71100</v>
       </c>
-      <c r="Z21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1773,8 +1813,8 @@
       <c r="M22" s="3">
         <v>0</v>
       </c>
-      <c r="N22" s="3" t="s">
-        <v>3</v>
+      <c r="N22" s="3">
+        <v>0</v>
       </c>
       <c r="O22" s="3" t="s">
         <v>3</v>
@@ -1791,14 +1831,14 @@
       <c r="S22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T22" s="3">
-        <v>100</v>
+      <c r="T22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U22" s="3">
         <v>100</v>
       </c>
-      <c r="V22" s="3" t="s">
-        <v>3</v>
+      <c r="V22" s="3">
+        <v>100</v>
       </c>
       <c r="W22" s="3" t="s">
         <v>3</v>
@@ -1818,112 +1858,118 @@
       <c r="AB22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-98700</v>
+      </c>
+      <c r="E23" s="3">
         <v>144200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-96100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-82800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-96500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-37300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-81700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-72000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-69200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-64700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-28100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-76300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-201600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-95500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-34500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-34200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-30500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-27900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-19000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-17900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-13600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-25200</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-71200</v>
       </c>
-      <c r="Z23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
+      <c r="D24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E24" s="3">
         <v>1400</v>
       </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>3</v>
+      <c r="F24" s="3">
+        <v>0</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H24" s="3">
+      <c r="H24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I24" s="3">
         <v>1000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>2400</v>
       </c>
-      <c r="J24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1957,18 +2003,18 @@
       <c r="U24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V24" s="3">
+      <c r="V24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W24" s="3">
         <v>-31500</v>
       </c>
-      <c r="W24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X24" s="3">
+      <c r="X24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y24" s="3">
         <v>-96300</v>
       </c>
-      <c r="Y24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1978,8 +2024,11 @@
       <c r="AB24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2058,168 +2107,177 @@
       <c r="AB25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-98700</v>
+      </c>
+      <c r="E26" s="3">
         <v>142800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-96100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-82800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-96500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-38300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-84100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-72000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-69200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-64700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-28100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-76300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-201600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-95500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-34500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-34200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-30500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-27900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-19000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-17900</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-13600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-23800</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-71200</v>
       </c>
-      <c r="Z26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-98700</v>
+      </c>
+      <c r="E27" s="3">
         <v>142800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-96100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-82800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-96500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-38300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-109600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-72000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-69200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-64700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-28100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-76300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-201600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-95500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-34500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-34200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-31700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-31100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-22300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-52600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-16600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-216700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-70400</v>
       </c>
-      <c r="Z27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2298,8 +2356,11 @@
       <c r="AB28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2378,8 +2439,11 @@
       <c r="AB29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2458,8 +2522,11 @@
       <c r="AB30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2538,168 +2605,177 @@
       <c r="AB31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="E32" s="3">
         <v>-11300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-12200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-19400</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-2500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-51700</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-9600</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-10000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-7000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>1300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-41500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>17300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>1200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>54700</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-2900</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>7900</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>2100</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>1400</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>900</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-30600</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>500</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-14600</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>58500</v>
       </c>
-      <c r="Z32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-98700</v>
+      </c>
+      <c r="E33" s="3">
         <v>142800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-96100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-82800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-96500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-38300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-109600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-72000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-69200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-64700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-28100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-76300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-201600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-95500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-34500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-34200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-31700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-31100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-22300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-52600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-16600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-216700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-70400</v>
       </c>
-      <c r="Z33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2778,173 +2854,182 @@
       <c r="AB34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-98700</v>
+      </c>
+      <c r="E35" s="3">
         <v>142800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-96100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-82800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-96500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-38300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-109600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-72000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-69200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-64700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-28100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-76300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-201600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-95500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-34500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-34200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-31700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-31100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-22300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-52600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-16600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-216700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-70400</v>
       </c>
-      <c r="Z35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Z38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AA38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AB38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2973,8 +3058,9 @@
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
-    </row>
-    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC39" s="3"/>
+    </row>
+    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3003,71 +3089,72 @@
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
-    </row>
-    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC40" s="3"/>
+    </row>
+    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>287800</v>
+      </c>
+      <c r="E41" s="3">
         <v>435900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>169000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>225500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>249800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>232800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>156500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>265600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>296800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>560000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>612000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>212000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>97200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>162200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>137900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>125300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>126100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>37200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>37800</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>37900</v>
       </c>
-      <c r="W41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3083,71 +3170,74 @@
       <c r="AB41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>806700</v>
+      </c>
+      <c r="E42" s="3">
         <v>754000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>846400</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>847500</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>809700</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>845400</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>938000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>900500</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>925800</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>405700</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>321400</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>403300</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>406200</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>137500</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>64300</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>102600</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>127400</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>54600</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>73100</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>88900</v>
       </c>
-      <c r="W42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3163,8 +3253,11 @@
       <c r="AB42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3193,17 +3286,17 @@
         <v>0</v>
       </c>
       <c r="L43" s="3">
+        <v>0</v>
+      </c>
+      <c r="M43" s="3">
         <v>300000</v>
       </c>
-      <c r="M43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N43" s="3">
+      <c r="N43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O43" s="3">
         <v>50000</v>
       </c>
-      <c r="O43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3219,8 +3312,8 @@
       <c r="T43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U43" s="3">
-        <v>0</v>
+      <c r="U43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V43" s="3">
         <v>0</v>
@@ -3243,8 +3336,11 @@
       <c r="AB43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3323,71 +3419,74 @@
       <c r="AB44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>27200</v>
+      </c>
+      <c r="E45" s="3">
         <v>21200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>24100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>21800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>23600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>14800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>14400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>13800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>16900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>7400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>8000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>12700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>11100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>8700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>6500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>6900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>6200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>2700</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>3900</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>2600</v>
       </c>
-      <c r="W45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3403,71 +3502,74 @@
       <c r="AB45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1121700</v>
+      </c>
+      <c r="E46" s="3">
         <v>1211000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1039500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1094800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1083000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1092900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1108900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1179900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1239500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1273000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>941400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>678000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>514600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>308300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>208700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>234800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>259600</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>94500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>114800</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>129400</v>
       </c>
-      <c r="W46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3483,8 +3585,11 @@
       <c r="AB46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3512,18 +3617,18 @@
       <c r="K47" s="3">
         <v>0</v>
       </c>
-      <c r="L47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M47" s="3">
+      <c r="L47" s="3">
+        <v>0</v>
+      </c>
+      <c r="M47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N47" s="3">
         <v>24500</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>29400</v>
       </c>
-      <c r="O47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3539,8 +3644,8 @@
       <c r="T47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U47" s="3">
-        <v>0</v>
+      <c r="U47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V47" s="3">
         <v>0</v>
@@ -3563,71 +3668,74 @@
       <c r="AB47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>229900</v>
+      </c>
+      <c r="E48" s="3">
         <v>237800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>239700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>242300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>238000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>234100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>226700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>223500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>199800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>187000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>174700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>169700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>158800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>125400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>51200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>48600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>46900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>43200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>38000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>36800</v>
       </c>
-      <c r="W48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3643,8 +3751,11 @@
       <c r="AB48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3723,8 +3834,11 @@
       <c r="AB49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3803,8 +3917,11 @@
       <c r="AB50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3883,71 +4000,74 @@
       <c r="AB51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>8100</v>
+      </c>
+      <c r="E52" s="3">
         <v>10900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>11300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>16800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>11300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>14700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>14600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>15000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>14100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>14500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>15900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>16000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>19900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>18000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>18400</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>16600</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>16100</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>18300</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>17800</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>14400</v>
       </c>
-      <c r="W52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3963,8 +4083,11 @@
       <c r="AB52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4043,71 +4166,74 @@
       <c r="AB53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1359800</v>
+      </c>
+      <c r="E54" s="3">
         <v>1459700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1290500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1353900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1332400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1341700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1350300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1418400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1453400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1474500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1156600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>893100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>693200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>451700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>278300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>300000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>322600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>156100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>170600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>180500</v>
       </c>
-      <c r="W54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4123,8 +4249,11 @@
       <c r="AB54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4153,8 +4282,9 @@
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
-    </row>
-    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC55" s="3"/>
+    </row>
+    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4183,71 +4313,72 @@
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
-    </row>
-    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC56" s="3"/>
+    </row>
+    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E57" s="3">
         <v>1600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>3200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>6900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>14100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>9000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>7000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>7100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>6300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>7500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>7300</v>
-      </c>
-      <c r="N57" s="3">
-        <v>8000</v>
       </c>
       <c r="O57" s="3">
         <v>8000</v>
       </c>
       <c r="P57" s="3">
+        <v>8000</v>
+      </c>
+      <c r="Q57" s="3">
         <v>6300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>6600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>6200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>6100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>7800</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>3900</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>4000</v>
       </c>
-      <c r="W57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4263,52 +4394,55 @@
       <c r="AB57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3">
+      <c r="D58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E58" s="3">
         <v>500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>2200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>2400</v>
-      </c>
-      <c r="K58" s="3">
-        <v>2300</v>
       </c>
       <c r="L58" s="3">
         <v>2300</v>
       </c>
       <c r="M58" s="3">
-        <v>2200</v>
+        <v>2300</v>
       </c>
       <c r="N58" s="3">
         <v>2200</v>
       </c>
       <c r="O58" s="3">
-        <v>2100</v>
+        <v>2200</v>
       </c>
       <c r="P58" s="3">
         <v>2100</v>
       </c>
       <c r="Q58" s="3">
-        <v>1700</v>
+        <v>2100</v>
       </c>
       <c r="R58" s="3">
         <v>1700</v>
@@ -4317,17 +4451,17 @@
         <v>1700</v>
       </c>
       <c r="T58" s="3">
+        <v>1700</v>
+      </c>
+      <c r="U58" s="3">
         <v>1300</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>800</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>7300</v>
       </c>
-      <c r="W58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X58" s="3" t="s">
         <v>3</v>
       </c>
@@ -4343,71 +4477,74 @@
       <c r="AB58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>184400</v>
+      </c>
+      <c r="E59" s="3">
         <v>203500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>216100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>201700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>204400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>212700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>229600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>202800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>210200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>203700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>91900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>118500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>92000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>93900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>39100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>31100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>23700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>20000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>15300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>56200</v>
       </c>
-      <c r="W59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4423,71 +4560,74 @@
       <c r="AB59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>187200</v>
+      </c>
+      <c r="E60" s="3">
         <v>205600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>220400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>209500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>219900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>223600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>238900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>212300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>218800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>213400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>101400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>128700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>102100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>102300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>47500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>39000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>31400</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>29100</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>19900</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>52200</v>
       </c>
-      <c r="W60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4503,8 +4643,11 @@
       <c r="AB60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4512,62 +4655,62 @@
         <v>0</v>
       </c>
       <c r="E61" s="3">
+        <v>0</v>
+      </c>
+      <c r="F61" s="3">
         <v>300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>3000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>3600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>4200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>4700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>5300</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>4400</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>4900</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>5300</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>4400</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>2800</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>300</v>
       </c>
-      <c r="W61" s="3">
-        <v>0</v>
-      </c>
       <c r="X61" s="3">
         <v>0</v>
       </c>
@@ -4583,68 +4726,71 @@
       <c r="AB61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>259100</v>
+      </c>
+      <c r="E62" s="3">
         <v>272800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>290900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>331800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>349900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>383500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>395500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>404100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>403100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>431300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>197800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>211600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>164000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>98500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>26300</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>25300</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>24500</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>21600</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>21100</v>
       </c>
-      <c r="V62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4663,8 +4809,11 @@
       <c r="AB62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4743,8 +4892,11 @@
       <c r="AB63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4823,8 +4975,11 @@
       <c r="AB64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4903,71 +5058,74 @@
       <c r="AB65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>446300</v>
+      </c>
+      <c r="E66" s="3">
         <v>478400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>511600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>542200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>570800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>608200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>635800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>618200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>624300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>647700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>302700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>344500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>270800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>206100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>78200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>69200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>61200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>55200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>43800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>36900</v>
       </c>
-      <c r="W66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4983,8 +5141,11 @@
       <c r="AB66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5013,8 +5174,9 @@
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
-    </row>
-    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC67" s="3"/>
+    </row>
+    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5093,8 +5255,11 @@
       <c r="AB68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5173,8 +5338,11 @@
       <c r="AB69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5227,17 +5395,17 @@
         <v>0</v>
       </c>
       <c r="T70" s="3">
+        <v>0</v>
+      </c>
+      <c r="U70" s="3">
         <v>302000</v>
       </c>
-      <c r="U70" s="3">
+      <c r="V70" s="3">
         <v>298800</v>
       </c>
-      <c r="V70" s="3">
+      <c r="W70" s="3">
         <v>439200</v>
       </c>
-      <c r="W70" s="3">
-        <v>0</v>
-      </c>
       <c r="X70" s="3">
         <v>0</v>
       </c>
@@ -5253,8 +5421,11 @@
       <c r="AB70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5333,71 +5504,74 @@
       <c r="AB71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1288600</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1189900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1332700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1236600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1153800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-1057400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-1019000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-909400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-837500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-768300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-703600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-675400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-599200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-397600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-302200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-267700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-233500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-203000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-175200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-156200</v>
       </c>
-      <c r="W72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5413,8 +5587,11 @@
       <c r="AB72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5493,8 +5670,11 @@
       <c r="AB73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5573,8 +5753,11 @@
       <c r="AB74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5653,71 +5836,74 @@
       <c r="AB75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>913500</v>
+      </c>
+      <c r="E76" s="3">
         <v>981300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>778900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>811600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>761500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>733500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>714500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>800200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>829100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>826700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>853800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>548600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>422400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>245600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>200100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>230800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>261400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>-201100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>-172100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>-295500</v>
       </c>
-      <c r="W76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5733,8 +5919,11 @@
       <c r="AB76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5813,173 +6002,182 @@
       <c r="AB77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Z80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AA80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AB80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-98700</v>
+      </c>
+      <c r="E81" s="3">
         <v>142800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-96100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-82800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-96500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-38300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-109600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-72000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-69200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-64700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-28100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-76300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-201600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-95500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-34500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-34200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-31700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-31100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-22300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-52600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-16600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-216700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-70400</v>
       </c>
-      <c r="Z81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6008,8 +6206,9 @@
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
-    </row>
-    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC82" s="3"/>
+    </row>
+    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6017,79 +6216,82 @@
         <v>5400</v>
       </c>
       <c r="E83" s="3">
+        <v>5400</v>
+      </c>
+      <c r="F83" s="3">
         <v>5200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>4800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>4600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>3900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>3500</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>3400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>3300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>2600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>1800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>1700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>1400</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>1300</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>1200</v>
-      </c>
-      <c r="R83" s="3">
-        <v>1100</v>
       </c>
       <c r="S83" s="3">
         <v>1100</v>
       </c>
       <c r="T83" s="3">
+        <v>1100</v>
+      </c>
+      <c r="U83" s="3">
         <v>1000</v>
-      </c>
-      <c r="U83" s="3">
-        <v>900</v>
       </c>
       <c r="V83" s="3">
         <v>900</v>
       </c>
       <c r="W83" s="3">
+        <v>900</v>
+      </c>
+      <c r="X83" s="3">
         <v>700</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>500</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>100</v>
       </c>
-      <c r="Z83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA83" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6168,8 +6370,11 @@
       <c r="AB84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6248,8 +6453,11 @@
       <c r="AB85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6328,8 +6536,11 @@
       <c r="AB86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6408,8 +6619,11 @@
       <c r="AB87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6488,88 +6702,94 @@
       <c r="AB88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-99700</v>
+      </c>
+      <c r="E89" s="3">
         <v>135100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-89800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-84700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-109800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-69200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-74500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-52300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>218500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>3000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-32500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-38600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-24300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-21200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-22800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-27400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-17800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-17000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>16900</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-25900</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>4200</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-9400</v>
       </c>
-      <c r="Z89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6598,88 +6818,92 @@
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
-    </row>
-    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC90" s="3"/>
+    </row>
+    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-3600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-7900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-16200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-6000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-8300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-11800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-21600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-7300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-13400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-5800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-16200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-11500</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-8100</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-2800</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-2400</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-3000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-2200</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-1400</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-6600</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-2400</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-11200</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-700</v>
       </c>
-      <c r="Z91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA91" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6758,8 +6982,11 @@
       <c r="AB92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6838,88 +7065,94 @@
       <c r="AB93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-53500</v>
+      </c>
+      <c r="E94" s="3">
         <v>98100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-10200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-41500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>25500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>113400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-36200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-537300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-77500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>76100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-13100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-279600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-81400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>35200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>22900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-76800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>16600</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-83200</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>2400</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-2400</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>22000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-2200</v>
       </c>
-      <c r="Z94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6948,8 +7181,9 @@
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
-    </row>
-    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC95" s="3"/>
+    </row>
+    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7028,8 +7262,11 @@
       <c r="AB96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7108,8 +7345,11 @@
       <c r="AB97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7188,8 +7428,11 @@
       <c r="AB98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7268,88 +7511,94 @@
       <c r="AB99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E100" s="3">
         <v>33700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>36800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>107500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>98400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>32000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>1600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>22300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>55700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>21500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>320900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>160400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>253300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>130000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>193000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>700</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>2700</v>
       </c>
-      <c r="V100" s="3">
-        <v>0</v>
-      </c>
       <c r="W100" s="3">
+        <v>0</v>
+      </c>
+      <c r="X100" s="3">
         <v>37900</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>120100</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>9900</v>
       </c>
-      <c r="Z100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7428,84 +7677,90 @@
       <c r="AB101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-150300</v>
+      </c>
+      <c r="E102" s="3">
         <v>266900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-63200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-18600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>14100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>76300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-109100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-31200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-263200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-54100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>400000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>114800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-64900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>24300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>14100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>88800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-106500</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>9700</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>105900</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-500</v>
       </c>
-      <c r="Z102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BEAM_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BEAM_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="92">
   <si>
     <t>BEAM</t>
   </si>
@@ -656,166 +656,170 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AC102"/>
+  <dimension ref="A5:AD102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="29" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="30" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
-      <c r="AA7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AB7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AC7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>11800</v>
+      </c>
+      <c r="E8" s="3">
         <v>7400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>316200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>17200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>20100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>24200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>20000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>15800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>16700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>8400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>51100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>800</v>
       </c>
-      <c r="O8" s="3">
-        <v>0</v>
-      </c>
       <c r="P8" s="3">
         <v>0</v>
       </c>
@@ -858,8 +862,11 @@
       <c r="AC8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -941,8 +948,11 @@
       <c r="AC9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1024,8 +1034,11 @@
       <c r="AC10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1055,91 +1068,95 @@
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
-    </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD11" s="3"/>
+    </row>
+    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>87000</v>
+      </c>
+      <c r="E12" s="3">
         <v>84800</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>140100</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>100100</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>97600</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>99600</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>86300</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>85300</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>74600</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>65400</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>96800</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>54600</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>45600</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>190100</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>32500</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>29800</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>19400</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>21500</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>20200</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>12500</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>34500</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>9200</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>29600</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>9900</v>
       </c>
-      <c r="AA12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1221,8 +1238,11 @@
       <c r="AC13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1304,8 +1324,11 @@
       <c r="AC14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1387,8 +1410,11 @@
       <c r="AC15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1415,174 +1441,181 @@
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
-    </row>
-    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD16" s="3"/>
+    </row>
+    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>116700</v>
+      </c>
+      <c r="E17" s="3">
         <v>111500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>183300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>125500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>122300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>123100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>109000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>107100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>98600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>84700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>114600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>70400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>59000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>200400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>40800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>37300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>26300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>28400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>26400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>18000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>48400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>13100</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>39800</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>12700</v>
       </c>
-      <c r="AA17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-104900</v>
+      </c>
+      <c r="E18" s="3">
         <v>-104100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>132900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-108300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-102200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-98900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-89000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-91300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-81900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-76300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-63500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-69600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-59000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-200400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-40800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-37300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-26300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-28400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-26400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-18000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-48400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-13100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-39800</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-12700</v>
       </c>
-      <c r="AA18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1612,174 +1645,181 @@
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
-    </row>
-    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD19" s="3"/>
+    </row>
+    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>13900</v>
+      </c>
+      <c r="E20" s="3">
         <v>5500</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>11300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>12200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>19400</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>2500</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>51700</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>9600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>10000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>7000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-1300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>41500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-17300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-1200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-54700</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>2900</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-7900</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-2100</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-1400</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-900</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>30600</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-500</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>14600</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-58500</v>
       </c>
-      <c r="AA20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-85400</v>
+      </c>
+      <c r="E21" s="3">
         <v>-93200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>149500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-90900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-78000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-91800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-33400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-78200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-68500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-65900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-62100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-26400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-74600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-200200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-94200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-33200</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-33100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-29400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-26700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-19600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-15400</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-12900</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-24000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-71100</v>
       </c>
-      <c r="AA21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1816,8 +1856,8 @@
       <c r="N22" s="3">
         <v>0</v>
       </c>
-      <c r="O22" s="3" t="s">
-        <v>3</v>
+      <c r="O22" s="3">
+        <v>0</v>
       </c>
       <c r="P22" s="3" t="s">
         <v>3</v>
@@ -1834,14 +1874,14 @@
       <c r="T22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U22" s="3">
-        <v>100</v>
+      <c r="U22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V22" s="3">
         <v>100</v>
       </c>
-      <c r="W22" s="3" t="s">
-        <v>3</v>
+      <c r="W22" s="3">
+        <v>100</v>
       </c>
       <c r="X22" s="3" t="s">
         <v>3</v>
@@ -1861,118 +1901,124 @@
       <c r="AC22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-91000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-98700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>144200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-96100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-82800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-96500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-37300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-81700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-72000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-69200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-64700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-28100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-76300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-201600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-95500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-34500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-34200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-30500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-27900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-19000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-17900</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-13600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-25200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-71200</v>
       </c>
-      <c r="AA23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E24" s="3">
+      <c r="D24" s="3">
+        <v>0</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F24" s="3">
         <v>1400</v>
       </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>3</v>
+      <c r="G24" s="3">
+        <v>0</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I24" s="3">
+      <c r="I24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J24" s="3">
         <v>1000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>2400</v>
       </c>
-      <c r="K24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L24" s="3" t="s">
         <v>3</v>
       </c>
@@ -2006,18 +2052,18 @@
       <c r="V24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W24" s="3">
+      <c r="W24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X24" s="3">
         <v>-31500</v>
       </c>
-      <c r="X24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y24" s="3">
+      <c r="Y24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z24" s="3">
         <v>-96300</v>
       </c>
-      <c r="Z24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA24" s="3" t="s">
         <v>3</v>
       </c>
@@ -2027,8 +2073,11 @@
       <c r="AC24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2110,174 +2159,183 @@
       <c r="AC25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-91100</v>
+      </c>
+      <c r="E26" s="3">
         <v>-98700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>142800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-96100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-82800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-96500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-38300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-84100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-72000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-69200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-64700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-28100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-76300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-201600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-95500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-34500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-34200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-30500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-27900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-19000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-17900</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-13600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-23800</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-71200</v>
       </c>
-      <c r="AA26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-91100</v>
+      </c>
+      <c r="E27" s="3">
         <v>-98700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>142800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-96100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-82800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-96500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-38300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-109600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-72000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-69200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-64700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-28100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-76300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-201600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-95500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-34500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-34200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-31700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-31100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-22300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-52600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-16600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-216700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-70400</v>
       </c>
-      <c r="AA27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2359,8 +2417,11 @@
       <c r="AC28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2442,8 +2503,11 @@
       <c r="AC29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2525,8 +2589,11 @@
       <c r="AC30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2608,174 +2675,183 @@
       <c r="AC31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-13900</v>
+      </c>
+      <c r="E32" s="3">
         <v>-5500</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-11300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-12200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-19400</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-2500</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-51700</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-9600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-10000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-7000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>1300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-41500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>17300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>1200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>54700</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-2900</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>7900</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>2100</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>1400</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>900</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-30600</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>500</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-14600</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>58500</v>
       </c>
-      <c r="AA32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-91100</v>
+      </c>
+      <c r="E33" s="3">
         <v>-98700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>142800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-96100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-82800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-96500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-38300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-109600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-72000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-69200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-64700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-28100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-76300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-201600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-95500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-34500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-34200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-31700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-31100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-22300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-52600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-16600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-216700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-70400</v>
       </c>
-      <c r="AA33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2857,179 +2933,188 @@
       <c r="AC34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-91100</v>
+      </c>
+      <c r="E35" s="3">
         <v>-98700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>142800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-96100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-82800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-96500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-38300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-109600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-72000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-69200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-64700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-28100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-76300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-201600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-95500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-34500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-34200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-31700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-31100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-22300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-52600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-16600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-216700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-70400</v>
       </c>
-      <c r="AA35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
-      <c r="AA38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AB38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AC38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3059,8 +3144,9 @@
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
-    </row>
-    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD39" s="3"/>
+    </row>
+    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3090,74 +3176,75 @@
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
-    </row>
-    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD40" s="3"/>
+    </row>
+    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>292800</v>
+      </c>
+      <c r="E41" s="3">
         <v>287800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>435900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>169000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>225500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>249800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>232800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>156500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>265600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>296800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>560000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>612000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>212000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>97200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>162200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>137900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>125300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>126100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>37200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>37800</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>37900</v>
       </c>
-      <c r="X41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3173,74 +3260,77 @@
       <c r="AC41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>715400</v>
+      </c>
+      <c r="E42" s="3">
         <v>806700</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>754000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>846400</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>847500</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>809700</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>845400</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>938000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>900500</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>925800</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>405700</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>321400</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>403300</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>406200</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>137500</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>64300</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>102600</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>127400</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>54600</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>73100</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>88900</v>
       </c>
-      <c r="X42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3256,8 +3346,11 @@
       <c r="AC42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3289,17 +3382,17 @@
         <v>0</v>
       </c>
       <c r="M43" s="3">
+        <v>0</v>
+      </c>
+      <c r="N43" s="3">
         <v>300000</v>
       </c>
-      <c r="N43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O43" s="3">
+      <c r="O43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P43" s="3">
         <v>50000</v>
       </c>
-      <c r="P43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3315,8 +3408,8 @@
       <c r="U43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V43" s="3">
-        <v>0</v>
+      <c r="V43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W43" s="3">
         <v>0</v>
@@ -3339,8 +3432,11 @@
       <c r="AC43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3422,74 +3518,77 @@
       <c r="AC44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>21300</v>
+      </c>
+      <c r="E45" s="3">
         <v>27200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>21200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>24100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>21800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>23600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>14800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>14400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>13800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>16900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>7400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>8000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>12700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>11100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>8700</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>6500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>6900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>6200</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>2700</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>3900</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>2600</v>
       </c>
-      <c r="X45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3505,74 +3604,77 @@
       <c r="AC45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1029400</v>
+      </c>
+      <c r="E46" s="3">
         <v>1121700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1211000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1039500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1094800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1083000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1092900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1108900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1179900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1239500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1273000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>941400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>678000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>514600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>308300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>208700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>234800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>259600</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>94500</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>114800</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>129400</v>
       </c>
-      <c r="X46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3588,8 +3690,11 @@
       <c r="AC46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3620,18 +3725,18 @@
       <c r="L47" s="3">
         <v>0</v>
       </c>
-      <c r="M47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N47" s="3">
+      <c r="M47" s="3">
+        <v>0</v>
+      </c>
+      <c r="N47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O47" s="3">
         <v>24500</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>29400</v>
       </c>
-      <c r="P47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3647,8 +3752,8 @@
       <c r="U47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V47" s="3">
-        <v>0</v>
+      <c r="V47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W47" s="3">
         <v>0</v>
@@ -3671,74 +3776,77 @@
       <c r="AC47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>224300</v>
+      </c>
+      <c r="E48" s="3">
         <v>229900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>237800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>239700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>242300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>238000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>234100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>226700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>223500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>199800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>187000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>174700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>169700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>158800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>125400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>51200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>48600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>46900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>43200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>38000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>36800</v>
       </c>
-      <c r="X48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3754,8 +3862,11 @@
       <c r="AC48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3837,8 +3948,11 @@
       <c r="AC49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3920,8 +4034,11 @@
       <c r="AC50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4003,74 +4120,77 @@
       <c r="AC51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>7500</v>
+      </c>
+      <c r="E52" s="3">
         <v>8100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>10900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>11300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>16800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>11300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>14700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>14600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>15000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>14100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>14500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>15900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>16000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>19900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>18000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>18400</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>16600</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>16100</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>18300</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>17800</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>14400</v>
       </c>
-      <c r="X52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4086,8 +4206,11 @@
       <c r="AC52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4169,74 +4292,77 @@
       <c r="AC53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1261300</v>
+      </c>
+      <c r="E54" s="3">
         <v>1359800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1459700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1290500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1353900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1332400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1341700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1350300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1418400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1453400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1474500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1156600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>893100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>693200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>451700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>278300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>300000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>322600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>156100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>170600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>180500</v>
       </c>
-      <c r="X54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4252,8 +4378,11 @@
       <c r="AC54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4283,8 +4412,9 @@
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
-    </row>
-    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD55" s="3"/>
+    </row>
+    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4314,74 +4444,75 @@
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
-    </row>
-    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD56" s="3"/>
+    </row>
+    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E57" s="3">
         <v>2800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>3200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>6900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>14100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>9000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>7000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>7100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>6300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>7500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>7300</v>
-      </c>
-      <c r="O57" s="3">
-        <v>8000</v>
       </c>
       <c r="P57" s="3">
         <v>8000</v>
       </c>
       <c r="Q57" s="3">
+        <v>8000</v>
+      </c>
+      <c r="R57" s="3">
         <v>6300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>6600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>6200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>6100</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>7800</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>3900</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>4000</v>
       </c>
-      <c r="X57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4397,55 +4528,58 @@
       <c r="AC57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E58" s="3">
+      <c r="E58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F58" s="3">
         <v>500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>2200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>2400</v>
-      </c>
-      <c r="L58" s="3">
-        <v>2300</v>
       </c>
       <c r="M58" s="3">
         <v>2300</v>
       </c>
       <c r="N58" s="3">
-        <v>2200</v>
+        <v>2300</v>
       </c>
       <c r="O58" s="3">
         <v>2200</v>
       </c>
       <c r="P58" s="3">
-        <v>2100</v>
+        <v>2200</v>
       </c>
       <c r="Q58" s="3">
         <v>2100</v>
       </c>
       <c r="R58" s="3">
-        <v>1700</v>
+        <v>2100</v>
       </c>
       <c r="S58" s="3">
         <v>1700</v>
@@ -4454,17 +4588,17 @@
         <v>1700</v>
       </c>
       <c r="U58" s="3">
+        <v>1700</v>
+      </c>
+      <c r="V58" s="3">
         <v>1300</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>800</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>7300</v>
       </c>
-      <c r="X58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y58" s="3" t="s">
         <v>3</v>
       </c>
@@ -4480,74 +4614,77 @@
       <c r="AC58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>172900</v>
+      </c>
+      <c r="E59" s="3">
         <v>184400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>203500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>216100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>201700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>204400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>212700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>229600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>202800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>210200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>203700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>91900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>118500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>92000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>93900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>39100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>31100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>23700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>20000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>15300</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>56200</v>
       </c>
-      <c r="X59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4563,74 +4700,77 @@
       <c r="AC59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>177300</v>
+      </c>
+      <c r="E60" s="3">
         <v>187200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>205600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>220400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>209500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>219900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>223600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>238900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>212300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>218800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>213400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>101400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>128700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>102100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>102300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>47500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>39000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>31400</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>29100</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>19900</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>52200</v>
       </c>
-      <c r="X60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4646,8 +4786,11 @@
       <c r="AC60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4658,62 +4801,62 @@
         <v>0</v>
       </c>
       <c r="F61" s="3">
+        <v>0</v>
+      </c>
+      <c r="G61" s="3">
         <v>300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>3000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>3600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>4200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>4700</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>5300</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>4400</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>4900</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>5300</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>4400</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>2800</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>300</v>
       </c>
-      <c r="X61" s="3">
-        <v>0</v>
-      </c>
       <c r="Y61" s="3">
         <v>0</v>
       </c>
@@ -4729,71 +4872,74 @@
       <c r="AC61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>229800</v>
+      </c>
+      <c r="E62" s="3">
         <v>259100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>272800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>290900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>331800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>349900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>383500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>395500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>404100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>403100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>431300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>197800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>211600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>164000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>98500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>26300</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>25300</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>24500</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>21600</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>21100</v>
       </c>
-      <c r="W62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4812,8 +4958,11 @@
       <c r="AC62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4895,8 +5044,11 @@
       <c r="AC63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4978,8 +5130,11 @@
       <c r="AC64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5061,74 +5216,77 @@
       <c r="AC65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>407200</v>
+      </c>
+      <c r="E66" s="3">
         <v>446300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>478400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>511600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>542200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>570800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>608200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>635800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>618200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>624300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>647700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>302700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>344500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>270800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>206100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>78200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>69200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>61200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>55200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>43800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>36900</v>
       </c>
-      <c r="X66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5144,8 +5302,11 @@
       <c r="AC66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5175,8 +5336,9 @@
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
-    </row>
-    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD67" s="3"/>
+    </row>
+    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5258,8 +5420,11 @@
       <c r="AC68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5341,8 +5506,11 @@
       <c r="AC69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5398,17 +5566,17 @@
         <v>0</v>
       </c>
       <c r="U70" s="3">
+        <v>0</v>
+      </c>
+      <c r="V70" s="3">
         <v>302000</v>
       </c>
-      <c r="V70" s="3">
+      <c r="W70" s="3">
         <v>298800</v>
       </c>
-      <c r="W70" s="3">
+      <c r="X70" s="3">
         <v>439200</v>
       </c>
-      <c r="X70" s="3">
-        <v>0</v>
-      </c>
       <c r="Y70" s="3">
         <v>0</v>
       </c>
@@ -5424,8 +5592,11 @@
       <c r="AC70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5507,74 +5678,77 @@
       <c r="AC71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1379600</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1288600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1189900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1332700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1236600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-1153800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-1057400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-1019000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-909400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-837500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-768300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-703600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-675400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-599200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-397600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-302200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-267700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-233500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-203000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-175200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-156200</v>
       </c>
-      <c r="X72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5590,8 +5764,11 @@
       <c r="AC72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5673,8 +5850,11 @@
       <c r="AC73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5756,8 +5936,11 @@
       <c r="AC74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5839,74 +6022,77 @@
       <c r="AC75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>854100</v>
+      </c>
+      <c r="E76" s="3">
         <v>913500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>981300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>778900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>811600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>761500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>733500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>714500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>800200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>829100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>826700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>853800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>548600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>422400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>245600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>200100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>230800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>261400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>-201100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>-172100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>-295500</v>
       </c>
-      <c r="X76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5922,8 +6108,11 @@
       <c r="AC76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6005,179 +6194,188 @@
       <c r="AC77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
-      <c r="AA80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AB80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AC80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-91100</v>
+      </c>
+      <c r="E81" s="3">
         <v>-98700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>142800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-96100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-82800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-96500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-38300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-109600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-72000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-69200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-64700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-28100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-76300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-201600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-95500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-34500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-34200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-31700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-31100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-22300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-52600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-16600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-216700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-70400</v>
       </c>
-      <c r="AA81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6207,91 +6405,95 @@
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
-    </row>
-    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD82" s="3"/>
+    </row>
+    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>5400</v>
+        <v>5600</v>
       </c>
       <c r="E83" s="3">
         <v>5400</v>
       </c>
       <c r="F83" s="3">
+        <v>5400</v>
+      </c>
+      <c r="G83" s="3">
         <v>5200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>4800</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>4600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>3900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>3500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>3400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>3300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>2600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>1800</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>1700</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>1400</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>1300</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>1200</v>
-      </c>
-      <c r="S83" s="3">
-        <v>1100</v>
       </c>
       <c r="T83" s="3">
         <v>1100</v>
       </c>
       <c r="U83" s="3">
+        <v>1100</v>
+      </c>
+      <c r="V83" s="3">
         <v>1000</v>
-      </c>
-      <c r="V83" s="3">
-        <v>900</v>
       </c>
       <c r="W83" s="3">
         <v>900</v>
       </c>
       <c r="X83" s="3">
+        <v>900</v>
+      </c>
+      <c r="Y83" s="3">
         <v>700</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>500</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>100</v>
       </c>
-      <c r="AA83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB83" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6373,8 +6575,11 @@
       <c r="AC84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6456,8 +6661,11 @@
       <c r="AC85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6539,8 +6747,11 @@
       <c r="AC86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6622,8 +6833,11 @@
       <c r="AC87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6705,91 +6919,97 @@
       <c r="AC88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-83000</v>
+      </c>
+      <c r="E89" s="3">
         <v>-99700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>135100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-89800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-84700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-109800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-69200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-74500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-52300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>218500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>3000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-32500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-38600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-24300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-21200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-22800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-27400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-17800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-17000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>16900</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-25900</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>4200</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-9400</v>
       </c>
-      <c r="AA89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6819,91 +7039,95 @@
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
-    </row>
-    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD90" s="3"/>
+    </row>
+    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-2400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-3600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-7900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-16200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-6000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-8300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-11800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-21600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-7300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-13400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-5800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-16200</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-11500</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-8100</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-2800</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-2400</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-3000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-2200</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-1400</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-6600</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-2400</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-11200</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-700</v>
       </c>
-      <c r="AA91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB91" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6985,8 +7209,11 @@
       <c r="AC92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7068,91 +7295,97 @@
       <c r="AC93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>87500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-53500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>98100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-10200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-41500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>25500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>113400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-36200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-537300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-77500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>76100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-13100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-279600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-81400</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>35200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>22900</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-76800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>16600</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-83200</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>2400</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-2400</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>22000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-2200</v>
       </c>
-      <c r="AA94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7182,8 +7415,9 @@
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
-    </row>
-    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD95" s="3"/>
+    </row>
+    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7265,8 +7499,11 @@
       <c r="AC96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7348,8 +7585,11 @@
       <c r="AC97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7431,8 +7671,11 @@
       <c r="AC98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7514,91 +7757,97 @@
       <c r="AC99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>100</v>
+      </c>
+      <c r="E100" s="3">
         <v>2900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>33700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>36800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>107500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>98400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>32000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>1600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>22300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>55700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>21500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>320900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>160400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>253300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>130000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>193000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>700</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>2700</v>
       </c>
-      <c r="W100" s="3">
-        <v>0</v>
-      </c>
       <c r="X100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y100" s="3">
         <v>37900</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>120100</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>9900</v>
       </c>
-      <c r="AA100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7680,87 +7929,93 @@
       <c r="AC101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>4600</v>
+      </c>
+      <c r="E102" s="3">
         <v>-150300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>266900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-63200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-18600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>14100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>76300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-109100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-31200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-263200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-54100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>400000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>114800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-64900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>24300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>14100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>88800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-106500</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>9700</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>105900</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-500</v>
       </c>
-      <c r="AA102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BEAM_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BEAM_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="92">
   <si>
     <t>BEAM</t>
   </si>
@@ -656,173 +656,177 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AD102"/>
+  <dimension ref="A5:AE102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="30" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="31" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43373</v>
       </c>
-      <c r="AB7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AC7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AD7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>14300</v>
+      </c>
+      <c r="E8" s="3">
         <v>11800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>7400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>316200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>17200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>20100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>24200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>20000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>15800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>16700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>8400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>51100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>800</v>
       </c>
-      <c r="P8" s="3">
-        <v>0</v>
-      </c>
       <c r="Q8" s="3">
         <v>0</v>
       </c>
@@ -865,31 +869,34 @@
       <c r="AD8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>3</v>
+      <c r="D9" s="3">
+        <v>94300</v>
+      </c>
+      <c r="E9" s="3">
+        <v>87000</v>
+      </c>
+      <c r="F9" s="3">
+        <v>84800</v>
+      </c>
+      <c r="G9" s="3">
+        <v>140100</v>
+      </c>
+      <c r="H9" s="3">
+        <v>100100</v>
+      </c>
+      <c r="I9" s="3">
+        <v>97600</v>
+      </c>
+      <c r="J9" s="3">
+        <v>99600</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>3</v>
@@ -951,31 +958,34 @@
       <c r="AD9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>3</v>
+      <c r="D10" s="3">
+        <v>-80000</v>
+      </c>
+      <c r="E10" s="3">
+        <v>-75300</v>
+      </c>
+      <c r="F10" s="3">
+        <v>-77400</v>
+      </c>
+      <c r="G10" s="3">
+        <v>176100</v>
+      </c>
+      <c r="H10" s="3">
+        <v>-82900</v>
+      </c>
+      <c r="I10" s="3">
+        <v>-77500</v>
+      </c>
+      <c r="J10" s="3">
+        <v>-75400</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>3</v>
@@ -1037,8 +1047,11 @@
       <c r="AD10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1069,94 +1082,98 @@
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
-    </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE11" s="3"/>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>94300</v>
+      </c>
+      <c r="E12" s="3">
         <v>87000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>84800</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>140100</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>100100</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>97600</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>99600</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>86300</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>85300</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>74600</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>65400</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>96800</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>54600</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>45600</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>190100</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>32500</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>29800</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>19400</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>21500</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>20200</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>12500</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>34500</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>9200</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>29600</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>9900</v>
       </c>
-      <c r="AB12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1241,31 +1258,34 @@
       <c r="AD13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
+        <v>2100</v>
       </c>
       <c r="E14" s="3">
-        <v>0</v>
+        <v>5800</v>
       </c>
       <c r="F14" s="3">
-        <v>0</v>
+        <v>3500</v>
       </c>
       <c r="G14" s="3">
-        <v>0</v>
+        <v>-1100</v>
       </c>
       <c r="H14" s="3">
-        <v>0</v>
+        <v>5200</v>
       </c>
       <c r="I14" s="3">
-        <v>0</v>
+        <v>-8300</v>
       </c>
       <c r="J14" s="3">
-        <v>0</v>
+        <v>13100</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1327,31 +1347,34 @@
       <c r="AD14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>5500</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>5600</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>5400</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>5400</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>5200</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>4800</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>4600</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1413,8 +1436,11 @@
       <c r="AD15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1442,180 +1468,187 @@
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
-    </row>
-    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE16" s="3"/>
+    </row>
+    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>120800</v>
+      </c>
+      <c r="E17" s="3">
         <v>116700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>111500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>183300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>125500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>122300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>123100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>109000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>107100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>98600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>84700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>114600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>70400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>59000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>200400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>40800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>37300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>26300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>28400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>26400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>18000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>48400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>13100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>39800</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>12700</v>
       </c>
-      <c r="AB17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-106500</v>
+      </c>
+      <c r="E18" s="3">
         <v>-104900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-104100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>132900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-108300</v>
       </c>
-      <c r="H18" s="3">
-        <v>-102200</v>
-      </c>
       <c r="I18" s="3">
+        <v>-102100</v>
+      </c>
+      <c r="J18" s="3">
         <v>-98900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-89000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-91300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-81900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-76300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-63500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-69600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-59000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-200400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-40800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-37300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-26300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-28400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-26400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-18000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-48400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-13100</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-39800</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-12700</v>
       </c>
-      <c r="AB18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1646,203 +1679,210 @@
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
-    </row>
-    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE19" s="3"/>
+    </row>
+    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>13900</v>
+        <v>200</v>
       </c>
       <c r="E20" s="3">
-        <v>5500</v>
+        <v>-5500</v>
       </c>
       <c r="F20" s="3">
-        <v>11300</v>
+        <v>2900</v>
       </c>
       <c r="G20" s="3">
-        <v>12200</v>
+        <v>1900</v>
       </c>
       <c r="H20" s="3">
-        <v>19400</v>
+        <v>-4700</v>
       </c>
       <c r="I20" s="3">
-        <v>2500</v>
+        <v>900</v>
       </c>
       <c r="J20" s="3">
+        <v>-5600</v>
+      </c>
+      <c r="K20" s="3">
         <v>51700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>9600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>10000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>7000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-1300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>41500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-17300</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-1200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-54700</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>2900</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-7900</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-2100</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-1400</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-900</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>30600</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-500</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>14600</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-58500</v>
       </c>
-      <c r="AB20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-85400</v>
+        <v>-101200</v>
       </c>
       <c r="E21" s="3">
-        <v>-93200</v>
+        <v>-93800</v>
       </c>
       <c r="F21" s="3">
-        <v>149500</v>
+        <v>-101600</v>
       </c>
       <c r="G21" s="3">
-        <v>-90900</v>
+        <v>136300</v>
       </c>
       <c r="H21" s="3">
-        <v>-78000</v>
+        <v>-98400</v>
       </c>
       <c r="I21" s="3">
-        <v>-91800</v>
+        <v>-98200</v>
       </c>
       <c r="J21" s="3">
+        <v>-88700</v>
+      </c>
+      <c r="K21" s="3">
         <v>-33400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-78200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-68500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-65900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-62100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-26400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-74600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-200200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-94200</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-33200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-33100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-29400</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-26700</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-19600</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-15400</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-12900</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-24000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-71100</v>
       </c>
-      <c r="AB21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1859,8 +1899,8 @@
       <c r="O22" s="3">
         <v>0</v>
       </c>
-      <c r="P22" s="3" t="s">
-        <v>3</v>
+      <c r="P22" s="3">
+        <v>0</v>
       </c>
       <c r="Q22" s="3" t="s">
         <v>3</v>
@@ -1877,14 +1917,14 @@
       <c r="U22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V22" s="3">
-        <v>100</v>
+      <c r="V22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W22" s="3">
         <v>100</v>
       </c>
-      <c r="X22" s="3" t="s">
-        <v>3</v>
+      <c r="X22" s="3">
+        <v>100</v>
       </c>
       <c r="Y22" s="3" t="s">
         <v>3</v>
@@ -1904,124 +1944,130 @@
       <c r="AD22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-96700</v>
+      </c>
+      <c r="E23" s="3">
         <v>-91000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-98700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>144200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-96100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-82800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-96500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-37300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-81700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-72000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-69200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-64700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-28100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-76300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-201600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-95500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-34500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-34200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-30500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-27900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-19000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-17900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-13600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-25200</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-71200</v>
       </c>
-      <c r="AB23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>0</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F24" s="3">
+      <c r="D24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E24" s="3">
+        <v>0</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G24" s="3">
         <v>1400</v>
       </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
       <c r="H24" s="3" t="s">
         <v>3</v>
       </c>
       <c r="I24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J24" s="3">
+      <c r="J24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K24" s="3">
         <v>1000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>2400</v>
       </c>
-      <c r="L24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M24" s="3" t="s">
         <v>3</v>
       </c>
@@ -2055,18 +2101,18 @@
       <c r="W24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X24" s="3">
+      <c r="X24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y24" s="3">
         <v>-31500</v>
       </c>
-      <c r="Y24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z24" s="3">
+      <c r="Z24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA24" s="3">
         <v>-96300</v>
       </c>
-      <c r="AA24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB24" s="3" t="s">
         <v>3</v>
       </c>
@@ -2076,8 +2122,11 @@
       <c r="AD24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2162,180 +2211,189 @@
       <c r="AD25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-96700</v>
+      </c>
+      <c r="E26" s="3">
         <v>-91100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-98700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>142800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-96100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-82800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-96500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-38300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-84100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-72000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-69200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-64700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-28100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-76300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-201600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-95500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-34500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-34200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-30500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-27900</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-19000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-17900</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-13600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-23800</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-71200</v>
       </c>
-      <c r="AB26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-96700</v>
+      </c>
+      <c r="E27" s="3">
         <v>-91100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-98700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>142800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-96100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-82800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-96500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-38300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-109600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-72000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-69200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-64700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-28100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-76300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-201600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-95500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-34500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-34200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-31700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-31100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-22300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-52600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-16600</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-216700</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-70400</v>
       </c>
-      <c r="AB27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2420,8 +2478,11 @@
       <c r="AD28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2506,8 +2567,11 @@
       <c r="AD29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2592,8 +2656,11 @@
       <c r="AD30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2678,180 +2745,189 @@
       <c r="AD31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-13900</v>
+        <v>-200</v>
       </c>
       <c r="E32" s="3">
-        <v>-5500</v>
+        <v>5500</v>
       </c>
       <c r="F32" s="3">
-        <v>-11300</v>
+        <v>-2900</v>
       </c>
       <c r="G32" s="3">
-        <v>-12200</v>
+        <v>-1900</v>
       </c>
       <c r="H32" s="3">
-        <v>-19400</v>
+        <v>4700</v>
       </c>
       <c r="I32" s="3">
-        <v>-2500</v>
+        <v>-900</v>
       </c>
       <c r="J32" s="3">
+        <v>5600</v>
+      </c>
+      <c r="K32" s="3">
         <v>-51700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-9600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-10000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-7000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>1300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-41500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>17300</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>1200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>54700</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-2900</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>7900</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>2100</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>1400</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>900</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-30600</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>500</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-14600</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>58500</v>
       </c>
-      <c r="AB32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-96700</v>
+      </c>
+      <c r="E33" s="3">
         <v>-91100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-98700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>142800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-96100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-82800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-96500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-38300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-109600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-72000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-69200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-64700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-28100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-76300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-201600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-95500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-34500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-34200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-31700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-31100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-22300</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-52600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-16600</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-216700</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-70400</v>
       </c>
-      <c r="AB33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2936,185 +3012,194 @@
       <c r="AD34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-96700</v>
+      </c>
+      <c r="E35" s="3">
         <v>-91100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-98700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>142800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-96100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-82800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-96500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-38300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-109600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-72000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-69200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-64700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-28100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-76300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-201600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-95500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-34500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-34200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-31700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-31100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-22300</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-52600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-16600</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-216700</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-70400</v>
       </c>
-      <c r="AB35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43373</v>
       </c>
-      <c r="AB38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AC38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AD38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3145,8 +3230,9 @@
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
-    </row>
-    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE39" s="3"/>
+    </row>
+    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3177,77 +3263,78 @@
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
-    </row>
-    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE40" s="3"/>
+    </row>
+    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>230200</v>
+      </c>
+      <c r="E41" s="3">
         <v>292800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>287800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>435900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>169000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>225500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>249800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>232800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>156500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>265600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>296800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>560000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>612000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>212000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>97200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>162200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>137900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>125300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>126100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>37200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>37800</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>37900</v>
       </c>
-      <c r="Y41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3263,77 +3350,80 @@
       <c r="AD41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>695600</v>
+      </c>
+      <c r="E42" s="3">
         <v>715400</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>806700</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>754000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>846400</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>847500</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>809700</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>845400</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>938000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>900500</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>925800</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>405700</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>321400</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>403300</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>406200</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>137500</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>64300</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>102600</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>127400</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>54600</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>73100</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>88900</v>
       </c>
-      <c r="Y42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3349,31 +3439,34 @@
       <c r="AD42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
-        <v>0</v>
-      </c>
-      <c r="E43" s="3">
-        <v>0</v>
-      </c>
-      <c r="F43" s="3">
-        <v>0</v>
-      </c>
-      <c r="G43" s="3">
-        <v>0</v>
-      </c>
-      <c r="H43" s="3">
-        <v>0</v>
-      </c>
-      <c r="I43" s="3">
-        <v>0</v>
-      </c>
-      <c r="J43" s="3">
-        <v>0</v>
+      <c r="D43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K43" s="3">
         <v>0</v>
@@ -3385,17 +3478,17 @@
         <v>0</v>
       </c>
       <c r="N43" s="3">
+        <v>0</v>
+      </c>
+      <c r="O43" s="3">
         <v>300000</v>
       </c>
-      <c r="O43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P43" s="3">
+      <c r="P43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q43" s="3">
         <v>50000</v>
       </c>
-      <c r="Q43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3411,8 +3504,8 @@
       <c r="V43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W43" s="3">
-        <v>0</v>
+      <c r="W43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X43" s="3">
         <v>0</v>
@@ -3435,31 +3528,34 @@
       <c r="AD43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -3521,77 +3617,80 @@
       <c r="AD44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>21300</v>
-      </c>
-      <c r="E45" s="3">
-        <v>27200</v>
-      </c>
-      <c r="F45" s="3">
-        <v>21200</v>
-      </c>
-      <c r="G45" s="3">
-        <v>24100</v>
-      </c>
-      <c r="H45" s="3">
-        <v>21800</v>
-      </c>
-      <c r="I45" s="3">
-        <v>23600</v>
-      </c>
-      <c r="J45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K45" s="3">
         <v>14800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>14400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>13800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>16900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>7400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>8000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>12700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>11100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>8700</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>6500</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>6900</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>6200</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>2700</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>3900</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>2600</v>
       </c>
-      <c r="Y45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3607,77 +3706,80 @@
       <c r="AD45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>945500</v>
+      </c>
+      <c r="E46" s="3">
         <v>1029400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1121700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1211000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1039500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1094800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1083000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1092900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1108900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1179900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1239500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1273000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>941400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>678000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>514600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>308300</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>208700</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>234800</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>259600</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>94500</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>114800</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>129400</v>
       </c>
-      <c r="Y46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3693,31 +3795,34 @@
       <c r="AD46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -3728,18 +3833,18 @@
       <c r="M47" s="3">
         <v>0</v>
       </c>
-      <c r="N47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O47" s="3">
+      <c r="N47" s="3">
+        <v>0</v>
+      </c>
+      <c r="O47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P47" s="3">
         <v>24500</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>29400</v>
       </c>
-      <c r="Q47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3755,8 +3860,8 @@
       <c r="V47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W47" s="3">
-        <v>0</v>
+      <c r="W47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X47" s="3">
         <v>0</v>
@@ -3779,77 +3884,80 @@
       <c r="AD47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>218200</v>
+      </c>
+      <c r="E48" s="3">
         <v>224300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>229900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>237800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>239700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>242300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>238000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>234100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>226700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>223500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>199800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>187000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>174700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>169700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>158800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>125400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>51200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>48600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>46900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>43200</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>38000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>36800</v>
       </c>
-      <c r="Y48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3865,8 +3973,11 @@
       <c r="AD48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3951,8 +4062,11 @@
       <c r="AD49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4037,8 +4151,11 @@
       <c r="AD50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4123,77 +4240,80 @@
       <c r="AD51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>7600</v>
+      </c>
+      <c r="E52" s="3">
         <v>7500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>8100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>10900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>11300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>16800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>11300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>14700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>14600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>15000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>14100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>14500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>15900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>16000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>19900</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>18000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>18400</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>16600</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>16100</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>18300</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>17800</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>14400</v>
       </c>
-      <c r="Y52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4209,8 +4329,11 @@
       <c r="AD52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4295,77 +4418,80 @@
       <c r="AD53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1171400</v>
+      </c>
+      <c r="E54" s="3">
         <v>1261300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1359800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1459700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1290500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1353900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1332400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1341700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1350300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1418400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1453400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1474500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1156600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>893100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>693200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>451700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>278300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>300000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>322600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>156100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>170600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>180500</v>
       </c>
-      <c r="Y54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4381,8 +4507,11 @@
       <c r="AD54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4413,8 +4542,9 @@
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
-    </row>
-    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE55" s="3"/>
+    </row>
+    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4445,77 +4575,78 @@
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
-    </row>
-    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE56" s="3"/>
+    </row>
+    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E57" s="3">
         <v>4400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>3200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>6900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>14100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>9000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>7000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>7100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>6300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>7500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>7300</v>
-      </c>
-      <c r="P57" s="3">
-        <v>8000</v>
       </c>
       <c r="Q57" s="3">
         <v>8000</v>
       </c>
       <c r="R57" s="3">
+        <v>8000</v>
+      </c>
+      <c r="S57" s="3">
         <v>6300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>6600</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>6200</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>6100</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>7800</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>3900</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>4000</v>
       </c>
-      <c r="Y57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4531,58 +4662,61 @@
       <c r="AD57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E58" s="3" t="s">
-        <v>3</v>
+      <c r="D58" s="3">
+        <v>12900</v>
+      </c>
+      <c r="E58" s="3">
+        <v>12600</v>
       </c>
       <c r="F58" s="3">
-        <v>500</v>
+        <v>12200</v>
       </c>
       <c r="G58" s="3">
-        <v>1100</v>
+        <v>13300</v>
       </c>
       <c r="H58" s="3">
-        <v>900</v>
+        <v>13000</v>
       </c>
       <c r="I58" s="3">
-        <v>1400</v>
+        <v>12400</v>
       </c>
       <c r="J58" s="3">
+        <v>12600</v>
+      </c>
+      <c r="K58" s="3">
         <v>1900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>2200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>2400</v>
-      </c>
-      <c r="M58" s="3">
-        <v>2300</v>
       </c>
       <c r="N58" s="3">
         <v>2300</v>
       </c>
       <c r="O58" s="3">
-        <v>2200</v>
+        <v>2300</v>
       </c>
       <c r="P58" s="3">
         <v>2200</v>
       </c>
       <c r="Q58" s="3">
-        <v>2100</v>
+        <v>2200</v>
       </c>
       <c r="R58" s="3">
         <v>2100</v>
       </c>
       <c r="S58" s="3">
-        <v>1700</v>
+        <v>2100</v>
       </c>
       <c r="T58" s="3">
         <v>1700</v>
@@ -4591,17 +4725,17 @@
         <v>1700</v>
       </c>
       <c r="V58" s="3">
+        <v>1700</v>
+      </c>
+      <c r="W58" s="3">
         <v>1300</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>800</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>7300</v>
       </c>
-      <c r="Y58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z58" s="3" t="s">
         <v>3</v>
       </c>
@@ -4617,77 +4751,80 @@
       <c r="AD58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>172900</v>
+        <v>124000</v>
       </c>
       <c r="E59" s="3">
-        <v>184400</v>
+        <v>140000</v>
       </c>
       <c r="F59" s="3">
-        <v>203500</v>
+        <v>157800</v>
       </c>
       <c r="G59" s="3">
-        <v>216100</v>
+        <v>155600</v>
       </c>
       <c r="H59" s="3">
-        <v>201700</v>
+        <v>171600</v>
       </c>
       <c r="I59" s="3">
-        <v>204400</v>
+        <v>163800</v>
       </c>
       <c r="J59" s="3">
+        <v>172800</v>
+      </c>
+      <c r="K59" s="3">
         <v>212700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>229600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>202800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>210200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>203700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>91900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>118500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>92000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>93900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>39100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>31100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>23700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>20000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>15300</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>56200</v>
       </c>
-      <c r="Y59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4703,77 +4840,80 @@
       <c r="AD59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>166200</v>
+      </c>
+      <c r="E60" s="3">
         <v>177300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>187200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>205600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>220400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>209500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>219900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>223600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>238900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>212300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>218800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>213400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>101400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>128700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>102100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>102300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>47500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>39000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>31400</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>29100</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>19900</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>52200</v>
       </c>
-      <c r="Y60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4789,77 +4929,80 @@
       <c r="AD60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>149100</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>152600</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>155900</v>
       </c>
       <c r="G61" s="3">
+        <v>159900</v>
+      </c>
+      <c r="H61" s="3">
+        <v>160900</v>
+      </c>
+      <c r="I61" s="3">
+        <v>164700</v>
+      </c>
+      <c r="J61" s="3">
+        <v>166300</v>
+      </c>
+      <c r="K61" s="3">
+        <v>1200</v>
+      </c>
+      <c r="L61" s="3">
+        <v>1400</v>
+      </c>
+      <c r="M61" s="3">
+        <v>1800</v>
+      </c>
+      <c r="N61" s="3">
+        <v>2400</v>
+      </c>
+      <c r="O61" s="3">
+        <v>3000</v>
+      </c>
+      <c r="P61" s="3">
+        <v>3600</v>
+      </c>
+      <c r="Q61" s="3">
+        <v>4200</v>
+      </c>
+      <c r="R61" s="3">
+        <v>4700</v>
+      </c>
+      <c r="S61" s="3">
+        <v>5300</v>
+      </c>
+      <c r="T61" s="3">
+        <v>4400</v>
+      </c>
+      <c r="U61" s="3">
+        <v>4900</v>
+      </c>
+      <c r="V61" s="3">
+        <v>5300</v>
+      </c>
+      <c r="W61" s="3">
+        <v>4400</v>
+      </c>
+      <c r="X61" s="3">
+        <v>2800</v>
+      </c>
+      <c r="Y61" s="3">
         <v>300</v>
       </c>
-      <c r="H61" s="3">
-        <v>900</v>
-      </c>
-      <c r="I61" s="3">
-        <v>1000</v>
-      </c>
-      <c r="J61" s="3">
-        <v>1200</v>
-      </c>
-      <c r="K61" s="3">
-        <v>1400</v>
-      </c>
-      <c r="L61" s="3">
-        <v>1800</v>
-      </c>
-      <c r="M61" s="3">
-        <v>2400</v>
-      </c>
-      <c r="N61" s="3">
-        <v>3000</v>
-      </c>
-      <c r="O61" s="3">
-        <v>3600</v>
-      </c>
-      <c r="P61" s="3">
-        <v>4200</v>
-      </c>
-      <c r="Q61" s="3">
-        <v>4700</v>
-      </c>
-      <c r="R61" s="3">
-        <v>5300</v>
-      </c>
-      <c r="S61" s="3">
-        <v>4400</v>
-      </c>
-      <c r="T61" s="3">
-        <v>4900</v>
-      </c>
-      <c r="U61" s="3">
-        <v>5300</v>
-      </c>
-      <c r="V61" s="3">
-        <v>4400</v>
-      </c>
-      <c r="W61" s="3">
-        <v>2800</v>
-      </c>
-      <c r="X61" s="3">
-        <v>300</v>
-      </c>
-      <c r="Y61" s="3">
-        <v>0</v>
-      </c>
       <c r="Z61" s="3">
         <v>0</v>
       </c>
@@ -4875,74 +5018,77 @@
       <c r="AD61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>229800</v>
+        <v>6900</v>
       </c>
       <c r="E62" s="3">
-        <v>259100</v>
+        <v>1800</v>
       </c>
       <c r="F62" s="3">
-        <v>272800</v>
+        <v>3600</v>
       </c>
       <c r="G62" s="3">
-        <v>290900</v>
+        <v>3000</v>
       </c>
       <c r="H62" s="3">
-        <v>331800</v>
+        <v>5600</v>
       </c>
       <c r="I62" s="3">
-        <v>349900</v>
+        <v>11800</v>
       </c>
       <c r="J62" s="3">
+        <v>12900</v>
+      </c>
+      <c r="K62" s="3">
         <v>383500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>395500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>404100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>403100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>431300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>197800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>211600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>164000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>98500</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>26300</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>25300</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>24500</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>21600</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>21100</v>
       </c>
-      <c r="X62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4961,8 +5107,11 @@
       <c r="AD62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5047,8 +5196,11 @@
       <c r="AD63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5133,8 +5285,11 @@
       <c r="AD64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5219,77 +5374,80 @@
       <c r="AD65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>380100</v>
+      </c>
+      <c r="E66" s="3">
         <v>407200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>446300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>478400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>511600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>542200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>570800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>608200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>635800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>618200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>624300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>647700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>302700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>344500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>270800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>206100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>78200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>69200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>61200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>55200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>43800</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>36900</v>
       </c>
-      <c r="Y66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5305,8 +5463,11 @@
       <c r="AD66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5337,8 +5498,9 @@
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
-    </row>
-    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE67" s="3"/>
+    </row>
+    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5423,8 +5585,11 @@
       <c r="AD68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5509,8 +5674,11 @@
       <c r="AD69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5569,17 +5737,17 @@
         <v>0</v>
       </c>
       <c r="V70" s="3">
+        <v>0</v>
+      </c>
+      <c r="W70" s="3">
         <v>302000</v>
       </c>
-      <c r="W70" s="3">
+      <c r="X70" s="3">
         <v>298800</v>
       </c>
-      <c r="X70" s="3">
+      <c r="Y70" s="3">
         <v>439200</v>
       </c>
-      <c r="Y70" s="3">
-        <v>0</v>
-      </c>
       <c r="Z70" s="3">
         <v>0</v>
       </c>
@@ -5595,8 +5763,11 @@
       <c r="AD70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5681,77 +5852,80 @@
       <c r="AD71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1476300</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1379600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1288600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1189900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1332700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-1236600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-1153800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-1057400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-1019000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-909400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-837500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-768300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-703600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-675400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-599200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-397600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-302200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-267700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-233500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-203000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-175200</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-156200</v>
       </c>
-      <c r="Y72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5767,8 +5941,11 @@
       <c r="AD72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5853,8 +6030,11 @@
       <c r="AD73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5939,8 +6119,11 @@
       <c r="AD74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6025,77 +6208,80 @@
       <c r="AD75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>791300</v>
+      </c>
+      <c r="E76" s="3">
         <v>854100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>913500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>981300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>778900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>811600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>761500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>733500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>714500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>800200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>829100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>826700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>853800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>548600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>422400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>245600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>200100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>230800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>261400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>-201100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>-172100</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>-295500</v>
       </c>
-      <c r="Y76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z76" s="3" t="s">
         <v>3</v>
       </c>
@@ -6111,8 +6297,11 @@
       <c r="AD76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6197,185 +6386,194 @@
       <c r="AD77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43373</v>
       </c>
-      <c r="AB80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AC80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AD80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-96700</v>
+      </c>
+      <c r="E81" s="3">
         <v>-91100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-98700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>142800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-96100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-82800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-96500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-38300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-109600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-72000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-69200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-64700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-28100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-76300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-201600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-95500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-34500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-34200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-31700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-31100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-22300</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-52600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-16600</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-216700</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-70400</v>
       </c>
-      <c r="AB81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6406,94 +6604,98 @@
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
-    </row>
-    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE82" s="3"/>
+    </row>
+    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>5600</v>
+        <v>5200</v>
       </c>
       <c r="E83" s="3">
-        <v>5400</v>
+        <v>4800</v>
       </c>
       <c r="F83" s="3">
-        <v>5400</v>
+        <v>4600</v>
       </c>
       <c r="G83" s="3">
-        <v>5200</v>
+        <v>3900</v>
       </c>
       <c r="H83" s="3">
-        <v>4800</v>
+        <v>3500</v>
       </c>
       <c r="I83" s="3">
-        <v>4600</v>
+        <v>3400</v>
       </c>
       <c r="J83" s="3">
+        <v>3300</v>
+      </c>
+      <c r="K83" s="3">
         <v>3900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>3500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>3400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>3300</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>2600</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>1800</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>1700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>1400</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>1300</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>1200</v>
-      </c>
-      <c r="T83" s="3">
-        <v>1100</v>
       </c>
       <c r="U83" s="3">
         <v>1100</v>
       </c>
       <c r="V83" s="3">
+        <v>1100</v>
+      </c>
+      <c r="W83" s="3">
         <v>1000</v>
-      </c>
-      <c r="W83" s="3">
-        <v>900</v>
       </c>
       <c r="X83" s="3">
         <v>900</v>
       </c>
       <c r="Y83" s="3">
+        <v>900</v>
+      </c>
+      <c r="Z83" s="3">
         <v>700</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>500</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>100</v>
       </c>
-      <c r="AB83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC83" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6578,8 +6780,11 @@
       <c r="AD84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6664,8 +6869,11 @@
       <c r="AD85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6750,8 +6958,11 @@
       <c r="AD86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6836,8 +7047,11 @@
       <c r="AD87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6922,94 +7136,100 @@
       <c r="AD88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-88100</v>
+      </c>
+      <c r="E89" s="3">
         <v>-83000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-99700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>135100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-89800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-84700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-109800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-69200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-74500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-52300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>218500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>3000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-32500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-38600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-24300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-21200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-22800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-27400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-17800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-17000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>16900</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-25900</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>4200</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-9400</v>
       </c>
-      <c r="AB89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7040,94 +7260,98 @@
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
-    </row>
-    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE90" s="3"/>
+    </row>
+    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E91" s="3">
         <v>-2000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-2400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-3600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-7900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-16200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-6000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-8300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-11800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-21600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-7300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-13400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-5800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-16200</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-11500</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-8100</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-2800</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-2400</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-3000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-2200</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-1400</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-6600</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-2400</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-11200</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-700</v>
       </c>
-      <c r="AB91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC91" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7212,8 +7436,11 @@
       <c r="AD92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7298,94 +7525,100 @@
       <c r="AD93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>24700</v>
+      </c>
+      <c r="E94" s="3">
         <v>87500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-53500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>98100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-10200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-41500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>25500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>113400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-36200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-537300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-77500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>76100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-13100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-279600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-81400</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>35200</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>22900</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-76800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>16600</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-83200</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>2400</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-2400</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>22000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-2200</v>
       </c>
-      <c r="AB94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7416,31 +7649,32 @@
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
-    </row>
-    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE95" s="3"/>
+    </row>
+    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -7502,8 +7736,11 @@
       <c r="AD96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7588,8 +7825,11 @@
       <c r="AD97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7674,8 +7914,11 @@
       <c r="AD98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7760,117 +8003,123 @@
       <c r="AD99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E100" s="3">
         <v>100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>2900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>33700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>36800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>107500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>98400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>32000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>1600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>22300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>55700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>21500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>320900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>160400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>253300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>130000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-800</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>193000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>700</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>2700</v>
       </c>
-      <c r="X100" s="3">
-        <v>0</v>
-      </c>
       <c r="Y100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z100" s="3">
         <v>37900</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>120100</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>9900</v>
       </c>
-      <c r="AB100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -7932,90 +8181,96 @@
       <c r="AD101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-62200</v>
+      </c>
+      <c r="E102" s="3">
         <v>4600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-150300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>266900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-63200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-18600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>14100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>76300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-109100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-31200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-263200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-54100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>400000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>114800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-64900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>24300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>14100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>88800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-500</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-106500</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>9700</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>105900</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-500</v>
       </c>
-      <c r="AB102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BEAM_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BEAM_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="92">
   <si>
     <t>BEAM</t>
   </si>
@@ -656,180 +656,183 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AE102"/>
+  <dimension ref="A5:AF102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="31" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="32" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43555</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43465</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43373</v>
       </c>
-      <c r="AC7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AD7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AE7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>30100</v>
+      </c>
+      <c r="E8" s="3">
         <v>14300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>11800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>7400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>316200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>17200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>20100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>24200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>20000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>15800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>16700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>8400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>51100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>800</v>
       </c>
-      <c r="Q8" s="3">
-        <v>0</v>
-      </c>
       <c r="R8" s="3">
         <v>0</v>
       </c>
@@ -872,35 +875,38 @@
       <c r="AE8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>101400</v>
+      </c>
+      <c r="E9" s="3">
         <v>94300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>87000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>84800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>140100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>100100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>97600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>99600</v>
       </c>
-      <c r="K9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L9" s="3" t="s">
         <v>3</v>
       </c>
@@ -961,35 +967,38 @@
       <c r="AE9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>-71400</v>
+      </c>
+      <c r="E10" s="3">
         <v>-80000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>-75300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>-77400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>176100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>-82900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>-77500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>-75400</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L10" s="3" t="s">
         <v>3</v>
       </c>
@@ -1050,8 +1059,11 @@
       <c r="AE10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1083,97 +1095,101 @@
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF11" s="3"/>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>101400</v>
+      </c>
+      <c r="E12" s="3">
         <v>94300</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>87000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>84800</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>140100</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>100100</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>97600</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>99600</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>86300</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>85300</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>74600</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>65400</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>96800</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>54600</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>45600</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>190100</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>32500</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>29800</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>19400</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>21500</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>20200</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>12500</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>34500</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>9200</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>29600</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>9900</v>
       </c>
-      <c r="AC12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1261,35 +1277,38 @@
       <c r="AE13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E14" s="3">
         <v>2100</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>5800</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>3500</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-1100</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>5200</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-8300</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>13100</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
       <c r="L14" s="3">
         <v>0</v>
       </c>
@@ -1350,35 +1369,38 @@
       <c r="AE14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>5400</v>
+      </c>
+      <c r="E15" s="3">
         <v>5500</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>5600</v>
-      </c>
-      <c r="F15" s="3">
-        <v>5400</v>
       </c>
       <c r="G15" s="3">
         <v>5400</v>
       </c>
       <c r="H15" s="3">
+        <v>5400</v>
+      </c>
+      <c r="I15" s="3">
         <v>5200</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>4800</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>4600</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
@@ -1439,8 +1461,11 @@
       <c r="AE15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1469,186 +1494,193 @@
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
-    </row>
-    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF16" s="3"/>
+    </row>
+    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>130100</v>
+      </c>
+      <c r="E17" s="3">
         <v>120800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>116700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>111500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>183300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>125500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>122300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>123100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>109000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>107100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>98600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>84700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>114600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>70400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>59000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>200400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>40800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>37300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>26300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>28400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>26400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>18000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>48400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>13100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>39800</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>12700</v>
       </c>
-      <c r="AC17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-100000</v>
+      </c>
+      <c r="E18" s="3">
         <v>-106500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-104900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-104100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>132900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-108300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-102100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-98900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-89000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-91300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-81900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-76300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-63500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-69600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-59000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-200400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-40800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-37300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-26300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-28400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-26400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-18000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-48400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-13100</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-39800</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-12700</v>
       </c>
-      <c r="AC18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1680,186 +1712,193 @@
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
-    </row>
-    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF19" s="3"/>
+    </row>
+    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>100</v>
+      </c>
+      <c r="E20" s="3">
         <v>200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-5500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>2900</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>1900</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-4700</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>900</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-5600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>51700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>9600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>10000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>7000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-1300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>41500</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-17300</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-1200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-54700</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>2900</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-7900</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-2100</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-1400</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-900</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>30600</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-500</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>14600</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-58500</v>
       </c>
-      <c r="AC20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-94700</v>
+      </c>
+      <c r="E21" s="3">
         <v>-101200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-93800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-101600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>136300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-98400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-98200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-88700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-33400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-78200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-68500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-65900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-62100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-26400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-74600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-200200</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-94200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-33200</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-33100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-29400</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-26700</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-19600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-15400</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-12900</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-24000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-71100</v>
       </c>
-      <c r="AC21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1884,8 +1923,8 @@
       <c r="J22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
@@ -1902,8 +1941,8 @@
       <c r="P22" s="3">
         <v>0</v>
       </c>
-      <c r="Q22" s="3" t="s">
-        <v>3</v>
+      <c r="Q22" s="3">
+        <v>0</v>
       </c>
       <c r="R22" s="3" t="s">
         <v>3</v>
@@ -1920,14 +1959,14 @@
       <c r="V22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W22" s="3">
-        <v>100</v>
+      <c r="W22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X22" s="3">
         <v>100</v>
       </c>
-      <c r="Y22" s="3" t="s">
-        <v>3</v>
+      <c r="Y22" s="3">
+        <v>100</v>
       </c>
       <c r="Z22" s="3" t="s">
         <v>3</v>
@@ -1947,130 +1986,136 @@
       <c r="AE22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-90400</v>
+      </c>
+      <c r="E23" s="3">
         <v>-96700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-91000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-98700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>144200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-96100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-82800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-96500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-37300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-81700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-72000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-69200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-64700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-28100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-76300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-201600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-95500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-34500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-34200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-30500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-27900</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-19000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-17900</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-13600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-25200</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-71200</v>
       </c>
-      <c r="AC23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G24" s="3">
+      <c r="D24" s="3">
+        <v>0</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F24" s="3">
+        <v>0</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H24" s="3">
         <v>1400</v>
       </c>
-      <c r="H24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I24" s="3" t="s">
         <v>3</v>
       </c>
       <c r="J24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K24" s="3">
+      <c r="K24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L24" s="3">
         <v>1000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>2400</v>
       </c>
-      <c r="M24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N24" s="3" t="s">
         <v>3</v>
       </c>
@@ -2104,18 +2149,18 @@
       <c r="X24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Y24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z24" s="3">
         <v>-31500</v>
       </c>
-      <c r="Z24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA24" s="3">
+      <c r="AA24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB24" s="3">
         <v>-96300</v>
       </c>
-      <c r="AB24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC24" s="3" t="s">
         <v>3</v>
       </c>
@@ -2125,8 +2170,11 @@
       <c r="AE24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2214,186 +2262,195 @@
       <c r="AE25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-90400</v>
+      </c>
+      <c r="E26" s="3">
         <v>-96700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-91100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-98700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>142800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-96100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-82800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-96500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-38300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-84100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-72000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-69200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-64700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-28100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-76300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-201600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-95500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-34500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-34200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-30500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-27900</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-19000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-17900</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-13600</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-23800</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-71200</v>
       </c>
-      <c r="AC26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-90400</v>
+      </c>
+      <c r="E27" s="3">
         <v>-96700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-91100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-98700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>142800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-96100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-82800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-96500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-38300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-109600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-72000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-69200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-64700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-28100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-76300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-201600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-95500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-34500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-34200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-31700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-31100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-22300</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-52600</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-16600</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-216700</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-70400</v>
       </c>
-      <c r="AC27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2481,8 +2538,11 @@
       <c r="AE28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2570,8 +2630,11 @@
       <c r="AE29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2659,8 +2722,11 @@
       <c r="AE30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2748,186 +2814,195 @@
       <c r="AE31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E32" s="3">
         <v>-200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>5500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-2900</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-1900</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>4700</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-900</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>5600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-51700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-9600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-10000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-7000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>1300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-41500</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>17300</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>1200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>54700</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-2900</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>7900</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>2100</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>1400</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>900</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-30600</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>500</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-14600</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>58500</v>
       </c>
-      <c r="AC32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-90400</v>
+      </c>
+      <c r="E33" s="3">
         <v>-96700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-91100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-98700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>142800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-96100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-82800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-96500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-38300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-109600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-72000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-69200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-64700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-28100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-76300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-201600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-95500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-34500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-34200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-31700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-31100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-22300</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-52600</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-16600</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-216700</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-70400</v>
       </c>
-      <c r="AC33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3015,191 +3090,200 @@
       <c r="AE34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-90400</v>
+      </c>
+      <c r="E35" s="3">
         <v>-96700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-91100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-98700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>142800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-96100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-82800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-96500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-38300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-109600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-72000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-69200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-64700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-28100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-76300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-201600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-95500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-34500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-34200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-31700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-31100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-22300</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-52600</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-16600</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-216700</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-70400</v>
       </c>
-      <c r="AC35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43555</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43465</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43373</v>
       </c>
-      <c r="AC38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AD38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AE38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3231,8 +3315,9 @@
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
-    </row>
-    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF39" s="3"/>
+    </row>
+    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3264,80 +3349,81 @@
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
-    </row>
-    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF40" s="3"/>
+    </row>
+    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>282000</v>
+      </c>
+      <c r="E41" s="3">
         <v>230200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>292800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>287800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>435900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>169000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>225500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>249800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>232800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>156500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>265600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>296800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>560000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>612000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>212000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>97200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>162200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>137900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>125300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>126100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>37200</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>37800</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>37900</v>
       </c>
-      <c r="Z41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3353,80 +3439,83 @@
       <c r="AE41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>568800</v>
+      </c>
+      <c r="E42" s="3">
         <v>695600</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>715400</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>806700</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>754000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>846400</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>847500</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>809700</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>845400</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>938000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>900500</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>925800</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>405700</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>321400</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>403300</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>406200</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>137500</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>64300</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>102600</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>127400</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>54600</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>73100</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>88900</v>
       </c>
-      <c r="Z42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3442,8 +3531,11 @@
       <c r="AE42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3468,8 +3560,8 @@
       <c r="J43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K43" s="3">
-        <v>0</v>
+      <c r="K43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L43" s="3">
         <v>0</v>
@@ -3481,17 +3573,17 @@
         <v>0</v>
       </c>
       <c r="O43" s="3">
+        <v>0</v>
+      </c>
+      <c r="P43" s="3">
         <v>300000</v>
       </c>
-      <c r="P43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q43" s="3">
+      <c r="Q43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R43" s="3">
         <v>50000</v>
       </c>
-      <c r="R43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3507,8 +3599,8 @@
       <c r="W43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X43" s="3">
-        <v>0</v>
+      <c r="X43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y43" s="3">
         <v>0</v>
@@ -3531,8 +3623,11 @@
       <c r="AE43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3557,8 +3652,8 @@
       <c r="J44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -3620,8 +3715,11 @@
       <c r="AE44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3646,54 +3744,54 @@
       <c r="J45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L45" s="3">
         <v>14800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>14400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>13800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>16900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>7400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>8000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>12700</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>11100</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>8700</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>6500</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>6900</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>6200</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>2700</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>3900</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>2600</v>
       </c>
-      <c r="Z45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3709,80 +3807,83 @@
       <c r="AE45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>878100</v>
+      </c>
+      <c r="E46" s="3">
         <v>945500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1029400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1121700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1211000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1039500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1094800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1083000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1092900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1108900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1179900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1239500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1273000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>941400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>678000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>514600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>308300</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>208700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>234800</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>259600</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>94500</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>114800</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>129400</v>
       </c>
-      <c r="Z46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3798,8 +3899,11 @@
       <c r="AE46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3824,8 +3928,8 @@
       <c r="J47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
@@ -3836,18 +3940,18 @@
       <c r="N47" s="3">
         <v>0</v>
       </c>
-      <c r="O47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P47" s="3">
+      <c r="O47" s="3">
+        <v>0</v>
+      </c>
+      <c r="P47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q47" s="3">
         <v>24500</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>29400</v>
       </c>
-      <c r="R47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3863,8 +3967,8 @@
       <c r="W47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X47" s="3">
-        <v>0</v>
+      <c r="X47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y47" s="3">
         <v>0</v>
@@ -3887,80 +3991,83 @@
       <c r="AE47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>216300</v>
+      </c>
+      <c r="E48" s="3">
         <v>218200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>224300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>229900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>237800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>239700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>242300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>238000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>234100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>226700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>223500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>199800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>187000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>174700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>169700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>158800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>125400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>51200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>48600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>46900</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>43200</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>38000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>36800</v>
       </c>
-      <c r="Z48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3976,8 +4083,11 @@
       <c r="AE48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4065,8 +4175,11 @@
       <c r="AE49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4154,8 +4267,11 @@
       <c r="AE50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4243,80 +4359,83 @@
       <c r="AE51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>9400</v>
+      </c>
+      <c r="E52" s="3">
         <v>7600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>7500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>8100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>10900</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>11300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>16800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>11300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>14700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>14600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>15000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>14100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>14500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>15900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>16000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>19900</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>18000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>18400</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>16600</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>16100</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>18300</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>17800</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>14400</v>
       </c>
-      <c r="Z52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4332,8 +4451,11 @@
       <c r="AE52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4421,80 +4543,83 @@
       <c r="AE53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1103800</v>
+      </c>
+      <c r="E54" s="3">
         <v>1171400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1261300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1359800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1459700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1290500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1353900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1332400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1341700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1350300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1418400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1453400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1474500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1156600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>893100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>693200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>451700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>278300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>300000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>322600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>156100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>170600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>180500</v>
       </c>
-      <c r="Z54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4510,8 +4635,11 @@
       <c r="AE54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4543,8 +4671,9 @@
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
-    </row>
-    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF55" s="3"/>
+    </row>
+    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4576,80 +4705,81 @@
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
-    </row>
-    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF56" s="3"/>
+    </row>
+    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E57" s="3">
         <v>3800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>4400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>3200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>6900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>14100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>9000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>7000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>7100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>6300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>7500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>7300</v>
-      </c>
-      <c r="Q57" s="3">
-        <v>8000</v>
       </c>
       <c r="R57" s="3">
         <v>8000</v>
       </c>
       <c r="S57" s="3">
+        <v>8000</v>
+      </c>
+      <c r="T57" s="3">
         <v>6300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>6600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>6200</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>6100</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>7800</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>3900</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>4000</v>
       </c>
-      <c r="Z57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4665,61 +4795,64 @@
       <c r="AE57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>13500</v>
+      </c>
+      <c r="E58" s="3">
         <v>12900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>12600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>12200</v>
       </c>
-      <c r="G58" s="3">
-        <v>13300</v>
-      </c>
       <c r="H58" s="3">
+        <v>12800</v>
+      </c>
+      <c r="I58" s="3">
         <v>13000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>12400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>12600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>2200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>2400</v>
-      </c>
-      <c r="N58" s="3">
-        <v>2300</v>
       </c>
       <c r="O58" s="3">
         <v>2300</v>
       </c>
       <c r="P58" s="3">
-        <v>2200</v>
+        <v>2300</v>
       </c>
       <c r="Q58" s="3">
         <v>2200</v>
       </c>
       <c r="R58" s="3">
-        <v>2100</v>
+        <v>2200</v>
       </c>
       <c r="S58" s="3">
         <v>2100</v>
       </c>
       <c r="T58" s="3">
-        <v>1700</v>
+        <v>2100</v>
       </c>
       <c r="U58" s="3">
         <v>1700</v>
@@ -4728,17 +4861,17 @@
         <v>1700</v>
       </c>
       <c r="W58" s="3">
+        <v>1700</v>
+      </c>
+      <c r="X58" s="3">
         <v>1300</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>800</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>7300</v>
       </c>
-      <c r="Z58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA58" s="3" t="s">
         <v>3</v>
       </c>
@@ -4754,80 +4887,83 @@
       <c r="AE58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>128600</v>
+      </c>
+      <c r="E59" s="3">
         <v>124000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>140000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>157800</v>
       </c>
-      <c r="G59" s="3">
-        <v>155600</v>
-      </c>
       <c r="H59" s="3">
+        <v>156100</v>
+      </c>
+      <c r="I59" s="3">
         <v>171600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>163800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>172800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>212700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>229600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>202800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>210200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>203700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>91900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>118500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>92000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>93900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>39100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>31100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>23700</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>20000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>15300</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>56200</v>
       </c>
-      <c r="Z59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4843,80 +4979,83 @@
       <c r="AE59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>182100</v>
+      </c>
+      <c r="E60" s="3">
         <v>166200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>177300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>187200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>205600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>220400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>209500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>219900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>223600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>238900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>212300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>218800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>213400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>101400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>128700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>102100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>102300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>47500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>39000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>31400</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>29100</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>19900</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>52200</v>
       </c>
-      <c r="Z60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4932,80 +5071,83 @@
       <c r="AE60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>148000</v>
+      </c>
+      <c r="E61" s="3">
         <v>149100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>152600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>155900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>159900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>160900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>164700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>166300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>3000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>3600</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>4200</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>4700</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>5300</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>4400</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>4900</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>5300</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>4400</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>2800</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>300</v>
       </c>
-      <c r="Z61" s="3">
-        <v>0</v>
-      </c>
       <c r="AA61" s="3">
         <v>0</v>
       </c>
@@ -5021,77 +5163,80 @@
       <c r="AE61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>7000</v>
+      </c>
+      <c r="E62" s="3">
         <v>6900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>3600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>3000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>5600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>11800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>12900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>383500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>395500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>404100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>403100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>431300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>197800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>211600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>164000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>98500</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>26300</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>25300</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>24500</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>21600</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>21100</v>
       </c>
-      <c r="Y62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z62" s="3" t="s">
         <v>3</v>
       </c>
@@ -5110,8 +5255,11 @@
       <c r="AE62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5199,8 +5347,11 @@
       <c r="AE63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5288,8 +5439,11 @@
       <c r="AE64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5377,80 +5531,83 @@
       <c r="AE65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>370300</v>
+      </c>
+      <c r="E66" s="3">
         <v>380100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>407200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>446300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>478400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>511600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>542200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>570800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>608200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>635800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>618200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>624300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>647700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>302700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>344500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>270800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>206100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>78200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>69200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>61200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>55200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>43800</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>36900</v>
       </c>
-      <c r="Z66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5466,8 +5623,11 @@
       <c r="AE66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5499,8 +5659,9 @@
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
-    </row>
-    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF67" s="3"/>
+    </row>
+    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5588,8 +5749,11 @@
       <c r="AE68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5677,8 +5841,11 @@
       <c r="AE69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5740,17 +5907,17 @@
         <v>0</v>
       </c>
       <c r="W70" s="3">
+        <v>0</v>
+      </c>
+      <c r="X70" s="3">
         <v>302000</v>
       </c>
-      <c r="X70" s="3">
+      <c r="Y70" s="3">
         <v>298800</v>
       </c>
-      <c r="Y70" s="3">
+      <c r="Z70" s="3">
         <v>439200</v>
       </c>
-      <c r="Z70" s="3">
-        <v>0</v>
-      </c>
       <c r="AA70" s="3">
         <v>0</v>
       </c>
@@ -5766,8 +5933,11 @@
       <c r="AE70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5855,80 +6025,83 @@
       <c r="AE71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1566600</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1476300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1379600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1288600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1189900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-1332700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-1236600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-1153800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-1057400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-1019000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-909400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-837500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-768300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-703600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-675400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-599200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-397600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-302200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-267700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-233500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-203000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-175200</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-156200</v>
       </c>
-      <c r="Z72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5944,8 +6117,11 @@
       <c r="AE72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6033,8 +6209,11 @@
       <c r="AE73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6122,8 +6301,11 @@
       <c r="AE74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6211,80 +6393,83 @@
       <c r="AE75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>733500</v>
+      </c>
+      <c r="E76" s="3">
         <v>791300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>854100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>913500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>981300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>778900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>811600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>761500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>733500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>714500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>800200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>829100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>826700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>853800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>548600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>422400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>245600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>200100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>230800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>261400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>-201100</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>-172100</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>-295500</v>
       </c>
-      <c r="Z76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA76" s="3" t="s">
         <v>3</v>
       </c>
@@ -6300,8 +6485,11 @@
       <c r="AE76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6389,191 +6577,200 @@
       <c r="AE77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43555</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43465</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43373</v>
       </c>
-      <c r="AC80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AD80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AE80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-90400</v>
+      </c>
+      <c r="E81" s="3">
         <v>-96700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-91100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-98700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>142800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-96100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-82800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-96500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-38300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-109600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-72000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-69200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-64700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-28100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-76300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-201600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-95500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-34500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-34200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-31700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-31100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-22300</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-52600</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-16600</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-216700</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-70400</v>
       </c>
-      <c r="AC81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6605,97 +6802,101 @@
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
-    </row>
-    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF82" s="3"/>
+    </row>
+    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>5400</v>
+      </c>
+      <c r="E83" s="3">
         <v>5200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>4800</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>4600</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>3900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>3500</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>3400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>3300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>3900</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>3500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>3400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>3300</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>2600</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>1800</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>1700</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>1400</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>1300</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>1200</v>
-      </c>
-      <c r="U83" s="3">
-        <v>1100</v>
       </c>
       <c r="V83" s="3">
         <v>1100</v>
       </c>
       <c r="W83" s="3">
+        <v>1100</v>
+      </c>
+      <c r="X83" s="3">
         <v>1000</v>
-      </c>
-      <c r="X83" s="3">
-        <v>900</v>
       </c>
       <c r="Y83" s="3">
         <v>900</v>
       </c>
       <c r="Z83" s="3">
+        <v>900</v>
+      </c>
+      <c r="AA83" s="3">
         <v>700</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>500</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>100</v>
       </c>
-      <c r="AC83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD83" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6783,8 +6984,11 @@
       <c r="AE84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6872,8 +7076,11 @@
       <c r="AE85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6961,8 +7168,11 @@
       <c r="AE86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7050,8 +7260,11 @@
       <c r="AE87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7139,97 +7352,103 @@
       <c r="AE88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-76400</v>
+      </c>
+      <c r="E89" s="3">
         <v>-88100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-83000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-99700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>135100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-89800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-84700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-109800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-69200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-74500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-52300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>218500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>3000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-32500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-38600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-24300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-21200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-22800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-27400</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-17800</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-17000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>16900</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-25900</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>4200</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-9400</v>
       </c>
-      <c r="AC89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7261,97 +7480,101 @@
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
-    </row>
-    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF90" s="3"/>
+    </row>
+    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-2000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-2400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-3600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-7900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-16200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-6000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-8300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-11800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-21600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-7300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-13400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-5800</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-16200</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-11500</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-8100</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-2800</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-2400</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-3000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-2200</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-1400</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-6600</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-2400</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-11200</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-700</v>
       </c>
-      <c r="AC91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD91" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7439,8 +7662,11 @@
       <c r="AE92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7528,97 +7754,103 @@
       <c r="AE93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>126300</v>
+      </c>
+      <c r="E94" s="3">
         <v>24700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>87500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-53500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>98100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-10200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-41500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>25500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>113400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-36200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-537300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-77500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>76100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-13100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-279600</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-81400</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>35200</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>22900</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-76800</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>16600</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-83200</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>2400</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-2400</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>22000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-2200</v>
       </c>
-      <c r="AC94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7650,8 +7882,9 @@
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
-    </row>
-    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF95" s="3"/>
+    </row>
+    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7676,8 +7909,8 @@
       <c r="J96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -7739,8 +7972,11 @@
       <c r="AE96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7828,8 +8064,11 @@
       <c r="AE97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7917,8 +8156,11 @@
       <c r="AE98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8006,97 +8248,103 @@
       <c r="AE99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E100" s="3">
         <v>1300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>2900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>33700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>36800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>107500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>98400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>32000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>1600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>22300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>55700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>21500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>320900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>160400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>253300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>130000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-800</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>193000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>700</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>2700</v>
       </c>
-      <c r="Y100" s="3">
-        <v>0</v>
-      </c>
       <c r="Z100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA100" s="3">
         <v>37900</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>120100</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>9900</v>
       </c>
-      <c r="AC100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8121,8 +8369,8 @@
       <c r="J101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -8184,93 +8432,99 @@
       <c r="AE101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>53400</v>
+      </c>
+      <c r="E102" s="3">
         <v>-62200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>4600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-150300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>266900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-63200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-18600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>14100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>76300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-109100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-31200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-263200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-54100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>400000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>114800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-64900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>24300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>14100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-700</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>88800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-500</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-100</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-106500</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>9700</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>105900</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-500</v>
       </c>
-      <c r="AC102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BEAM_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BEAM_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="92">
   <si>
     <t>BEAM</t>
   </si>
@@ -656,186 +656,190 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="32" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="33" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43646</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43555</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43465</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43373</v>
       </c>
-      <c r="AD7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AE7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AF7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>7500</v>
+      </c>
+      <c r="E8" s="3">
         <v>30100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>14300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>11800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>7400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>316200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>17200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>20100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>24200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>20000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>15800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>16700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>8400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>51100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>800</v>
       </c>
-      <c r="R8" s="3">
-        <v>0</v>
-      </c>
       <c r="S8" s="3">
         <v>0</v>
       </c>
@@ -878,38 +882,41 @@
       <c r="AF8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>15700</v>
+      </c>
+      <c r="E9" s="3">
         <v>101400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>94300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>87000</v>
       </c>
-      <c r="G9" s="3">
-        <v>84800</v>
-      </c>
       <c r="H9" s="3">
+        <v>17600</v>
+      </c>
+      <c r="I9" s="3">
         <v>140100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>100100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>97600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>99600</v>
       </c>
-      <c r="L9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M9" s="3" t="s">
         <v>3</v>
       </c>
@@ -970,38 +977,41 @@
       <c r="AF9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>-8300</v>
+      </c>
+      <c r="E10" s="3">
         <v>-71400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>-80000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>-75300</v>
       </c>
-      <c r="G10" s="3">
-        <v>-77400</v>
-      </c>
       <c r="H10" s="3">
+        <v>-10200</v>
+      </c>
+      <c r="I10" s="3">
         <v>176100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>-82900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>-77500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>-75400</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M10" s="3" t="s">
         <v>3</v>
       </c>
@@ -1062,8 +1072,11 @@
       <c r="AF10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1096,100 +1109,104 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>83100</v>
+      </c>
+      <c r="E12" s="3">
         <v>101400</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>94300</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>87000</v>
       </c>
-      <c r="G12" s="3">
-        <v>84800</v>
-      </c>
       <c r="H12" s="3">
+        <v>67200</v>
+      </c>
+      <c r="I12" s="3">
         <v>140100</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>100100</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>97600</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>99600</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>86300</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>85300</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>74600</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>65400</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>96800</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>54600</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>45600</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>190100</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>32500</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>29800</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>19400</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>21500</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>20200</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>12500</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>34500</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>9200</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>29600</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>9900</v>
       </c>
-      <c r="AD12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AF12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1280,38 +1297,41 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E14" s="3">
         <v>1100</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>2100</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>5800</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>3500</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-1100</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>5200</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-8300</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>13100</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
       <c r="M14" s="3">
         <v>0</v>
       </c>
@@ -1372,38 +1392,41 @@
       <c r="AF14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>5500</v>
+      </c>
+      <c r="E15" s="3">
         <v>5400</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>5500</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>5600</v>
-      </c>
-      <c r="G15" s="3">
-        <v>5400</v>
       </c>
       <c r="H15" s="3">
         <v>5400</v>
       </c>
       <c r="I15" s="3">
+        <v>5400</v>
+      </c>
+      <c r="J15" s="3">
         <v>5200</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>4800</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>4600</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
@@ -1464,8 +1487,11 @@
       <c r="AF15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1495,192 +1521,199 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>126800</v>
+      </c>
+      <c r="E17" s="3">
         <v>130100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>120800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>116700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>111500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>183300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>125500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>122300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>123100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>109000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>107100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>98600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>84700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>114600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>70400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>59000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>200400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>40800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>37300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>26300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>28400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>26400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>18000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>48400</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>13100</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>39800</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>12700</v>
       </c>
-      <c r="AD17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AF17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-119300</v>
+      </c>
+      <c r="E18" s="3">
         <v>-100000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-106500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-104900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-104100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>132900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-108300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-102100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-98900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-89000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-91300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-81900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-76300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-63500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-69600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-59000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-200400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-40800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-37300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-26300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-28400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-26400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-18000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-48400</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-13100</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-39800</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-12700</v>
       </c>
-      <c r="AD18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AF18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1713,192 +1746,199 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="E20" s="3">
         <v>100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-5500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>2900</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>1900</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-4700</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-5600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>51700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>9600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>10000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>7000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-1300</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>41500</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-17300</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-1200</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-54700</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>2900</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-7900</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-2100</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-1400</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-900</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>30600</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-500</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>14600</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-58500</v>
       </c>
-      <c r="AD20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AF20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-111500</v>
+      </c>
+      <c r="E21" s="3">
         <v>-94700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-101200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-93800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-101600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>136300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-98400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-98200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-88700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-33400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-78200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-68500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-65900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-62100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-26400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-74600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-200200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-94200</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-33200</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-33100</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-29400</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-26700</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-19600</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-15400</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-12900</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-24000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-71100</v>
       </c>
-      <c r="AD21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AF21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1926,8 +1966,8 @@
       <c r="K22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="L22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -1944,8 +1984,8 @@
       <c r="Q22" s="3">
         <v>0</v>
       </c>
-      <c r="R22" s="3" t="s">
-        <v>3</v>
+      <c r="R22" s="3">
+        <v>0</v>
       </c>
       <c r="S22" s="3" t="s">
         <v>3</v>
@@ -1962,14 +2002,14 @@
       <c r="W22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X22" s="3">
-        <v>100</v>
+      <c r="X22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y22" s="3">
         <v>100</v>
       </c>
-      <c r="Z22" s="3" t="s">
-        <v>3</v>
+      <c r="Z22" s="3">
+        <v>100</v>
       </c>
       <c r="AA22" s="3" t="s">
         <v>3</v>
@@ -1989,136 +2029,142 @@
       <c r="AF22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-109300</v>
+      </c>
+      <c r="E23" s="3">
         <v>-90400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-96700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-91000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-98700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>144200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-96100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-82800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-96500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-37300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-81700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-72000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-69200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-64700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-28100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-76300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-201600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-95500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-34500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-34200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-30500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-27900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-19000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-17900</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-13600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-25200</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-71200</v>
       </c>
-      <c r="AD23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AF23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>0</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H24" s="3">
+      <c r="D24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E24" s="3">
+        <v>0</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G24" s="3">
+        <v>0</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I24" s="3">
         <v>1400</v>
       </c>
-      <c r="I24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J24" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L24" s="3">
+      <c r="L24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M24" s="3">
         <v>1000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>2400</v>
       </c>
-      <c r="N24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O24" s="3" t="s">
         <v>3</v>
       </c>
@@ -2152,18 +2198,18 @@
       <c r="Y24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="Z24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA24" s="3">
         <v>-31500</v>
       </c>
-      <c r="AA24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB24" s="3">
+      <c r="AB24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC24" s="3">
         <v>-96300</v>
       </c>
-      <c r="AC24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD24" s="3" t="s">
         <v>3</v>
       </c>
@@ -2173,8 +2219,11 @@
       <c r="AF24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2265,192 +2314,201 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-109300</v>
+      </c>
+      <c r="E26" s="3">
         <v>-90400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-96700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-91100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-98700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>142800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-96100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-82800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-96500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-38300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-84100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-72000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-69200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-64700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-28100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-76300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-201600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-95500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-34500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-34200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-30500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-27900</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-19000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-17900</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-13600</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-23800</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-71200</v>
       </c>
-      <c r="AD26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AF26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-109300</v>
+      </c>
+      <c r="E27" s="3">
         <v>-90400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-96700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-91100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-98700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>142800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-96100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-82800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-96500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-38300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-109600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-72000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-69200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-64700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-28100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-76300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-201600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-95500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-34500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-34200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-31700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-31100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-22300</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-52600</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-16600</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-216700</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-70400</v>
       </c>
-      <c r="AD27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AF27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2541,8 +2599,11 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2633,8 +2694,11 @@
       <c r="AF29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2725,8 +2789,11 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2817,192 +2884,201 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E32" s="3">
         <v>-100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>5500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-2900</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-1900</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>4700</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>5600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-51700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-9600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-10000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-7000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>1300</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-41500</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>17300</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>1200</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>54700</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-2900</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>7900</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>2100</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>1400</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>900</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-30600</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>500</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-14600</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>58500</v>
       </c>
-      <c r="AD32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AF32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-109300</v>
+      </c>
+      <c r="E33" s="3">
         <v>-90400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-96700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-91100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-98700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>142800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-96100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-82800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-96500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-38300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-109600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-72000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-69200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-64700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-28100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-76300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-201600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-95500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-34500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-34200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-31700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-31100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-22300</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-52600</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-16600</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-216700</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-70400</v>
       </c>
-      <c r="AD33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AF33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3093,197 +3169,206 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-109300</v>
+      </c>
+      <c r="E35" s="3">
         <v>-90400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-96700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-91100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-98700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>142800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-96100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-82800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-96500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-38300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-109600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-72000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-69200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-64700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-28100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-76300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-201600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-95500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-34500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-34200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-31700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-31100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-22300</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-52600</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-16600</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-216700</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-70400</v>
       </c>
-      <c r="AD35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AF35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43646</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43555</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43465</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43373</v>
       </c>
-      <c r="AD38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AE38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AF38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3316,8 +3401,9 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3350,83 +3436,84 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>527900</v>
+      </c>
+      <c r="E41" s="3">
         <v>282000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>230200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>292800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>287800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>435900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>169000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>225500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>249800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>232800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>156500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>265600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>296800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>560000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>612000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>212000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>97200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>162200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>137900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>125300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>126100</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>37200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>37800</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>37900</v>
       </c>
-      <c r="AA41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3442,83 +3529,86 @@
       <c r="AF41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>692000</v>
+      </c>
+      <c r="E42" s="3">
         <v>568800</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>695600</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>715400</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>806700</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>754000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>846400</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>847500</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>809700</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>845400</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>938000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>900500</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>925800</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>405700</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>321400</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>403300</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>406200</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>137500</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>64300</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>102600</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>127400</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>54600</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>73100</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>88900</v>
       </c>
-      <c r="AA42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3534,8 +3624,11 @@
       <c r="AF42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3563,8 +3656,8 @@
       <c r="K43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L43" s="3">
-        <v>0</v>
+      <c r="L43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M43" s="3">
         <v>0</v>
@@ -3576,17 +3669,17 @@
         <v>0</v>
       </c>
       <c r="P43" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q43" s="3">
         <v>300000</v>
       </c>
-      <c r="Q43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R43" s="3">
+      <c r="R43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S43" s="3">
         <v>50000</v>
       </c>
-      <c r="S43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3602,8 +3695,8 @@
       <c r="X43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y43" s="3">
-        <v>0</v>
+      <c r="Y43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z43" s="3">
         <v>0</v>
@@ -3626,8 +3719,11 @@
       <c r="AF43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3655,8 +3751,8 @@
       <c r="K44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -3718,8 +3814,11 @@
       <c r="AF44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3747,54 +3846,54 @@
       <c r="K45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M45" s="3">
         <v>14800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>14400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>13800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>16900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>7400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>8000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>12700</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>11100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>8700</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>6500</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>6900</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>6200</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>2700</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>3900</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>2600</v>
       </c>
-      <c r="AA45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3810,83 +3909,86 @@
       <c r="AF45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1247600</v>
+      </c>
+      <c r="E46" s="3">
         <v>878100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>945500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1029400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1121700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1211000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1039500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1094800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1083000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1092900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1108900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1179900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1239500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1273000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>941400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>678000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>514600</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>308300</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>208700</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>234800</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>259600</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>94500</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>114800</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>129400</v>
       </c>
-      <c r="AA46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3902,8 +4004,11 @@
       <c r="AF46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3931,8 +4036,8 @@
       <c r="K47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="L47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -3943,18 +4048,18 @@
       <c r="O47" s="3">
         <v>0</v>
       </c>
-      <c r="P47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q47" s="3">
+      <c r="P47" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R47" s="3">
         <v>24500</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>29400</v>
       </c>
-      <c r="S47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3970,8 +4075,8 @@
       <c r="X47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y47" s="3">
-        <v>0</v>
+      <c r="Y47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z47" s="3">
         <v>0</v>
@@ -3994,83 +4099,86 @@
       <c r="AF47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>211800</v>
+      </c>
+      <c r="E48" s="3">
         <v>216300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>218200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>224300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>229900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>237800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>239700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>242300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>238000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>234100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>226700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>223500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>199800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>187000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>174700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>169700</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>158800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>125400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>51200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>48600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>46900</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>43200</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>38000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>36800</v>
       </c>
-      <c r="AA48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB48" s="3" t="s">
         <v>3</v>
       </c>
@@ -4086,8 +4194,11 @@
       <c r="AF48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4178,8 +4289,11 @@
       <c r="AF49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4270,8 +4384,11 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4362,83 +4479,86 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>7500</v>
+      </c>
+      <c r="E52" s="3">
         <v>9400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>7600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>7500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>8100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>10900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>11300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>16800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>11300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>14700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>14600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>15000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>14100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>14500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>15900</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>16000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>19900</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>18000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>18400</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>16600</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>16100</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>18300</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>17800</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>14400</v>
       </c>
-      <c r="AA52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4454,8 +4574,11 @@
       <c r="AF52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4546,83 +4669,86 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1466900</v>
+      </c>
+      <c r="E54" s="3">
         <v>1103800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1171400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1261300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1359800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1459700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1290500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1353900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1332400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1341700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1350300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1418400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1453400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1474500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1156600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>893100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>693200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>451700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>278300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>300000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>322600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>156100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>170600</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>180500</v>
       </c>
-      <c r="AA54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4638,8 +4764,11 @@
       <c r="AF54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4672,8 +4801,9 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4706,83 +4836,84 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>7700</v>
+      </c>
+      <c r="E57" s="3">
         <v>3900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>3800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>4400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>3200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>6900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>14100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>9000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>7000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>7100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>6300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>7500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>7300</v>
-      </c>
-      <c r="R57" s="3">
-        <v>8000</v>
       </c>
       <c r="S57" s="3">
         <v>8000</v>
       </c>
       <c r="T57" s="3">
+        <v>8000</v>
+      </c>
+      <c r="U57" s="3">
         <v>6300</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>6600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>6200</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>6100</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>7800</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>3900</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>4000</v>
       </c>
-      <c r="AA57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4798,64 +4929,67 @@
       <c r="AF57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>13200</v>
+      </c>
+      <c r="E58" s="3">
         <v>13500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>12900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>12600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>12200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>12800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>13000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>12400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>12600</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1900</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>2200</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>2400</v>
-      </c>
-      <c r="O58" s="3">
-        <v>2300</v>
       </c>
       <c r="P58" s="3">
         <v>2300</v>
       </c>
       <c r="Q58" s="3">
-        <v>2200</v>
+        <v>2300</v>
       </c>
       <c r="R58" s="3">
         <v>2200</v>
       </c>
       <c r="S58" s="3">
-        <v>2100</v>
+        <v>2200</v>
       </c>
       <c r="T58" s="3">
         <v>2100</v>
       </c>
       <c r="U58" s="3">
-        <v>1700</v>
+        <v>2100</v>
       </c>
       <c r="V58" s="3">
         <v>1700</v>
@@ -4864,17 +4998,17 @@
         <v>1700</v>
       </c>
       <c r="X58" s="3">
+        <v>1700</v>
+      </c>
+      <c r="Y58" s="3">
         <v>1300</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>800</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>7300</v>
       </c>
-      <c r="AA58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB58" s="3" t="s">
         <v>3</v>
       </c>
@@ -4890,83 +5024,86 @@
       <c r="AF58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>98300</v>
+      </c>
+      <c r="E59" s="3">
         <v>128600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>124000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>140000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>157800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>156100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>171600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>163800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>172800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>212700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>229600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>202800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>210200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>203700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>91900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>118500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>92000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>93900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>39100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>31100</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>23700</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>20000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>15300</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>56200</v>
       </c>
-      <c r="AA59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4982,83 +5119,86 @@
       <c r="AF59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>141500</v>
+      </c>
+      <c r="E60" s="3">
         <v>182100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>166200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>177300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>187200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>205600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>220400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>209500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>219900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>223600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>238900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>212300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>218800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>213400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>101400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>128700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>102100</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>102300</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>47500</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>39000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>31400</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>29100</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>19900</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>52200</v>
       </c>
-      <c r="AA60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB60" s="3" t="s">
         <v>3</v>
       </c>
@@ -5074,83 +5214,86 @@
       <c r="AF60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>144900</v>
+      </c>
+      <c r="E61" s="3">
         <v>148000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>149100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>152600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>155900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>159900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>160900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>164700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>166300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>3000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>3600</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>4200</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>4700</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>5300</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>4400</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>4900</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>5300</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>4400</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>2800</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>300</v>
       </c>
-      <c r="AA61" s="3">
-        <v>0</v>
-      </c>
       <c r="AB61" s="3">
         <v>0</v>
       </c>
@@ -5166,80 +5309,83 @@
       <c r="AF61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>7900</v>
+      </c>
+      <c r="E62" s="3">
         <v>7000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>6900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>3600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>3000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>5600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>11800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>12900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>383500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>395500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>404100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>403100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>431300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>197800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>211600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>164000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>98500</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>26300</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>25300</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>24500</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>21600</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>21100</v>
       </c>
-      <c r="Z62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA62" s="3" t="s">
         <v>3</v>
       </c>
@@ -5258,8 +5404,11 @@
       <c r="AF62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5350,8 +5499,11 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5442,8 +5594,11 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5534,83 +5689,86 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>343800</v>
+      </c>
+      <c r="E66" s="3">
         <v>370300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>380100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>407200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>446300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>478400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>511600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>542200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>570800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>608200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>635800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>618200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>624300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>647700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>302700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>344500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>270800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>206100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>78200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>69200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>61200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>55200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>43800</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>36900</v>
       </c>
-      <c r="AA66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5626,8 +5784,11 @@
       <c r="AF66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5660,8 +5821,9 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5752,8 +5914,11 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5844,8 +6009,11 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5910,17 +6078,17 @@
         <v>0</v>
       </c>
       <c r="X70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y70" s="3">
         <v>302000</v>
       </c>
-      <c r="Y70" s="3">
+      <c r="Z70" s="3">
         <v>298800</v>
       </c>
-      <c r="Z70" s="3">
+      <c r="AA70" s="3">
         <v>439200</v>
       </c>
-      <c r="AA70" s="3">
-        <v>0</v>
-      </c>
       <c r="AB70" s="3">
         <v>0</v>
       </c>
@@ -5936,8 +6104,11 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6028,83 +6199,86 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1675900</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1566600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1476300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1379600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1288600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-1189900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-1332700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-1236600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-1153800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-1057400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-1019000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-909400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-837500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-768300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-703600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-675400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-599200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-397600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-302200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-267700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-233500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-203000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-175200</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-156200</v>
       </c>
-      <c r="AA72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB72" s="3" t="s">
         <v>3</v>
       </c>
@@ -6120,8 +6294,11 @@
       <c r="AF72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6212,8 +6389,11 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6304,8 +6484,11 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6396,83 +6579,86 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1123100</v>
+      </c>
+      <c r="E76" s="3">
         <v>733500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>791300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>854100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>913500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>981300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>778900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>811600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>761500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>733500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>714500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>800200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>829100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>826700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>853800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>548600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>422400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>245600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>200100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>230800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>261400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>-201100</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>-172100</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>-295500</v>
       </c>
-      <c r="AA76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB76" s="3" t="s">
         <v>3</v>
       </c>
@@ -6488,8 +6674,11 @@
       <c r="AF76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6580,197 +6769,206 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43646</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43555</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43465</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43373</v>
       </c>
-      <c r="AD80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AE80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AF80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-109300</v>
+      </c>
+      <c r="E81" s="3">
         <v>-90400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-96700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-91100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-98700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>142800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-96100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-82800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-96500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-38300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-109600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-72000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-69200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-64700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-28100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-76300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-201600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-95500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-34500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-34200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-31700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-31100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-22300</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-52600</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-16600</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-216700</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-70400</v>
       </c>
-      <c r="AD81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AF81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6803,8 +7001,9 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6812,91 +7011,94 @@
         <v>5400</v>
       </c>
       <c r="E83" s="3">
+        <v>5400</v>
+      </c>
+      <c r="F83" s="3">
         <v>5200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>4800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>4600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>3900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>3500</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>3400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>3300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>3900</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>3500</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>3400</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>3300</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>2600</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>1800</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>1700</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>1400</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>1300</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>1200</v>
-      </c>
-      <c r="V83" s="3">
-        <v>1100</v>
       </c>
       <c r="W83" s="3">
         <v>1100</v>
       </c>
       <c r="X83" s="3">
+        <v>1100</v>
+      </c>
+      <c r="Y83" s="3">
         <v>1000</v>
-      </c>
-      <c r="Y83" s="3">
-        <v>900</v>
       </c>
       <c r="Z83" s="3">
         <v>900</v>
       </c>
       <c r="AA83" s="3">
+        <v>900</v>
+      </c>
+      <c r="AB83" s="3">
         <v>700</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>500</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>100</v>
       </c>
-      <c r="AD83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE83" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AF83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6987,8 +7189,11 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7079,8 +7284,11 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7171,8 +7379,11 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7263,8 +7474,11 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7355,100 +7569,106 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-103900</v>
+      </c>
+      <c r="E89" s="3">
         <v>-76400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-88100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-83000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-99700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>135100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-89800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-84700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-109800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-69200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-74500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-52300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>218500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>3000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-32500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-38600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-24300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-21200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-22800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-27400</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-17800</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-17000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>16900</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-25900</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>4200</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-9400</v>
       </c>
-      <c r="AD89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AF89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7481,100 +7701,104 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-3000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-2000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-2400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-3600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-7900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-16200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-6000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-8300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-11800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-21600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-7300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-13400</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-5800</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-16200</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-11500</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-8100</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-2800</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-2400</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-3000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-2200</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-1400</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-6600</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-2400</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-11200</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-700</v>
       </c>
-      <c r="AD91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE91" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AF91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7665,8 +7889,11 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7757,100 +7984,106 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-125100</v>
+      </c>
+      <c r="E94" s="3">
         <v>126300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>24700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>87500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-53500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>98100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-10200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-41500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>25500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>113400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-36200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-537300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-77500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>76100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-13100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-279600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-81400</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>35200</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>22900</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-76800</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>16600</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-83200</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>2400</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-2400</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>22000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-2200</v>
       </c>
-      <c r="AD94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AF94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7883,8 +8116,9 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7912,8 +8146,8 @@
       <c r="K96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -7975,8 +8209,11 @@
       <c r="AF96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8067,8 +8304,11 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8159,8 +8399,11 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8251,100 +8494,106 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>473400</v>
+      </c>
+      <c r="E100" s="3">
         <v>3400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>1300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>2900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>33700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>36800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>107500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>98400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>32000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>1600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>22300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>55700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>21500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>320900</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>160400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>253300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>130000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>100</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-800</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>193000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>700</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>2700</v>
       </c>
-      <c r="Z100" s="3">
-        <v>0</v>
-      </c>
       <c r="AA100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB100" s="3">
         <v>37900</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>120100</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>9900</v>
       </c>
-      <c r="AD100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AF100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8372,8 +8621,8 @@
       <c r="K101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -8435,96 +8684,102 @@
       <c r="AF101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>244400</v>
+      </c>
+      <c r="E102" s="3">
         <v>53400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-62200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>4600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-150300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>266900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-63200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-18600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>14100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>76300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-109100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-31200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-263200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-54100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>400000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>114800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-64900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>24300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>14100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-700</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>88800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-500</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-106500</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>9700</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>105900</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-500</v>
       </c>
-      <c r="AD102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AF102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BEAM_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BEAM_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="92">
   <si>
     <t>BEAM</t>
   </si>
@@ -656,193 +656,197 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="33" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="34" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43738</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43646</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43555</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43465</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43373</v>
       </c>
-      <c r="AE7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AF7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AG7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>8500</v>
+      </c>
+      <c r="E8" s="3">
         <v>7500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>30100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>14300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>11800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>7400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>316200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>17200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>20100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>24200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>20000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>15800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>16700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>8400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>51100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>800</v>
       </c>
-      <c r="S8" s="3">
-        <v>0</v>
-      </c>
       <c r="T8" s="3">
         <v>0</v>
       </c>
@@ -885,41 +889,44 @@
       <c r="AG8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>14800</v>
+      </c>
+      <c r="E9" s="3">
         <v>15700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>101400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>94300</v>
       </c>
-      <c r="G9" s="3">
-        <v>87000</v>
-      </c>
       <c r="H9" s="3">
+        <v>18800</v>
+      </c>
+      <c r="I9" s="3">
         <v>17600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>140100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>100100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>97600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>99600</v>
       </c>
-      <c r="M9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N9" s="3" t="s">
         <v>3</v>
       </c>
@@ -980,41 +987,44 @@
       <c r="AG9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>-6400</v>
+      </c>
+      <c r="E10" s="3">
         <v>-8300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>-71400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>-80000</v>
       </c>
-      <c r="G10" s="3">
-        <v>-75300</v>
-      </c>
       <c r="H10" s="3">
+        <v>-7000</v>
+      </c>
+      <c r="I10" s="3">
         <v>-10200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>176100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>-82900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>-77500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>-75400</v>
       </c>
-      <c r="M10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N10" s="3" t="s">
         <v>3</v>
       </c>
@@ -1075,8 +1085,11 @@
       <c r="AG10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1110,103 +1123,107 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>86900</v>
+      </c>
+      <c r="E12" s="3">
         <v>83100</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>101400</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>94300</v>
       </c>
-      <c r="G12" s="3">
-        <v>87000</v>
-      </c>
       <c r="H12" s="3">
+        <v>68200</v>
+      </c>
+      <c r="I12" s="3">
         <v>67200</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>140100</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>100100</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>97600</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>99600</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>86300</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>85300</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>74600</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>65400</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>96800</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>54600</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>45600</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>190100</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>32500</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>29800</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>19400</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>21500</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>20200</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>12500</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>34500</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>9200</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>29600</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>9900</v>
       </c>
-      <c r="AE12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1300,41 +1317,44 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-4400</v>
+      </c>
+      <c r="E14" s="3">
         <v>2100</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>1100</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>2100</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>5800</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>3500</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-1100</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>5200</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-8300</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>13100</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
       <c r="N14" s="3">
         <v>0</v>
       </c>
@@ -1395,8 +1415,11 @@
       <c r="AG14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1404,32 +1427,32 @@
         <v>5500</v>
       </c>
       <c r="E15" s="3">
+        <v>5500</v>
+      </c>
+      <c r="F15" s="3">
         <v>5400</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>5500</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>5600</v>
-      </c>
-      <c r="H15" s="3">
-        <v>5400</v>
       </c>
       <c r="I15" s="3">
         <v>5400</v>
       </c>
       <c r="J15" s="3">
+        <v>5400</v>
+      </c>
+      <c r="K15" s="3">
         <v>5200</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>4800</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>4600</v>
       </c>
-      <c r="M15" s="3">
-        <v>0</v>
-      </c>
       <c r="N15" s="3">
         <v>0</v>
       </c>
@@ -1490,8 +1513,11 @@
       <c r="AG15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1522,198 +1548,205 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>128600</v>
+      </c>
+      <c r="E17" s="3">
         <v>126800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>130100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>120800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>116700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>111500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>183300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>125500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>122300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>123100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>109000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>107100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>98600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>84700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>114600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>70400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>59000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>200400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>40800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>37300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>26300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>28400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>26400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>18000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>48400</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>13100</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>39800</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>12700</v>
       </c>
-      <c r="AE17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-120200</v>
+      </c>
+      <c r="E18" s="3">
         <v>-119300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-100000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-106500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-104900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-104100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>132900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-108300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-102100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-98900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-89000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-91300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-81900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-76300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-63500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-69600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-59000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-200400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-40800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-37300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-26300</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-28400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-26400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-18000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-48400</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-13100</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-39800</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-12700</v>
       </c>
-      <c r="AE18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1747,198 +1780,205 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E20" s="3">
         <v>-2300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-5500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>2900</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>1900</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-4700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>900</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-5600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>51700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>9600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>10000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>7000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-1300</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>41500</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-17300</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-1200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-54700</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>2900</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-7900</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-2100</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-1400</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-900</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>30600</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-500</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>14600</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-58500</v>
       </c>
-      <c r="AE20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-113500</v>
+      </c>
+      <c r="E21" s="3">
         <v>-111500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-94700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-101200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-93800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-101600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>136300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-98400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-98200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-88700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-33400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-78200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-68500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-65900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-62100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-26400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-74600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-200200</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-94200</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-33200</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-33100</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-29400</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-26700</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-19600</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-15400</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-12900</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-24000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-71100</v>
       </c>
-      <c r="AE21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1969,8 +2009,8 @@
       <c r="L22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
+      <c r="M22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N22" s="3">
         <v>0</v>
@@ -1987,8 +2027,8 @@
       <c r="R22" s="3">
         <v>0</v>
       </c>
-      <c r="S22" s="3" t="s">
-        <v>3</v>
+      <c r="S22" s="3">
+        <v>0</v>
       </c>
       <c r="T22" s="3" t="s">
         <v>3</v>
@@ -2005,14 +2045,14 @@
       <c r="X22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y22" s="3">
-        <v>100</v>
+      <c r="Y22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z22" s="3">
         <v>100</v>
       </c>
-      <c r="AA22" s="3" t="s">
-        <v>3</v>
+      <c r="AA22" s="3">
+        <v>100</v>
       </c>
       <c r="AB22" s="3" t="s">
         <v>3</v>
@@ -2032,142 +2072,148 @@
       <c r="AG22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-102300</v>
+      </c>
+      <c r="E23" s="3">
         <v>-109300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-90400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-96700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-91000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-98700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>144200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-96100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-82800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-96500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-37300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-81700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-72000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-69200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-64700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-28100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-76300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-201600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-95500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-34500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-34200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-30500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-27900</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-19000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-17900</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-13600</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-25200</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-71200</v>
       </c>
-      <c r="AE23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I24" s="3">
+      <c r="E24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F24" s="3">
+        <v>0</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H24" s="3">
+        <v>0</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J24" s="3">
         <v>1400</v>
       </c>
-      <c r="J24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K24" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M24" s="3">
+      <c r="M24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N24" s="3">
         <v>1000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>2400</v>
       </c>
-      <c r="O24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P24" s="3" t="s">
         <v>3</v>
       </c>
@@ -2201,18 +2247,18 @@
       <c r="Z24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AA24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB24" s="3">
         <v>-31500</v>
       </c>
-      <c r="AB24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC24" s="3">
+      <c r="AC24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD24" s="3">
         <v>-96300</v>
       </c>
-      <c r="AD24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE24" s="3" t="s">
         <v>3</v>
       </c>
@@ -2222,8 +2268,11 @@
       <c r="AG24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2317,198 +2366,207 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-102300</v>
+      </c>
+      <c r="E26" s="3">
         <v>-109300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-90400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-96700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-91100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-98700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>142800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-96100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-82800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-96500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-38300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-84100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-72000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-69200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-64700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-28100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-76300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-201600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-95500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-34500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-34200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-30500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-27900</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-19000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-17900</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-13600</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-23800</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-71200</v>
       </c>
-      <c r="AE26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-102300</v>
+      </c>
+      <c r="E27" s="3">
         <v>-109300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-90400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-96700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-91100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-98700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>142800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-96100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-82800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-96500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-38300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-109600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-72000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-69200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-64700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-28100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-76300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-201600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-95500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-34500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-34200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-31700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-31100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-22300</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-52600</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-16600</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-216700</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-70400</v>
       </c>
-      <c r="AE27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2602,8 +2660,11 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2697,8 +2758,11 @@
       <c r="AG29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2792,8 +2856,11 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2887,198 +2954,207 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E32" s="3">
         <v>2300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>5500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-2900</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-1900</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>4700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-900</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>5600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-51700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-9600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-10000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-7000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>1300</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-41500</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>17300</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>1200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>54700</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-2900</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>7900</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>2100</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>1400</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>900</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-30600</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>500</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-14600</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>58500</v>
       </c>
-      <c r="AE32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-102300</v>
+      </c>
+      <c r="E33" s="3">
         <v>-109300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-90400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-96700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-91100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-98700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>142800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-96100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-82800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-96500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-38300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-109600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-72000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-69200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-64700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-28100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-76300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-201600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-95500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-34500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-34200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-31700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-31100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-22300</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-52600</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-16600</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-216700</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-70400</v>
       </c>
-      <c r="AE33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3172,203 +3248,212 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-102300</v>
+      </c>
+      <c r="E35" s="3">
         <v>-109300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-90400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-96700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-91100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-98700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>142800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-96100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-82800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-96500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-38300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-109600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-72000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-69200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-64700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-28100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-76300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-201600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-95500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-34500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-34200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-31700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-31100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-22300</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-52600</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-16600</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-216700</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-70400</v>
       </c>
-      <c r="AE35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43738</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43646</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43555</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43465</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43373</v>
       </c>
-      <c r="AE38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AF38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AG38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3402,8 +3487,9 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3437,86 +3523,87 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>282100</v>
+      </c>
+      <c r="E41" s="3">
         <v>527900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>282000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>230200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>292800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>287800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>435900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>169000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>225500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>249800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>232800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>156500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>265600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>296800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>560000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>612000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>212000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>97200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>162200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>137900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>125300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>126100</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>37200</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>37800</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>37900</v>
       </c>
-      <c r="AB41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3532,86 +3619,89 @@
       <c r="AG41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>868200</v>
+      </c>
+      <c r="E42" s="3">
         <v>692000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>568800</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>695600</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>715400</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>806700</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>754000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>846400</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>847500</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>809700</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>845400</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>938000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>900500</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>925800</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>405700</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>321400</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>403300</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>406200</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>137500</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>64300</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>102600</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>127400</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>54600</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>73100</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>88900</v>
       </c>
-      <c r="AB42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3627,8 +3717,11 @@
       <c r="AG42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3659,8 +3752,8 @@
       <c r="L43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M43" s="3">
-        <v>0</v>
+      <c r="M43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N43" s="3">
         <v>0</v>
@@ -3672,17 +3765,17 @@
         <v>0</v>
       </c>
       <c r="Q43" s="3">
+        <v>0</v>
+      </c>
+      <c r="R43" s="3">
         <v>300000</v>
       </c>
-      <c r="R43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S43" s="3">
+      <c r="S43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T43" s="3">
         <v>50000</v>
       </c>
-      <c r="T43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3698,8 +3791,8 @@
       <c r="Y43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z43" s="3">
-        <v>0</v>
+      <c r="Z43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA43" s="3">
         <v>0</v>
@@ -3722,8 +3815,11 @@
       <c r="AG43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3754,8 +3850,8 @@
       <c r="L44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
+      <c r="M44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N44" s="3">
         <v>0</v>
@@ -3817,8 +3913,11 @@
       <c r="AG44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3849,54 +3948,54 @@
       <c r="L45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M45" s="3">
+      <c r="M45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N45" s="3">
         <v>14800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>14400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>13800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>16900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>7400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>8000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>12700</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>11100</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>8700</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>6500</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>6900</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>6200</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>2700</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>3900</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>2600</v>
       </c>
-      <c r="AB45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3912,86 +4011,89 @@
       <c r="AG45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1175500</v>
+      </c>
+      <c r="E46" s="3">
         <v>1247600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>878100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>945500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1029400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1121700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1211000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1039500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1094800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1083000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1092900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1108900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1179900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1239500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1273000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>941400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>678000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>514600</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>308300</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>208700</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>234800</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>259600</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>94500</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>114800</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>129400</v>
       </c>
-      <c r="AB46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC46" s="3" t="s">
         <v>3</v>
       </c>
@@ -4007,8 +4109,11 @@
       <c r="AG46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4039,8 +4144,8 @@
       <c r="L47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
+      <c r="M47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N47" s="3">
         <v>0</v>
@@ -4051,18 +4156,18 @@
       <c r="P47" s="3">
         <v>0</v>
       </c>
-      <c r="Q47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R47" s="3">
+      <c r="Q47" s="3">
+        <v>0</v>
+      </c>
+      <c r="R47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S47" s="3">
         <v>24500</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>29400</v>
       </c>
-      <c r="T47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U47" s="3" t="s">
         <v>3</v>
       </c>
@@ -4078,8 +4183,8 @@
       <c r="Y47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z47" s="3">
-        <v>0</v>
+      <c r="Z47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA47" s="3">
         <v>0</v>
@@ -4102,86 +4207,89 @@
       <c r="AG47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>208400</v>
+      </c>
+      <c r="E48" s="3">
         <v>211800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>216300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>218200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>224300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>229900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>237800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>239700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>242300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>238000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>234100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>226700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>223500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>199800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>187000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>174700</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>169700</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>158800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>125400</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>51200</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>48600</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>46900</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>43200</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>38000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>36800</v>
       </c>
-      <c r="AB48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC48" s="3" t="s">
         <v>3</v>
       </c>
@@ -4197,8 +4305,11 @@
       <c r="AG48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4292,8 +4403,11 @@
       <c r="AG49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4387,8 +4501,11 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4482,86 +4599,89 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>7300</v>
+      </c>
+      <c r="E52" s="3">
         <v>7500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>9400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>7600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>7500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>8100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>10900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>11300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>16800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>11300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>14700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>14600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>15000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>14100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>14500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>15900</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>16000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>19900</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>18000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>18400</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>16600</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>16100</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>18300</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>17800</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>14400</v>
       </c>
-      <c r="AB52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4577,8 +4697,11 @@
       <c r="AG52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4672,86 +4795,89 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1391200</v>
+      </c>
+      <c r="E54" s="3">
         <v>1466900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1103800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1171400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1261300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1359800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1459700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1290500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1353900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1332400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1341700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1350300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1418400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1453400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1474500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1156600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>893100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>693200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>451700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>278300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>300000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>322600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>156100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>170600</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>180500</v>
       </c>
-      <c r="AB54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4767,8 +4893,11 @@
       <c r="AG54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4802,8 +4931,9 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4837,86 +4967,87 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>10600</v>
+      </c>
+      <c r="E57" s="3">
         <v>7700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>3900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>3800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>4400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>3200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>6900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>14100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>9000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>7000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>7100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>6300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>7500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>7300</v>
-      </c>
-      <c r="S57" s="3">
-        <v>8000</v>
       </c>
       <c r="T57" s="3">
         <v>8000</v>
       </c>
       <c r="U57" s="3">
+        <v>8000</v>
+      </c>
+      <c r="V57" s="3">
         <v>6300</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>6600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>6200</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>6100</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>7800</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>3900</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>4000</v>
       </c>
-      <c r="AB57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4932,67 +5063,70 @@
       <c r="AG57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>12900</v>
+      </c>
+      <c r="E58" s="3">
         <v>13200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>13500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>12900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>12600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>12200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>12800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>13000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>12400</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>12600</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1900</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>2200</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>2400</v>
-      </c>
-      <c r="P58" s="3">
-        <v>2300</v>
       </c>
       <c r="Q58" s="3">
         <v>2300</v>
       </c>
       <c r="R58" s="3">
-        <v>2200</v>
+        <v>2300</v>
       </c>
       <c r="S58" s="3">
         <v>2200</v>
       </c>
       <c r="T58" s="3">
-        <v>2100</v>
+        <v>2200</v>
       </c>
       <c r="U58" s="3">
         <v>2100</v>
       </c>
       <c r="V58" s="3">
-        <v>1700</v>
+        <v>2100</v>
       </c>
       <c r="W58" s="3">
         <v>1700</v>
@@ -5001,17 +5135,17 @@
         <v>1700</v>
       </c>
       <c r="Y58" s="3">
+        <v>1700</v>
+      </c>
+      <c r="Z58" s="3">
         <v>1300</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>800</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>7300</v>
       </c>
-      <c r="AB58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC58" s="3" t="s">
         <v>3</v>
       </c>
@@ -5027,86 +5161,89 @@
       <c r="AG58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>118800</v>
+      </c>
+      <c r="E59" s="3">
         <v>98300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>128600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>124000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>140000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>157800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>156100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>171600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>163800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>172800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>212700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>229600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>202800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>210200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>203700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>91900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>118500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>92000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>93900</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>39100</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>31100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>23700</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>20000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>15300</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>56200</v>
       </c>
-      <c r="AB59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC59" s="3" t="s">
         <v>3</v>
       </c>
@@ -5122,86 +5259,89 @@
       <c r="AG59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>174100</v>
+      </c>
+      <c r="E60" s="3">
         <v>141500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>182100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>166200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>177300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>187200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>205600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>220400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>209500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>219900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>223600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>238900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>212300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>218800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>213400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>101400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>128700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>102100</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>102300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>47500</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>39000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>31400</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>29100</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>19900</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>52200</v>
       </c>
-      <c r="AB60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC60" s="3" t="s">
         <v>3</v>
       </c>
@@ -5217,86 +5357,89 @@
       <c r="AG60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>141900</v>
+      </c>
+      <c r="E61" s="3">
         <v>144900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>148000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>149100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>152600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>155900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>159900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>160900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>164700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>166300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>3000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>3600</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>4200</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>4700</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>5300</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>4400</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>4900</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>5300</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>4400</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>2800</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>300</v>
       </c>
-      <c r="AB61" s="3">
-        <v>0</v>
-      </c>
       <c r="AC61" s="3">
         <v>0</v>
       </c>
@@ -5312,83 +5455,86 @@
       <c r="AG61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>8000</v>
+      </c>
+      <c r="E62" s="3">
         <v>7900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>7000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>6900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>3600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>3000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>5600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>11800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>12900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>383500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>395500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>404100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>403100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>431300</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>197800</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>211600</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>164000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>98500</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>26300</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>25300</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>24500</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>21600</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>21100</v>
       </c>
-      <c r="AA62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB62" s="3" t="s">
         <v>3</v>
       </c>
@@ -5407,8 +5553,11 @@
       <c r="AG62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5502,8 +5651,11 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5597,8 +5749,11 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5692,86 +5847,89 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>344300</v>
+      </c>
+      <c r="E66" s="3">
         <v>343800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>370300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>380100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>407200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>446300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>478400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>511600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>542200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>570800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>608200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>635800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>618200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>624300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>647700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>302700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>344500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>270800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>206100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>78200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>69200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>61200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>55200</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>43800</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>36900</v>
       </c>
-      <c r="AB66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5787,8 +5945,11 @@
       <c r="AG66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5822,8 +5983,9 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5917,8 +6079,11 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6012,8 +6177,11 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6081,17 +6249,17 @@
         <v>0</v>
       </c>
       <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z70" s="3">
         <v>302000</v>
       </c>
-      <c r="Z70" s="3">
+      <c r="AA70" s="3">
         <v>298800</v>
       </c>
-      <c r="AA70" s="3">
+      <c r="AB70" s="3">
         <v>439200</v>
       </c>
-      <c r="AB70" s="3">
-        <v>0</v>
-      </c>
       <c r="AC70" s="3">
         <v>0</v>
       </c>
@@ -6107,8 +6275,11 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6202,86 +6373,89 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1778200</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1675900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1566600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1476300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1379600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-1288600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-1189900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-1332700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-1236600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-1153800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-1057400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-1019000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-909400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-837500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-768300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-703600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-675400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-599200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-397600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-302200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-267700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-233500</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-203000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-175200</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-156200</v>
       </c>
-      <c r="AB72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC72" s="3" t="s">
         <v>3</v>
       </c>
@@ -6297,8 +6471,11 @@
       <c r="AG72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6392,8 +6569,11 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6487,8 +6667,11 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6582,86 +6765,89 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1046800</v>
+      </c>
+      <c r="E76" s="3">
         <v>1123100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>733500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>791300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>854100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>913500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>981300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>778900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>811600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>761500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>733500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>714500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>800200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>829100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>826700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>853800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>548600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>422400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>245600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>200100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>230800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>261400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>-201100</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>-172100</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>-295500</v>
       </c>
-      <c r="AB76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC76" s="3" t="s">
         <v>3</v>
       </c>
@@ -6677,8 +6863,11 @@
       <c r="AG76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6772,203 +6961,212 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43738</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43646</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43555</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43465</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43373</v>
       </c>
-      <c r="AE80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AF80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AG80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-102300</v>
+      </c>
+      <c r="E81" s="3">
         <v>-109300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-90400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-96700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-91100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-98700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>142800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-96100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-82800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-96500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-38300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-109600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-72000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-69200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-64700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-28100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-76300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-201600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-95500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-34500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-34200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-31700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-31100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-22300</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-52600</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-16600</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-216700</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-70400</v>
       </c>
-      <c r="AE81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7002,103 +7200,107 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>5400</v>
+        <v>5600</v>
       </c>
       <c r="E83" s="3">
         <v>5400</v>
       </c>
       <c r="F83" s="3">
+        <v>5400</v>
+      </c>
+      <c r="G83" s="3">
         <v>5200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>4800</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>4600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>3900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>3500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>3400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>3300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>3900</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>3500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>3400</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>3300</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>2600</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>1800</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>1700</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>1400</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>1300</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>1200</v>
-      </c>
-      <c r="W83" s="3">
-        <v>1100</v>
       </c>
       <c r="X83" s="3">
         <v>1100</v>
       </c>
       <c r="Y83" s="3">
+        <v>1100</v>
+      </c>
+      <c r="Z83" s="3">
         <v>1000</v>
-      </c>
-      <c r="Z83" s="3">
-        <v>900</v>
       </c>
       <c r="AA83" s="3">
         <v>900</v>
       </c>
       <c r="AB83" s="3">
+        <v>900</v>
+      </c>
+      <c r="AC83" s="3">
         <v>700</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>500</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>100</v>
       </c>
-      <c r="AE83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF83" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7192,8 +7394,11 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7287,8 +7492,11 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7382,8 +7590,11 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7477,8 +7688,11 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7572,103 +7786,109 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-76500</v>
+      </c>
+      <c r="E89" s="3">
         <v>-103900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-76400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-88100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-83000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-99700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>135100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-89800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-84700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-109800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-69200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-74500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-52300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>218500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>3000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-32500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-38600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-24300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-21200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-22800</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-27400</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-17800</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-17000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>16900</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-25900</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>4200</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-9400</v>
       </c>
-      <c r="AE89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7702,8 +7922,9 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7711,94 +7932,97 @@
         <v>-3100</v>
       </c>
       <c r="E91" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="F91" s="3">
         <v>-3000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-2000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-2400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-3600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-7900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-16200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-6000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-8300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-11800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-21600</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-7300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-13400</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-5800</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-16200</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-11500</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-8100</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-2800</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-2400</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-3000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-2200</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-1400</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-6600</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-2400</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-11200</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-700</v>
       </c>
-      <c r="AE91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF91" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7892,8 +8116,11 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7987,103 +8214,109 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-170400</v>
+      </c>
+      <c r="E94" s="3">
         <v>-125100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>126300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>24700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>87500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-53500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>98100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-10200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-41500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>25500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>113400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-36200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-537300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-77500</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>76100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-13100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-279600</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-81400</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>35200</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>22900</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-76800</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>16600</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-83200</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>2400</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-2400</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>22000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-2200</v>
       </c>
-      <c r="AE94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8117,8 +8350,9 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8149,8 +8383,8 @@
       <c r="L96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -8212,8 +8446,11 @@
       <c r="AG96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8307,8 +8544,11 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8402,8 +8642,11 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8497,103 +8740,109 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E100" s="3">
         <v>473400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>3400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>1300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>2900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>33700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>36800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>107500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>98400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>32000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>1600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>22300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>55700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>21500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>320900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>160400</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>253300</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>130000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>100</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-800</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>193000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>700</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>2700</v>
       </c>
-      <c r="AA100" s="3">
-        <v>0</v>
-      </c>
       <c r="AB100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC100" s="3">
         <v>37900</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>120100</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>9900</v>
       </c>
-      <c r="AE100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8624,8 +8873,8 @@
       <c r="L101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -8687,99 +8936,105 @@
       <c r="AG101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-245800</v>
+      </c>
+      <c r="E102" s="3">
         <v>244400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>53400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-62200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>4600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-150300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>266900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-63200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-18600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>14100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>76300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-109100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-31200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-263200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-54100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>400000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>114800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-64900</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>24300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>14100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-700</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>88800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-500</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-100</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-106500</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>9700</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>105900</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-500</v>
       </c>
-      <c r="AE102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BEAM_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BEAM_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="420" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="428" uniqueCount="92">
   <si>
     <t>BEAM</t>
   </si>
@@ -656,207 +656,210 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="35" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="36" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44012</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43921</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43830</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43738</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43646</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43555</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43465</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43373</v>
       </c>
-      <c r="AG7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AH7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AI7" s="2" t="s">
         <v>3</v>
       </c>
+      <c r="AJ7" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>114100</v>
+      </c>
+      <c r="E8" s="3">
         <v>9700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>8500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>7500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>30100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>14300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>11800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>7400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>316200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>17200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>20100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>24200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>20000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>15800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>16700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>8400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>51100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>800</v>
       </c>
-      <c r="U8" s="3">
-        <v>0</v>
-      </c>
       <c r="V8" s="3">
         <v>0</v>
       </c>
@@ -899,47 +902,50 @@
       <c r="AI8" s="3">
         <v>0</v>
       </c>
+      <c r="AJ8" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>99300</v>
+      </c>
+      <c r="E9" s="3">
         <v>109800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>101800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>98800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>101400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>94300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>87000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>84800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>140100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>100100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>97600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>99600</v>
       </c>
-      <c r="O9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P9" s="3" t="s">
         <v>3</v>
       </c>
@@ -1000,47 +1006,50 @@
       <c r="AI9" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ9" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>14800</v>
+      </c>
+      <c r="E10" s="3">
         <v>-100100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>-93300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>-91300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>-71400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>-80000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>-75300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>-77400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>176100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>-82900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>-77500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>-75400</v>
       </c>
-      <c r="O10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P10" s="3" t="s">
         <v>3</v>
       </c>
@@ -1101,8 +1110,11 @@
       <c r="AI10" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ10" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1138,109 +1150,113 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>113800</v>
+      </c>
+      <c r="E12" s="3">
         <v>109800</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>101800</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>98800</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>101400</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>94300</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>87000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>84800</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>140100</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>100100</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>97600</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>99600</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>86300</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>85300</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>74600</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>65400</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>96800</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>54600</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>45600</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>190100</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>32500</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>29800</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>19400</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>21500</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>20200</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>12500</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>34500</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>9200</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>29600</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>9900</v>
       </c>
-      <c r="AG12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AI12" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ12" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1340,47 +1356,50 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>4100</v>
+      </c>
+      <c r="E14" s="3">
         <v>-5500</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-4400</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>2100</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>1100</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>2100</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>5800</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>3500</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-1100</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>5200</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-8300</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>13100</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
       <c r="P14" s="3">
         <v>0</v>
       </c>
@@ -1441,47 +1460,50 @@
       <c r="AI14" s="3">
         <v>0</v>
       </c>
+      <c r="AJ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>5700</v>
+      </c>
+      <c r="E15" s="3">
         <v>5600</v>
-      </c>
-      <c r="E15" s="3">
-        <v>5500</v>
       </c>
       <c r="F15" s="3">
         <v>5500</v>
       </c>
       <c r="G15" s="3">
+        <v>5500</v>
+      </c>
+      <c r="H15" s="3">
         <v>5400</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>5500</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>5600</v>
-      </c>
-      <c r="J15" s="3">
-        <v>5400</v>
       </c>
       <c r="K15" s="3">
         <v>5400</v>
       </c>
       <c r="L15" s="3">
+        <v>5400</v>
+      </c>
+      <c r="M15" s="3">
         <v>5200</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>4800</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>4600</v>
       </c>
-      <c r="O15" s="3">
-        <v>0</v>
-      </c>
       <c r="P15" s="3">
         <v>0</v>
       </c>
@@ -1542,8 +1564,11 @@
       <c r="AI15" s="3">
         <v>0</v>
       </c>
+      <c r="AJ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1576,210 +1601,217 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>131600</v>
+      </c>
+      <c r="E17" s="3">
         <v>136500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>128600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>126800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>130100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>120800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>116700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>111500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>183300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>125500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>122300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>123100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>109000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>107100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>98600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>84700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>114600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>70400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>59000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>200400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>40800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>37300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>26300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>28400</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>26400</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>18000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>48400</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>13100</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>39800</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>12700</v>
       </c>
-      <c r="AG17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AI17" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ17" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-17400</v>
+      </c>
+      <c r="E18" s="3">
         <v>-126800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-120200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-119300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-100000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-106500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-104900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-104100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>132900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-108300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-102100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-98900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-89000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-91300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-81900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-76300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-63500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-69600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-59000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-200400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-40800</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-37300</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-26300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-28400</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-26400</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-18000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-48400</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-13100</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-39800</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-12700</v>
       </c>
-      <c r="AG18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AI18" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ18" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1815,210 +1847,217 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-255200</v>
+      </c>
+      <c r="E20" s="3">
         <v>-8500</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-1100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-2300</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-5500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>2900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>1900</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-4700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>900</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-5600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>51700</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>9600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>10000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>7000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-1300</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>41500</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-17300</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-1200</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-54700</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>2900</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-7900</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-2100</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-1400</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-900</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>30600</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-500</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>14600</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-58500</v>
       </c>
-      <c r="AG20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AI20" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ20" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>243400</v>
+      </c>
+      <c r="E21" s="3">
         <v>-112700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-113500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-111500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-94700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-101200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-93800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-101600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>136300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-98400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-98200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-88700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-33400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-78200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-68500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-65900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-62100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-26400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-74600</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-200200</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-94200</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-33200</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-33100</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-29400</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-26700</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-19600</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-15400</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-12900</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>-24000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>-71100</v>
       </c>
-      <c r="AG21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AI21" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ21" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2055,8 +2094,8 @@
       <c r="N22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
+      <c r="O22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P22" s="3">
         <v>0</v>
@@ -2073,8 +2112,8 @@
       <c r="T22" s="3">
         <v>0</v>
       </c>
-      <c r="U22" s="3" t="s">
-        <v>3</v>
+      <c r="U22" s="3">
+        <v>0</v>
       </c>
       <c r="V22" s="3" t="s">
         <v>3</v>
@@ -2091,14 +2130,14 @@
       <c r="Z22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA22" s="3">
-        <v>100</v>
+      <c r="AA22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB22" s="3">
         <v>100</v>
       </c>
-      <c r="AC22" s="3" t="s">
-        <v>3</v>
+      <c r="AC22" s="3">
+        <v>100</v>
       </c>
       <c r="AD22" s="3" t="s">
         <v>3</v>
@@ -2118,109 +2157,115 @@
       <c r="AI22" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ22" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>244300</v>
+      </c>
+      <c r="E23" s="3">
         <v>-112700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-102300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-109300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-90400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-96700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-91000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-98700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>144200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-96100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-82800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-96500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-37300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-81700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-72000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-69200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-64700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-28100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-76300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-201600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-95500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-34500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-34200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-30500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-27900</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-19000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-17900</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-13600</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-25200</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-71200</v>
       </c>
-      <c r="AG23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AI23" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ23" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2233,39 +2278,39 @@
       <c r="F24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K24" s="3">
+      <c r="G24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H24" s="3">
+        <v>0</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J24" s="3">
+        <v>0</v>
+      </c>
+      <c r="K24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L24" s="3">
         <v>1400</v>
       </c>
-      <c r="L24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M24" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O24" s="3">
+      <c r="O24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P24" s="3">
         <v>1000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>2400</v>
       </c>
-      <c r="Q24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R24" s="3" t="s">
         <v>3</v>
       </c>
@@ -2299,18 +2344,18 @@
       <c r="AB24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AC24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD24" s="3">
         <v>-31500</v>
       </c>
-      <c r="AD24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AE24" s="3">
+      <c r="AE24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF24" s="3">
         <v>-96300</v>
       </c>
-      <c r="AF24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG24" s="3" t="s">
         <v>3</v>
       </c>
@@ -2320,8 +2365,11 @@
       <c r="AI24" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ24" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2421,210 +2469,219 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>244300</v>
+      </c>
+      <c r="E26" s="3">
         <v>-112700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-102300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-109300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-90400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-96700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-91100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-98700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>142800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-96100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-82800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-96500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-38300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-84100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-72000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-69200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-64700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-28100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-76300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-201600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-95500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-34500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-34200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-30500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-27900</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-19000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-17900</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-13600</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-23800</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-71200</v>
       </c>
-      <c r="AG26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AI26" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ26" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>244300</v>
+      </c>
+      <c r="E27" s="3">
         <v>-112700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-102300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-109300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-90400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-96700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-91100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-98700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>142800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-96100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-82800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-96500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-38300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-109600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-72000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-69200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-64700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-28100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-76300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-201600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-95500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-34500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-34200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-31700</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-31100</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-22300</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-52600</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-16600</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-216700</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-70400</v>
       </c>
-      <c r="AG27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AI27" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ27" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2724,8 +2781,11 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2825,8 +2885,11 @@
       <c r="AI29" s="3">
         <v>0</v>
       </c>
+      <c r="AJ29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2926,8 +2989,11 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3027,210 +3093,219 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>255200</v>
+      </c>
+      <c r="E32" s="3">
         <v>8500</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>1100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>2300</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>5500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-2900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-1900</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>4700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-900</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>5600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-51700</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-9600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-10000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-7000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>1300</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-41500</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>17300</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>1200</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>54700</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-2900</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>7900</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>2100</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>1400</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>900</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-30600</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>500</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-14600</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>58500</v>
       </c>
-      <c r="AG32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AI32" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ32" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>244300</v>
+      </c>
+      <c r="E33" s="3">
         <v>-112700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-102300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-109300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-90400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-96700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-91100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-98700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>142800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-96100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-82800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-96500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-38300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-109600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-72000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-69200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-64700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-28100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-76300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-201600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-95500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-34500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-34200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-31700</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-31100</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-22300</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-52600</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-16600</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-216700</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-70400</v>
       </c>
-      <c r="AG33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AI33" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ33" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3330,215 +3405,224 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>244300</v>
+      </c>
+      <c r="E35" s="3">
         <v>-112700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-102300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-109300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-90400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-96700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-91100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-98700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>142800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-96100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-82800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-96500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-38300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-109600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-72000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-69200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-64700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-28100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-76300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-201600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-95500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-34500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-34200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-31700</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-31100</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-22300</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-52600</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-16600</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-216700</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-70400</v>
       </c>
-      <c r="AG35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AI35" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ35" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44012</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43921</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43830</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43738</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43646</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43555</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43465</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43373</v>
       </c>
-      <c r="AG38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AH38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AI38" s="2" t="s">
         <v>3</v>
       </c>
+      <c r="AJ38" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3574,8 +3658,9 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3611,92 +3696,93 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>294900</v>
+      </c>
+      <c r="E41" s="3">
         <v>268000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>282100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>527900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>282000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>230200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>292800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>287800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>435900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>169000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>225500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>249800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>232800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>156500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>265600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>296800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>560000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>612000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>212000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>97200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>162200</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>137900</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>125300</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>126100</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>37200</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>37800</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>37900</v>
       </c>
-      <c r="AD41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3712,92 +3798,95 @@
       <c r="AI41" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ41" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>950300</v>
+      </c>
+      <c r="E42" s="3">
         <v>807000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>868200</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>692000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>568800</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>695600</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>715400</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>806700</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>754000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>846400</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>847500</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>809700</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>845400</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>938000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>900500</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>925800</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>405700</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>321400</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>403300</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>406200</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>137500</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>64300</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>102600</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>127400</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>54600</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>73100</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>88900</v>
       </c>
-      <c r="AD42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3813,8 +3902,11 @@
       <c r="AI42" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ42" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3851,8 +3943,8 @@
       <c r="N43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O43" s="3">
-        <v>0</v>
+      <c r="O43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P43" s="3">
         <v>0</v>
@@ -3864,17 +3956,17 @@
         <v>0</v>
       </c>
       <c r="S43" s="3">
+        <v>0</v>
+      </c>
+      <c r="T43" s="3">
         <v>300000</v>
       </c>
-      <c r="T43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U43" s="3">
+      <c r="U43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V43" s="3">
         <v>50000</v>
       </c>
-      <c r="V43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3890,8 +3982,8 @@
       <c r="AA43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB43" s="3">
-        <v>0</v>
+      <c r="AB43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC43" s="3">
         <v>0</v>
@@ -3914,8 +4006,11 @@
       <c r="AI43" s="3">
         <v>0</v>
       </c>
+      <c r="AJ43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3952,8 +4047,8 @@
       <c r="N44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
+      <c r="O44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P44" s="3">
         <v>0</v>
@@ -4015,8 +4110,11 @@
       <c r="AI44" s="3">
         <v>0</v>
       </c>
+      <c r="AJ44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4053,54 +4151,54 @@
       <c r="N45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O45" s="3">
+      <c r="O45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P45" s="3">
         <v>14800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>14400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>13800</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>16900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>7400</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>8000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>12700</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>11100</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>8700</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>6500</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>6900</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>6200</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>2700</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>3900</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>2600</v>
       </c>
-      <c r="AD45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE45" s="3" t="s">
         <v>3</v>
       </c>
@@ -4116,92 +4214,95 @@
       <c r="AI45" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ45" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1268700</v>
+      </c>
+      <c r="E46" s="3">
         <v>1098500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1175500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1247600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>878100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>945500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1029400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1121700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1211000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1039500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1094800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1083000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1092900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1108900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1179900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1239500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1273000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>941400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>678000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>514600</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>308300</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>208700</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>234800</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>259600</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>94500</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>114800</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>129400</v>
       </c>
-      <c r="AD46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE46" s="3" t="s">
         <v>3</v>
       </c>
@@ -4217,8 +4318,11 @@
       <c r="AI46" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ46" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4255,8 +4359,8 @@
       <c r="N47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
+      <c r="O47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P47" s="3">
         <v>0</v>
@@ -4267,18 +4371,18 @@
       <c r="R47" s="3">
         <v>0</v>
       </c>
-      <c r="S47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T47" s="3">
+      <c r="S47" s="3">
+        <v>0</v>
+      </c>
+      <c r="T47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U47" s="3">
         <v>24500</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>29400</v>
       </c>
-      <c r="V47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W47" s="3" t="s">
         <v>3</v>
       </c>
@@ -4294,8 +4398,8 @@
       <c r="AA47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB47" s="3">
-        <v>0</v>
+      <c r="AB47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC47" s="3">
         <v>0</v>
@@ -4318,92 +4422,95 @@
       <c r="AI47" s="3">
         <v>0</v>
       </c>
+      <c r="AJ47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>205200</v>
+      </c>
+      <c r="E48" s="3">
         <v>205300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>208400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>211800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>216300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>218200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>224300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>229900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>237800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>239700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>242300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>238000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>234100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>226700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>223500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>199800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>187000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>174700</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>169700</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>158800</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>125400</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>51200</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>48600</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>46900</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>43200</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>38000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>36800</v>
       </c>
-      <c r="AD48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE48" s="3" t="s">
         <v>3</v>
       </c>
@@ -4419,8 +4526,11 @@
       <c r="AI48" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ48" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4520,8 +4630,11 @@
       <c r="AI49" s="3">
         <v>0</v>
       </c>
+      <c r="AJ49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4621,8 +4734,11 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4722,92 +4838,95 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>7300</v>
+      </c>
+      <c r="E52" s="3">
         <v>7200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>7300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>7500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>9400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>7600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>7500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>8100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>10900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>11300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>16800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>11300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>14700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>14600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>15000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>14100</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>14500</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>15900</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>16000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>19900</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>18000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>18400</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>16600</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>16100</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>18300</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>17800</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>14400</v>
       </c>
-      <c r="AD52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4823,8 +4942,11 @@
       <c r="AI52" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ52" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4924,92 +5046,95 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1481200</v>
+      </c>
+      <c r="E54" s="3">
         <v>1311100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1391200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1466900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1103800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1171400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1261300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1359800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1459700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1290500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1353900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1332400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1341700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1350300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1418400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1453400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1474500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1156600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>893100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>693200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>451700</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>278300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>300000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>322600</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>156100</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>170600</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>180500</v>
       </c>
-      <c r="AD54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE54" s="3" t="s">
         <v>3</v>
       </c>
@@ -5025,8 +5150,11 @@
       <c r="AI54" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ54" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5062,8 +5190,9 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5099,92 +5228,93 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>10200</v>
+      </c>
+      <c r="E57" s="3">
         <v>9500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>10600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>7700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>3900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>3800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>4400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>3200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>6900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>14100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>9000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>7000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>7100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>6300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>7500</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>7300</v>
-      </c>
-      <c r="U57" s="3">
-        <v>8000</v>
       </c>
       <c r="V57" s="3">
         <v>8000</v>
       </c>
       <c r="W57" s="3">
+        <v>8000</v>
+      </c>
+      <c r="X57" s="3">
         <v>6300</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>6600</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>6200</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>6100</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>7800</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>3900</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>4000</v>
       </c>
-      <c r="AD57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE57" s="3" t="s">
         <v>3</v>
       </c>
@@ -5200,73 +5330,76 @@
       <c r="AI57" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ57" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>14400</v>
+      </c>
+      <c r="E58" s="3">
         <v>12700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>12900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>13200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>13500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>12900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>12600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>12200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>12800</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>13000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>12400</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>12600</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1900</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>2200</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>2400</v>
-      </c>
-      <c r="R58" s="3">
-        <v>2300</v>
       </c>
       <c r="S58" s="3">
         <v>2300</v>
       </c>
       <c r="T58" s="3">
-        <v>2200</v>
+        <v>2300</v>
       </c>
       <c r="U58" s="3">
         <v>2200</v>
       </c>
       <c r="V58" s="3">
-        <v>2100</v>
+        <v>2200</v>
       </c>
       <c r="W58" s="3">
         <v>2100</v>
       </c>
       <c r="X58" s="3">
-        <v>1700</v>
+        <v>2100</v>
       </c>
       <c r="Y58" s="3">
         <v>1700</v>
@@ -5275,17 +5408,17 @@
         <v>1700</v>
       </c>
       <c r="AA58" s="3">
+        <v>1700</v>
+      </c>
+      <c r="AB58" s="3">
         <v>1300</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>800</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>7300</v>
       </c>
-      <c r="AD58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE58" s="3" t="s">
         <v>3</v>
       </c>
@@ -5301,92 +5434,95 @@
       <c r="AI58" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ58" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>22700</v>
+      </c>
+      <c r="E59" s="3">
         <v>124000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>118800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>98300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>128600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>124000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>140000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>157800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>156100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>171600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>163800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>172800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>212700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>229600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>202800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>210200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>203700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>91900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>118500</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>92000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>93900</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>39100</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>31100</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>23700</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>20000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>15300</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>56200</v>
       </c>
-      <c r="AD59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE59" s="3" t="s">
         <v>3</v>
       </c>
@@ -5402,92 +5538,95 @@
       <c r="AI59" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ59" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>96900</v>
+      </c>
+      <c r="E60" s="3">
         <v>182600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>174100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>141500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>182100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>166200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>177300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>187200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>205600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>220400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>209500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>219900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>223600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>238900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>212300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>218800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>213400</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>101400</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>128700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>102100</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>102300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>47500</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>39000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>31400</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>29100</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>19900</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>52200</v>
       </c>
-      <c r="AD60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE60" s="3" t="s">
         <v>3</v>
       </c>
@@ -5503,92 +5642,95 @@
       <c r="AI60" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ60" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>139800</v>
+      </c>
+      <c r="E61" s="3">
         <v>138700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>141900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>144900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>148000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>149100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>152600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>155900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>159900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>160900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>164700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>166300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1800</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>2400</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>3000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>3600</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>4200</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>4700</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>5300</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>4400</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>4900</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>5300</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>4400</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>2800</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>300</v>
       </c>
-      <c r="AD61" s="3">
-        <v>0</v>
-      </c>
       <c r="AE61" s="3">
         <v>0</v>
       </c>
@@ -5604,89 +5746,92 @@
       <c r="AI61" s="3">
         <v>0</v>
       </c>
+      <c r="AJ61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>6100</v>
+      </c>
+      <c r="E62" s="3">
         <v>13600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>8000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>7900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>7000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>6900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>3600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>3000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>5600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>11800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>12900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>383500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>395500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>404100</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>403100</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>431300</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>197800</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>211600</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>164000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>98500</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>26300</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>25300</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>24500</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>21600</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>21100</v>
       </c>
-      <c r="AC62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD62" s="3" t="s">
         <v>3</v>
       </c>
@@ -5705,8 +5850,11 @@
       <c r="AI62" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ62" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5806,8 +5954,11 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5907,8 +6058,11 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6008,92 +6162,95 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>242800</v>
+      </c>
+      <c r="E66" s="3">
         <v>345100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>344300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>343800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>370300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>380100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>407200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>446300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>478400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>511600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>542200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>570800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>608200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>635800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>618200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>624300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>647700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>302700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>344500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>270800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>206100</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>78200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>69200</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>61200</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>55200</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>43800</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>36900</v>
       </c>
-      <c r="AD66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE66" s="3" t="s">
         <v>3</v>
       </c>
@@ -6109,8 +6266,11 @@
       <c r="AI66" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ66" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6146,8 +6306,9 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6247,8 +6408,11 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6348,8 +6512,11 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6423,17 +6590,17 @@
         <v>0</v>
       </c>
       <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB70" s="3">
         <v>302000</v>
       </c>
-      <c r="AB70" s="3">
+      <c r="AC70" s="3">
         <v>298800</v>
       </c>
-      <c r="AC70" s="3">
+      <c r="AD70" s="3">
         <v>439200</v>
       </c>
-      <c r="AD70" s="3">
-        <v>0</v>
-      </c>
       <c r="AE70" s="3">
         <v>0</v>
       </c>
@@ -6449,8 +6616,11 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6550,92 +6720,95 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1641200</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1890900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1778200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1675900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1566600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-1476300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-1379600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-1288600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-1189900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-1332700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-1236600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-1153800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-1057400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-1019000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-909400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-837500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-768300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-703600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-675400</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-599200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-397600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-302200</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-267700</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-233500</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-203000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-175200</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-156200</v>
       </c>
-      <c r="AD72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE72" s="3" t="s">
         <v>3</v>
       </c>
@@ -6651,8 +6824,11 @@
       <c r="AI72" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ72" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6752,8 +6928,11 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6853,8 +7032,11 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6954,92 +7136,95 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1238400</v>
+      </c>
+      <c r="E76" s="3">
         <v>966000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1046800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1123100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>733500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>791300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>854100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>913500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>981300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>778900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>811600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>761500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>733500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>714500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>800200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>829100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>826700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>853800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>548600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>422400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>245600</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>200100</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>230800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>261400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>-201100</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>-172100</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>-295500</v>
       </c>
-      <c r="AD76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE76" s="3" t="s">
         <v>3</v>
       </c>
@@ -7055,8 +7240,11 @@
       <c r="AI76" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ76" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7156,215 +7344,224 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44012</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43921</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43830</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43738</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43646</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43555</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43465</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43373</v>
       </c>
-      <c r="AG80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AH80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AI80" s="2" t="s">
         <v>3</v>
       </c>
+      <c r="AJ80" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>244300</v>
+      </c>
+      <c r="E81" s="3">
         <v>-112700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-102300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-109300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-90400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-96700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-91100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-98700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>142800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-96100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-82800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-96500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-38300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-109600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-72000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-69200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-64700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-28100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-76300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-201600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-95500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-34500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-34200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-31700</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-31100</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-22300</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-52600</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-16600</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-216700</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-70400</v>
       </c>
-      <c r="AG81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AI81" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ81" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7400,109 +7597,113 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>5400</v>
+      </c>
+      <c r="E83" s="3">
         <v>5500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>5600</v>
-      </c>
-      <c r="F83" s="3">
-        <v>5400</v>
       </c>
       <c r="G83" s="3">
         <v>5400</v>
       </c>
       <c r="H83" s="3">
+        <v>5400</v>
+      </c>
+      <c r="I83" s="3">
         <v>5200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>4800</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>4600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>3900</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>3500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>3400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>3300</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>3900</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>3500</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>3400</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>3300</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>2600</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>1800</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>1700</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>1400</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>1300</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>1200</v>
-      </c>
-      <c r="Y83" s="3">
-        <v>1100</v>
       </c>
       <c r="Z83" s="3">
         <v>1100</v>
       </c>
       <c r="AA83" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AB83" s="3">
         <v>1000</v>
-      </c>
-      <c r="AB83" s="3">
-        <v>900</v>
       </c>
       <c r="AC83" s="3">
         <v>900</v>
       </c>
       <c r="AD83" s="3">
+        <v>900</v>
+      </c>
+      <c r="AE83" s="3">
         <v>700</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>500</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>100</v>
       </c>
-      <c r="AG83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH83" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AI83" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ83" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7602,8 +7803,11 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7703,8 +7907,11 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7804,8 +8011,11 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7905,8 +8115,11 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8006,109 +8219,115 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-83300</v>
+      </c>
+      <c r="E89" s="3">
         <v>-81500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-76500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-103900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-76400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-88100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-83000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-99700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>135100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-89800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-84700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-109800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-69200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-74500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-52300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>218500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>3000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-32500</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-38600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-24300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-21200</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-22800</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-27400</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-17800</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-17000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>16900</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-25900</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>4200</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-9400</v>
       </c>
-      <c r="AG89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AI89" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ89" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8144,109 +8363,113 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-5000</v>
-      </c>
-      <c r="E91" s="3">
-        <v>-3100</v>
       </c>
       <c r="F91" s="3">
         <v>-3100</v>
       </c>
       <c r="G91" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="H91" s="3">
         <v>-3000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-2000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-2400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-3600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-7900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-16200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-6000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-8300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-11800</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-21600</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-7300</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-13400</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-5800</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-16200</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-11500</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-8100</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-2800</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-2400</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-3000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-2200</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-1400</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-6600</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-2400</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-11200</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-700</v>
       </c>
-      <c r="AG91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH91" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AI91" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ91" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8346,8 +8569,11 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8447,109 +8673,115 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>108400</v>
+      </c>
+      <c r="E94" s="3">
         <v>65700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-170400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-125100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>126300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>24700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>87500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-53500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>98100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-10200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-41500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>25500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>113400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-36200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-537300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-77500</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>76100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-13100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-279600</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-81400</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>35200</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>22900</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-76800</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>16600</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-83200</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>2400</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-2400</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>22000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-2200</v>
       </c>
-      <c r="AG94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AI94" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ94" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8585,8 +8817,9 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8623,8 +8856,8 @@
       <c r="N96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
@@ -8686,8 +8919,11 @@
       <c r="AI96" s="3">
         <v>0</v>
       </c>
+      <c r="AJ96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8787,8 +9023,11 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8888,8 +9127,11 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8989,109 +9231,115 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E100" s="3">
         <v>1700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>1100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>473400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>3400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>1300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>2900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>33700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>36800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>107500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>98400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>32000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>1600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>22300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>55700</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>21500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>320900</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>160400</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>253300</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>130000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>100</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-800</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>193000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>700</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>2700</v>
       </c>
-      <c r="AC100" s="3">
-        <v>0</v>
-      </c>
       <c r="AD100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE100" s="3">
         <v>37900</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>120100</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>9900</v>
       </c>
-      <c r="AG100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AI100" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ100" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9128,8 +9376,8 @@
       <c r="N101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
+      <c r="O101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P101" s="3">
         <v>0</v>
@@ -9191,105 +9439,111 @@
       <c r="AI101" s="3">
         <v>0</v>
       </c>
+      <c r="AJ101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>27000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-14100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-245800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>244400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>53400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-62200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>4600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-150300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>266900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-63200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-18600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>14100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>76300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-109100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-31200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-263200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-54100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>400000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>114800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-64900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>24300</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>14100</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-700</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>88800</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-500</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-100</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-106500</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>9700</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>105900</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-500</v>
       </c>
-      <c r="AG102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AI102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AJ102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BEAM_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BEAM_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="428" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="92">
   <si>
     <t>BEAM</t>
   </si>
@@ -656,213 +656,217 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AJ102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="36" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="37" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44104</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44012</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43921</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43830</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43738</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43646</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43555</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43465</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43373</v>
       </c>
-      <c r="AH7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AI7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AJ7" s="2" t="s">
         <v>3</v>
       </c>
+      <c r="AK7" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>31700</v>
+      </c>
+      <c r="E8" s="3">
         <v>114100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>9700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>8500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>7500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>30100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>14300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>11800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>7400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>316200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>17200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>20100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>24200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>20000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>15800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>16700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>8400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>51100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>800</v>
       </c>
-      <c r="V8" s="3">
-        <v>0</v>
-      </c>
       <c r="W8" s="3">
         <v>0</v>
       </c>
@@ -905,50 +909,53 @@
       <c r="AJ8" s="3">
         <v>0</v>
       </c>
+      <c r="AK8" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>11100</v>
+      </c>
+      <c r="E9" s="3">
         <v>99300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>109800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>101800</v>
       </c>
-      <c r="G9" s="3">
-        <v>98800</v>
-      </c>
       <c r="H9" s="3">
+        <v>15700</v>
+      </c>
+      <c r="I9" s="3">
         <v>101400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>94300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>87000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>84800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>140100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>100100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>97600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>99600</v>
       </c>
-      <c r="P9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q9" s="3" t="s">
         <v>3</v>
       </c>
@@ -1009,50 +1016,53 @@
       <c r="AJ9" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK9" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>20700</v>
+      </c>
+      <c r="E10" s="3">
         <v>14800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>-100100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>-93300</v>
       </c>
-      <c r="G10" s="3">
-        <v>-91300</v>
-      </c>
       <c r="H10" s="3">
+        <v>-8300</v>
+      </c>
+      <c r="I10" s="3">
         <v>-71400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>-80000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>-75300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>-77400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>176100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>-82900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>-77500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>-75400</v>
       </c>
-      <c r="P10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q10" s="3" t="s">
         <v>3</v>
       </c>
@@ -1113,8 +1123,11 @@
       <c r="AJ10" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK10" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1151,112 +1164,116 @@
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>93500</v>
+      </c>
+      <c r="E12" s="3">
         <v>113800</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>109800</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>101800</v>
       </c>
-      <c r="G12" s="3">
-        <v>98800</v>
-      </c>
       <c r="H12" s="3">
+        <v>83100</v>
+      </c>
+      <c r="I12" s="3">
         <v>101400</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>94300</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>87000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>84800</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>140100</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>100100</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>97600</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>99600</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>86300</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>85300</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>74600</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>65400</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>96800</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>54600</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>45600</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>190100</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>32500</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>29800</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>19400</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>21500</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>20200</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>12500</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>34500</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>9200</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>29600</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>9900</v>
       </c>
-      <c r="AH12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AI12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AJ12" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK12" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1359,50 +1376,53 @@
       <c r="AJ13" s="3">
         <v>0</v>
       </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E14" s="3">
         <v>4100</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-5500</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-4400</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>2100</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>1100</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>2100</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>5800</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>3500</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-1100</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>5200</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-8300</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>13100</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
       <c r="Q14" s="3">
         <v>0</v>
       </c>
@@ -1463,50 +1483,53 @@
       <c r="AJ14" s="3">
         <v>0</v>
       </c>
+      <c r="AK14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>5600</v>
+      </c>
+      <c r="E15" s="3">
         <v>5700</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>5600</v>
-      </c>
-      <c r="F15" s="3">
-        <v>5500</v>
       </c>
       <c r="G15" s="3">
         <v>5500</v>
       </c>
       <c r="H15" s="3">
+        <v>5500</v>
+      </c>
+      <c r="I15" s="3">
         <v>5400</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>5500</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>5600</v>
-      </c>
-      <c r="K15" s="3">
-        <v>5400</v>
       </c>
       <c r="L15" s="3">
         <v>5400</v>
       </c>
       <c r="M15" s="3">
+        <v>5400</v>
+      </c>
+      <c r="N15" s="3">
         <v>5200</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>4800</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>4600</v>
       </c>
-      <c r="P15" s="3">
-        <v>0</v>
-      </c>
       <c r="Q15" s="3">
         <v>0</v>
       </c>
@@ -1567,8 +1590,11 @@
       <c r="AJ15" s="3">
         <v>0</v>
       </c>
+      <c r="AK15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1602,216 +1628,223 @@
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>139000</v>
+      </c>
+      <c r="E17" s="3">
         <v>131600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>136500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>128600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>126800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>130100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>120800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>116700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>111500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>183300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>125500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>122300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>123100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>109000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>107100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>98600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>84700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>114600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>70400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>59000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>200400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>40800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>37300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>26300</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>28400</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>26400</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>18000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>48400</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>13100</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>39800</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>12700</v>
       </c>
-      <c r="AH17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AI17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AJ17" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK17" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-107200</v>
+      </c>
+      <c r="E18" s="3">
         <v>-17400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-126800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-120200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-119300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-100000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-106500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-104900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-104100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>132900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-108300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-102100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-98900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-89000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-91300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-81900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-76300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-63500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-69600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-59000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-200400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-40800</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-37300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-26300</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-28400</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-26400</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-18000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-48400</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-13100</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-39800</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-12700</v>
       </c>
-      <c r="AH18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AI18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AJ18" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK18" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1848,216 +1881,223 @@
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="E20" s="3">
         <v>-255200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-8500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-1100</v>
       </c>
-      <c r="G20" s="3">
-        <v>-2300</v>
-      </c>
       <c r="H20" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="I20" s="3">
         <v>100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-5500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>2900</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>1900</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-4700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>900</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-5600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>51700</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>9600</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>10000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>7000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-1300</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>41500</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-17300</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-1200</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-54700</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>2900</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-7900</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-2100</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-1400</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-900</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>30600</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-500</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>14600</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-58500</v>
       </c>
-      <c r="AH20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AI20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AJ20" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK20" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-99100</v>
+      </c>
+      <c r="E21" s="3">
         <v>243400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-112700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-113500</v>
       </c>
-      <c r="G21" s="3">
-        <v>-111500</v>
-      </c>
       <c r="H21" s="3">
+        <v>-110600</v>
+      </c>
+      <c r="I21" s="3">
         <v>-94700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-101200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-93800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-101600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>136300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-98400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-98200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-88700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-33400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-78200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-68500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-65900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-62100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-26400</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-74600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-200200</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-94200</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-33200</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-33100</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-29400</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-26700</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-19600</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-15400</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>-12900</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>-24000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>-71100</v>
       </c>
-      <c r="AH21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AI21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AJ21" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK21" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2097,8 +2137,8 @@
       <c r="O22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P22" s="3">
-        <v>0</v>
+      <c r="P22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q22" s="3">
         <v>0</v>
@@ -2115,8 +2155,8 @@
       <c r="U22" s="3">
         <v>0</v>
       </c>
-      <c r="V22" s="3" t="s">
-        <v>3</v>
+      <c r="V22" s="3">
+        <v>0</v>
       </c>
       <c r="W22" s="3" t="s">
         <v>3</v>
@@ -2133,14 +2173,14 @@
       <c r="AA22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB22" s="3">
-        <v>100</v>
+      <c r="AB22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC22" s="3">
         <v>100</v>
       </c>
-      <c r="AD22" s="3" t="s">
-        <v>3</v>
+      <c r="AD22" s="3">
+        <v>100</v>
       </c>
       <c r="AE22" s="3" t="s">
         <v>3</v>
@@ -2160,112 +2200,118 @@
       <c r="AJ22" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK22" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-94300</v>
+      </c>
+      <c r="E23" s="3">
         <v>244300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-112700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-102300</v>
       </c>
-      <c r="G23" s="3">
-        <v>-109300</v>
-      </c>
       <c r="H23" s="3">
+        <v>-108300</v>
+      </c>
+      <c r="I23" s="3">
         <v>-90400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-96700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-91000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-98700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>144200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-96100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-82800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-96500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-37300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-81700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-72000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-69200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-64700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-28100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-76300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-201600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-95500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-34500</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-34200</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-30500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-27900</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-19000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-17900</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-13600</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-25200</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-71200</v>
       </c>
-      <c r="AH23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AI23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AJ23" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK23" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2281,39 +2327,39 @@
       <c r="G24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J24" s="3">
-        <v>0</v>
-      </c>
-      <c r="K24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L24" s="3">
+      <c r="H24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I24" s="3">
+        <v>0</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K24" s="3">
+        <v>0</v>
+      </c>
+      <c r="L24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M24" s="3">
         <v>1400</v>
       </c>
-      <c r="M24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N24" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P24" s="3">
+      <c r="P24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q24" s="3">
         <v>1000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>2400</v>
       </c>
-      <c r="R24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S24" s="3" t="s">
         <v>3</v>
       </c>
@@ -2347,18 +2393,18 @@
       <c r="AC24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AD24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE24" s="3">
         <v>-31500</v>
       </c>
-      <c r="AE24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AF24" s="3">
+      <c r="AF24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG24" s="3">
         <v>-96300</v>
       </c>
-      <c r="AG24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH24" s="3" t="s">
         <v>3</v>
       </c>
@@ -2368,8 +2414,11 @@
       <c r="AJ24" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK24" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2472,216 +2521,225 @@
       <c r="AJ25" s="3">
         <v>0</v>
       </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-94300</v>
+      </c>
+      <c r="E26" s="3">
         <v>244300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-112700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-102300</v>
       </c>
-      <c r="G26" s="3">
-        <v>-109300</v>
-      </c>
       <c r="H26" s="3">
+        <v>-108300</v>
+      </c>
+      <c r="I26" s="3">
         <v>-90400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-96700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-91100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-98700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>142800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-96100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-82800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-96500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-38300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-84100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-72000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-69200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-64700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-28100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-76300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-201600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-95500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-34500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-34200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-30500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-27900</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-19000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-17900</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-13600</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-23800</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-71200</v>
       </c>
-      <c r="AH26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AI26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AJ26" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK26" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-94300</v>
+      </c>
+      <c r="E27" s="3">
         <v>244300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-112700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-102300</v>
       </c>
-      <c r="G27" s="3">
-        <v>-109300</v>
-      </c>
       <c r="H27" s="3">
+        <v>-108300</v>
+      </c>
+      <c r="I27" s="3">
         <v>-90400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-96700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-91100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-98700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>142800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-96100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-82800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-96500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-38300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-109600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-72000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-69200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-64700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-28100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-76300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-201600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-95500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-34500</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-34200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-31700</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-31100</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-22300</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-52600</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-16600</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-216700</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-70400</v>
       </c>
-      <c r="AH27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AI27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AJ27" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK27" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2784,8 +2842,11 @@
       <c r="AJ28" s="3">
         <v>0</v>
       </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2888,8 +2949,11 @@
       <c r="AJ29" s="3">
         <v>0</v>
       </c>
+      <c r="AK29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2992,8 +3056,11 @@
       <c r="AJ30" s="3">
         <v>0</v>
       </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3096,216 +3163,225 @@
       <c r="AJ31" s="3">
         <v>0</v>
       </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E32" s="3">
         <v>255200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>8500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>1100</v>
       </c>
-      <c r="G32" s="3">
-        <v>2300</v>
-      </c>
       <c r="H32" s="3">
+        <v>3200</v>
+      </c>
+      <c r="I32" s="3">
         <v>-100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>5500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-2900</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-1900</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>4700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-900</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>5600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-51700</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-9600</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-10000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-7000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>1300</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-41500</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>17300</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>1200</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>54700</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-2900</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>7900</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>2100</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>1400</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>900</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-30600</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>500</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-14600</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>58500</v>
       </c>
-      <c r="AH32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AI32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AJ32" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK32" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-94300</v>
+      </c>
+      <c r="E33" s="3">
         <v>244300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-112700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-102300</v>
       </c>
-      <c r="G33" s="3">
-        <v>-109300</v>
-      </c>
       <c r="H33" s="3">
+        <v>-108300</v>
+      </c>
+      <c r="I33" s="3">
         <v>-90400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-96700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-91100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-98700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>142800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-96100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-82800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-96500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-38300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-109600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-72000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-69200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-64700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-28100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-76300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-201600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-95500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-34500</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-34200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-31700</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-31100</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-22300</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-52600</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-16600</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-216700</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-70400</v>
       </c>
-      <c r="AH33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AI33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AJ33" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK33" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3408,221 +3484,230 @@
       <c r="AJ34" s="3">
         <v>0</v>
       </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-94300</v>
+      </c>
+      <c r="E35" s="3">
         <v>244300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-112700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-102300</v>
       </c>
-      <c r="G35" s="3">
-        <v>-109300</v>
-      </c>
       <c r="H35" s="3">
+        <v>-108300</v>
+      </c>
+      <c r="I35" s="3">
         <v>-90400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-96700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-91100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-98700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>142800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-96100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-82800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-96500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-38300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-109600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-72000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-69200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-64700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-28100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-76300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-201600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-95500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-34500</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-34200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-31700</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-31100</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-22300</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-52600</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-16600</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-216700</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-70400</v>
       </c>
-      <c r="AH35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AI35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AJ35" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK35" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44104</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44012</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43921</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43830</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43738</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43646</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43555</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43465</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43373</v>
       </c>
-      <c r="AH38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AI38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AJ38" s="2" t="s">
         <v>3</v>
       </c>
+      <c r="AK38" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3659,8 +3744,9 @@
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3697,95 +3783,96 @@
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>288300</v>
+      </c>
+      <c r="E41" s="3">
         <v>294900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>268000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>282100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>527900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>282000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>230200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>292800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>287800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>435900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>169000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>225500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>249800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>232800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>156500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>265600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>296800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>560000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>612000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>212000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>97200</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>162200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>137900</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>125300</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>126100</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>37200</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>37800</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>37900</v>
       </c>
-      <c r="AE41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3801,95 +3888,98 @@
       <c r="AJ41" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK41" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>923400</v>
+      </c>
+      <c r="E42" s="3">
         <v>950300</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>807000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>868200</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>692000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>568800</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>695600</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>715400</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>806700</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>754000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>846400</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>847500</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>809700</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>845400</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>938000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>900500</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>925800</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>405700</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>321400</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>403300</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>406200</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>137500</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>64300</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>102600</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>127400</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>54600</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>73100</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>88900</v>
       </c>
-      <c r="AE42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3905,8 +3995,11 @@
       <c r="AJ42" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK42" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3946,8 +4039,8 @@
       <c r="O43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P43" s="3">
-        <v>0</v>
+      <c r="P43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q43" s="3">
         <v>0</v>
@@ -3959,17 +4052,17 @@
         <v>0</v>
       </c>
       <c r="T43" s="3">
+        <v>0</v>
+      </c>
+      <c r="U43" s="3">
         <v>300000</v>
       </c>
-      <c r="U43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V43" s="3">
+      <c r="V43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W43" s="3">
         <v>50000</v>
       </c>
-      <c r="W43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3985,8 +4078,8 @@
       <c r="AB43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC43" s="3">
-        <v>0</v>
+      <c r="AC43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AD43" s="3">
         <v>0</v>
@@ -4009,8 +4102,11 @@
       <c r="AJ43" s="3">
         <v>0</v>
       </c>
+      <c r="AK43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4050,8 +4146,8 @@
       <c r="O44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P44" s="3">
-        <v>0</v>
+      <c r="P44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q44" s="3">
         <v>0</v>
@@ -4113,8 +4209,11 @@
       <c r="AJ44" s="3">
         <v>0</v>
       </c>
+      <c r="AK44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4154,54 +4253,54 @@
       <c r="O45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P45" s="3">
+      <c r="P45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q45" s="3">
         <v>14800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>14400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>13800</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>16900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>7400</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>8000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>12700</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>11100</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>8700</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>6500</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>6900</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>6200</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>2700</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>3900</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>2600</v>
       </c>
-      <c r="AE45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF45" s="3" t="s">
         <v>3</v>
       </c>
@@ -4217,95 +4316,98 @@
       <c r="AJ45" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK45" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1267000</v>
+      </c>
+      <c r="E46" s="3">
         <v>1268700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1098500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1175500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1247600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>878100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>945500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1029400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1121700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1211000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1039500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1094800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1083000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1092900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1108900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1179900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1239500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1273000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>941400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>678000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>514600</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>308300</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>208700</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>234800</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>259600</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>94500</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>114800</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>129400</v>
       </c>
-      <c r="AE46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF46" s="3" t="s">
         <v>3</v>
       </c>
@@ -4321,8 +4423,11 @@
       <c r="AJ46" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK46" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4362,8 +4467,8 @@
       <c r="O47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P47" s="3">
-        <v>0</v>
+      <c r="P47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q47" s="3">
         <v>0</v>
@@ -4374,18 +4479,18 @@
       <c r="S47" s="3">
         <v>0</v>
       </c>
-      <c r="T47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U47" s="3">
+      <c r="T47" s="3">
+        <v>0</v>
+      </c>
+      <c r="U47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V47" s="3">
         <v>24500</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>29400</v>
       </c>
-      <c r="W47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X47" s="3" t="s">
         <v>3</v>
       </c>
@@ -4401,8 +4506,8 @@
       <c r="AB47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC47" s="3">
-        <v>0</v>
+      <c r="AC47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AD47" s="3">
         <v>0</v>
@@ -4425,95 +4530,98 @@
       <c r="AJ47" s="3">
         <v>0</v>
       </c>
+      <c r="AK47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>199400</v>
+      </c>
+      <c r="E48" s="3">
         <v>205200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>205300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>208400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>211800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>216300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>218200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>224300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>229900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>237800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>239700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>242300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>238000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>234100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>226700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>223500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>199800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>187000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>174700</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>169700</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>158800</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>125400</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>51200</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>48600</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>46900</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>43200</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>38000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>36800</v>
       </c>
-      <c r="AE48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF48" s="3" t="s">
         <v>3</v>
       </c>
@@ -4529,8 +4637,11 @@
       <c r="AJ48" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK48" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4633,8 +4744,11 @@
       <c r="AJ49" s="3">
         <v>0</v>
       </c>
+      <c r="AK49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4737,8 +4851,11 @@
       <c r="AJ50" s="3">
         <v>0</v>
       </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4841,95 +4958,98 @@
       <c r="AJ51" s="3">
         <v>0</v>
       </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>14500</v>
+      </c>
+      <c r="E52" s="3">
         <v>7300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>7200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>7300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>7500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>9400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>7600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>7500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>8100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>10900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>11300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>16800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>11300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>14700</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>14600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>15000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>14100</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>14500</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>15900</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>16000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>19900</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>18000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>18400</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>16600</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>16100</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>18300</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>17800</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>14400</v>
       </c>
-      <c r="AE52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4945,8 +5065,11 @@
       <c r="AJ52" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK52" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5049,95 +5172,98 @@
       <c r="AJ53" s="3">
         <v>0</v>
       </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1480800</v>
+      </c>
+      <c r="E54" s="3">
         <v>1481200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1311100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1391200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1466900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1103800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1171400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1261300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1359800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1459700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1290500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1353900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1332400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1341700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1350300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1418400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1453400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1474500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1156600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>893100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>693200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>451700</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>278300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>300000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>322600</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>156100</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>170600</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>180500</v>
       </c>
-      <c r="AE54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF54" s="3" t="s">
         <v>3</v>
       </c>
@@ -5153,8 +5279,11 @@
       <c r="AJ54" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK54" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5191,8 +5320,9 @@
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5229,95 +5359,96 @@
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>12300</v>
+      </c>
+      <c r="E57" s="3">
         <v>10200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>9500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>10600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>7700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>3900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>3800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>4400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>3200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>6900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>14100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>9000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>7000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>7100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>6300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>7500</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>7300</v>
-      </c>
-      <c r="V57" s="3">
-        <v>8000</v>
       </c>
       <c r="W57" s="3">
         <v>8000</v>
       </c>
       <c r="X57" s="3">
+        <v>8000</v>
+      </c>
+      <c r="Y57" s="3">
         <v>6300</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>6600</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>6200</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>6100</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>7800</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>3900</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>4000</v>
       </c>
-      <c r="AE57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF57" s="3" t="s">
         <v>3</v>
       </c>
@@ -5333,76 +5464,79 @@
       <c r="AJ57" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK57" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>14800</v>
+      </c>
+      <c r="E58" s="3">
         <v>14400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>12700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>12900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>13200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>13500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>12900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>12600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>12200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>12800</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>13000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>12400</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>12600</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1900</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>2200</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>2400</v>
-      </c>
-      <c r="S58" s="3">
-        <v>2300</v>
       </c>
       <c r="T58" s="3">
         <v>2300</v>
       </c>
       <c r="U58" s="3">
-        <v>2200</v>
+        <v>2300</v>
       </c>
       <c r="V58" s="3">
         <v>2200</v>
       </c>
       <c r="W58" s="3">
-        <v>2100</v>
+        <v>2200</v>
       </c>
       <c r="X58" s="3">
         <v>2100</v>
       </c>
       <c r="Y58" s="3">
-        <v>1700</v>
+        <v>2100</v>
       </c>
       <c r="Z58" s="3">
         <v>1700</v>
@@ -5411,17 +5545,17 @@
         <v>1700</v>
       </c>
       <c r="AB58" s="3">
+        <v>1700</v>
+      </c>
+      <c r="AC58" s="3">
         <v>1300</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>800</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>7300</v>
       </c>
-      <c r="AE58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF58" s="3" t="s">
         <v>3</v>
       </c>
@@ -5437,95 +5571,98 @@
       <c r="AJ58" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK58" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>20700</v>
+      </c>
+      <c r="E59" s="3">
         <v>22700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>124000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>118800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>98300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>128600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>124000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>140000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>157800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>156100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>171600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>163800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>172800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>212700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>229600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>202800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>210200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>203700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>91900</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>118500</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>92000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>93900</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>39100</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>31100</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>23700</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>20000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>15300</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>56200</v>
       </c>
-      <c r="AE59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF59" s="3" t="s">
         <v>3</v>
       </c>
@@ -5541,95 +5678,98 @@
       <c r="AJ59" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK59" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>74600</v>
+      </c>
+      <c r="E60" s="3">
         <v>96900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>182600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>174100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>141500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>182100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>166200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>177300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>187200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>205600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>220400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>209500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>219900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>223600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>238900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>212300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>218800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>213400</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>101400</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>128700</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>102100</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>102300</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>47500</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>39000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>31400</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>29100</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>19900</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>52200</v>
       </c>
-      <c r="AE60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF60" s="3" t="s">
         <v>3</v>
       </c>
@@ -5645,95 +5785,98 @@
       <c r="AJ60" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK60" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>236000</v>
+      </c>
+      <c r="E61" s="3">
         <v>139800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>138700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>141900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>144900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>148000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>149100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>152600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>155900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>159900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>160900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>164700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>166300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1200</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1400</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1800</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>2400</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>3000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>3600</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>4200</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>4700</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>5300</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>4400</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>4900</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>5300</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>4400</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>2800</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>300</v>
       </c>
-      <c r="AE61" s="3">
-        <v>0</v>
-      </c>
       <c r="AF61" s="3">
         <v>0</v>
       </c>
@@ -5749,92 +5892,95 @@
       <c r="AJ61" s="3">
         <v>0</v>
       </c>
+      <c r="AK61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>5800</v>
+      </c>
+      <c r="E62" s="3">
         <v>6100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>13600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>8000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>7900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>7000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>6900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>3600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>3000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>5600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>11800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>12900</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>383500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>395500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>404100</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>403100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>431300</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>197800</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>211600</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>164000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>98500</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>26300</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>25300</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>24500</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>21600</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>21100</v>
       </c>
-      <c r="AD62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE62" s="3" t="s">
         <v>3</v>
       </c>
@@ -5853,8 +5999,11 @@
       <c r="AJ62" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK62" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5957,8 +6106,11 @@
       <c r="AJ63" s="3">
         <v>0</v>
       </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6061,8 +6213,11 @@
       <c r="AJ64" s="3">
         <v>0</v>
       </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6165,95 +6320,98 @@
       <c r="AJ65" s="3">
         <v>0</v>
       </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>316400</v>
+      </c>
+      <c r="E66" s="3">
         <v>242800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>345100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>344300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>343800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>370300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>380100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>407200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>446300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>478400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>511600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>542200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>570800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>608200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>635800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>618200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>624300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>647700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>302700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>344500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>270800</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>206100</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>78200</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>69200</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>61200</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>55200</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>43800</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>36900</v>
       </c>
-      <c r="AE66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF66" s="3" t="s">
         <v>3</v>
       </c>
@@ -6269,8 +6427,11 @@
       <c r="AJ66" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK66" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6307,8 +6468,9 @@
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6411,8 +6573,11 @@
       <c r="AJ68" s="3">
         <v>0</v>
       </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6515,8 +6680,11 @@
       <c r="AJ69" s="3">
         <v>0</v>
       </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6593,17 +6761,17 @@
         <v>0</v>
       </c>
       <c r="AB70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC70" s="3">
         <v>302000</v>
       </c>
-      <c r="AC70" s="3">
+      <c r="AD70" s="3">
         <v>298800</v>
       </c>
-      <c r="AD70" s="3">
+      <c r="AE70" s="3">
         <v>439200</v>
       </c>
-      <c r="AE70" s="3">
-        <v>0</v>
-      </c>
       <c r="AF70" s="3">
         <v>0</v>
       </c>
@@ -6619,8 +6787,11 @@
       <c r="AJ70" s="3">
         <v>0</v>
       </c>
+      <c r="AK70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6723,95 +6894,98 @@
       <c r="AJ71" s="3">
         <v>0</v>
       </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1735500</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1641200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1890900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1778200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1675900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-1566600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-1476300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-1379600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-1288600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-1189900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-1332700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-1236600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-1153800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-1057400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-1019000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-909400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-837500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-768300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-703600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-675400</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-599200</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-397600</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-302200</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-267700</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-233500</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-203000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-175200</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-156200</v>
       </c>
-      <c r="AE72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF72" s="3" t="s">
         <v>3</v>
       </c>
@@ -6827,8 +7001,11 @@
       <c r="AJ72" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK72" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6931,8 +7108,11 @@
       <c r="AJ73" s="3">
         <v>0</v>
       </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7035,8 +7215,11 @@
       <c r="AJ74" s="3">
         <v>0</v>
       </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7139,95 +7322,98 @@
       <c r="AJ75" s="3">
         <v>0</v>
       </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1164400</v>
+      </c>
+      <c r="E76" s="3">
         <v>1238400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>966000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1046800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1123100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>733500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>791300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>854100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>913500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>981300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>778900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>811600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>761500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>733500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>714500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>800200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>829100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>826700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>853800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>548600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>422400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>245600</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>200100</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>230800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>261400</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>-201100</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>-172100</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>-295500</v>
       </c>
-      <c r="AE76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF76" s="3" t="s">
         <v>3</v>
       </c>
@@ -7243,8 +7429,11 @@
       <c r="AJ76" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK76" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7347,221 +7536,230 @@
       <c r="AJ77" s="3">
         <v>0</v>
       </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44104</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44012</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43921</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43830</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43738</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43646</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43555</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43465</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43373</v>
       </c>
-      <c r="AH80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AI80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AJ80" s="2" t="s">
         <v>3</v>
       </c>
+      <c r="AK80" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-94300</v>
+      </c>
+      <c r="E81" s="3">
         <v>244300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-112700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-102300</v>
       </c>
-      <c r="G81" s="3">
-        <v>-109300</v>
-      </c>
       <c r="H81" s="3">
+        <v>-108300</v>
+      </c>
+      <c r="I81" s="3">
         <v>-90400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-96700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-91100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-98700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>142800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-96100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-82800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-96500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-38300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-109600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-72000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-69200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-64700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-28100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-76300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-201600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-95500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-34500</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-34200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-31700</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-31100</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-22300</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-52600</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-16600</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-216700</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-70400</v>
       </c>
-      <c r="AH81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AI81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AJ81" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK81" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7598,112 +7796,116 @@
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>5500</v>
+      </c>
+      <c r="E83" s="3">
         <v>5400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>5500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>5600</v>
-      </c>
-      <c r="G83" s="3">
-        <v>5400</v>
       </c>
       <c r="H83" s="3">
         <v>5400</v>
       </c>
       <c r="I83" s="3">
+        <v>5400</v>
+      </c>
+      <c r="J83" s="3">
         <v>5200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>4800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>4600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>3900</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>3500</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>3400</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>3300</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>3900</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>3500</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>3400</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>3300</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>2600</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>1800</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>1700</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>1400</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>1300</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>1200</v>
-      </c>
-      <c r="Z83" s="3">
-        <v>1100</v>
       </c>
       <c r="AA83" s="3">
         <v>1100</v>
       </c>
       <c r="AB83" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AC83" s="3">
         <v>1000</v>
-      </c>
-      <c r="AC83" s="3">
-        <v>900</v>
       </c>
       <c r="AD83" s="3">
         <v>900</v>
       </c>
       <c r="AE83" s="3">
+        <v>900</v>
+      </c>
+      <c r="AF83" s="3">
         <v>700</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>500</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>100</v>
       </c>
-      <c r="AH83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AI83" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AJ83" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK83" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7806,8 +8008,11 @@
       <c r="AJ84" s="3">
         <v>0</v>
       </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7910,8 +8115,11 @@
       <c r="AJ85" s="3">
         <v>0</v>
       </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8014,8 +8222,11 @@
       <c r="AJ86" s="3">
         <v>0</v>
       </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8118,8 +8329,11 @@
       <c r="AJ87" s="3">
         <v>0</v>
       </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8222,112 +8436,118 @@
       <c r="AJ88" s="3">
         <v>0</v>
       </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-128500</v>
+      </c>
+      <c r="E89" s="3">
         <v>-83300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-81500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-76500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-103900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-76400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-88100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-83000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-99700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>135100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-89800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-84700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-109800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-69200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-74500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-52300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>218500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>1800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>3000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-32500</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-38600</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-24300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-21200</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-22800</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-27400</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-17800</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-17000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>16900</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-25900</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>4200</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-9400</v>
       </c>
-      <c r="AH89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AI89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AJ89" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK89" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8364,112 +8584,116 @@
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-3700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-5000</v>
-      </c>
-      <c r="F91" s="3">
-        <v>-3100</v>
       </c>
       <c r="G91" s="3">
         <v>-3100</v>
       </c>
       <c r="H91" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="I91" s="3">
         <v>-3000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-2000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-2400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-3600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-7900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-16200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-6000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-8300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-11800</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-21600</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-7300</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-13400</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-5800</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-16200</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-11500</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-8100</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-2800</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-2400</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-3000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-2200</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-1400</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-6600</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-2400</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-11200</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-700</v>
       </c>
-      <c r="AH91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AI91" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AJ91" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK91" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8572,8 +8796,11 @@
       <c r="AJ92" s="3">
         <v>0</v>
       </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8676,112 +8903,118 @@
       <c r="AJ93" s="3">
         <v>0</v>
       </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>25300</v>
+      </c>
+      <c r="E94" s="3">
         <v>108400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>65700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-170400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-125100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>126300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>24700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>87500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-53500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>98100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-10200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-41500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>25500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>113400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-36200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-1300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-537300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-77500</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>76100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-13100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-279600</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-81400</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>35200</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>22900</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-76800</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>16600</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-83200</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>2400</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-2400</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>22000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-2200</v>
       </c>
-      <c r="AH94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AI94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AJ94" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK94" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8818,8 +9051,9 @@
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8859,8 +9093,8 @@
       <c r="O96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="P96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -8922,8 +9156,11 @@
       <c r="AJ96" s="3">
         <v>0</v>
       </c>
+      <c r="AK96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9026,8 +9263,11 @@
       <c r="AJ97" s="3">
         <v>0</v>
       </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9130,8 +9370,11 @@
       <c r="AJ98" s="3">
         <v>0</v>
       </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9234,112 +9477,118 @@
       <c r="AJ99" s="3">
         <v>0</v>
       </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>96600</v>
+      </c>
+      <c r="E100" s="3">
         <v>1900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>1700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>1100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>473400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>3400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>1300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>2900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>33700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>36800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>107500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>98400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>32000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>1600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>22300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>55700</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>21500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>320900</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>160400</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>253300</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>130000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>100</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-800</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>193000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>700</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>2700</v>
       </c>
-      <c r="AD100" s="3">
-        <v>0</v>
-      </c>
       <c r="AE100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF100" s="3">
         <v>37900</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>120100</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>9900</v>
       </c>
-      <c r="AH100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AI100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AJ100" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK100" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9379,8 +9628,8 @@
       <c r="O101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
+      <c r="P101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q101" s="3">
         <v>0</v>
@@ -9442,108 +9691,114 @@
       <c r="AJ101" s="3">
         <v>0</v>
       </c>
+      <c r="AK101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-6600</v>
+      </c>
+      <c r="E102" s="3">
         <v>27000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-14100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-245800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>244400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>53400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-62200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>4600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-150300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>266900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-63200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-18600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>14100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>76300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-109100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-31200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-263200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-54100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>400000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>114800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-64900</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>24300</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>14100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-700</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>88800</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-500</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-100</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-106500</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>9700</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>105900</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-500</v>
       </c>
-      <c r="AH102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AI102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AJ102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
